--- a/Översikt ÄLMHULT.xlsx
+++ b/Översikt ÄLMHULT.xlsx
@@ -601,7 +601,7 @@
         <v>46209</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>45786</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
         <v>46041</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
         <v>45945</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>44883</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>45215</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>45645</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>46211</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>44889</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>45012</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         <v>45183</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>44830</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
         <v>44883</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         <v>46171</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         <v>45818</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>45050</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>45908</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2454,7 +2454,7 @@
         <v>45560</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2563,7 +2563,7 @@
         <v>45888</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         <v>45932</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2777,7 +2777,7 @@
         <v>45631</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
         <v>45218</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         <v>45386</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3092,7 +3092,7 @@
         <v>45719</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
         <v>44882</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3302,7 +3302,7 @@
         <v>45280</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3407,7 +3407,7 @@
         <v>46129</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         <v>45769</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         <v>46204</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3722,7 +3722,7 @@
         <v>45763</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3827,7 +3827,7 @@
         <v>45856</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3936,7 +3936,7 @@
         <v>44869</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4041,7 +4041,7 @@
         <v>45786</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4146,7 +4146,7 @@
         <v>46043</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4251,7 +4251,7 @@
         <v>44609</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4324,7 +4324,7 @@
         <v>44525</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4397,7 +4397,7 @@
         <v>44785</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4470,7 +4470,7 @@
         <v>44785</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4543,7 +4543,7 @@
         <v>44785</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4616,7 +4616,7 @@
         <v>44477</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4689,7 +4689,7 @@
         <v>44473</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4762,7 +4762,7 @@
         <v>44463</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4835,7 +4835,7 @@
         <v>44463</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4908,7 +4908,7 @@
         <v>44515</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4981,7 +4981,7 @@
         <v>44802</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5054,7 +5054,7 @@
         <v>44785</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5127,7 +5127,7 @@
         <v>44802</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5200,7 +5200,7 @@
         <v>44749</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5273,7 +5273,7 @@
         <v>44474</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5346,7 +5346,7 @@
         <v>44798</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5419,7 +5419,7 @@
         <v>44523</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5492,7 +5492,7 @@
         <v>44503</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5565,7 +5565,7 @@
         <v>44503</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5638,7 +5638,7 @@
         <v>44785</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5711,7 +5711,7 @@
         <v>44665</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5789,7 +5789,7 @@
         <v>44462</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5862,7 +5862,7 @@
         <v>44846</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5935,7 +5935,7 @@
         <v>44460</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6008,7 +6008,7 @@
         <v>44847</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         <v>44498</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6154,7 +6154,7 @@
         <v>44690</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6227,7 +6227,7 @@
         <v>44812</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6300,7 +6300,7 @@
         <v>44504</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6373,7 +6373,7 @@
         <v>44602</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6446,7 +6446,7 @@
         <v>44512</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6519,7 +6519,7 @@
         <v>44621</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6592,7 +6592,7 @@
         <v>44609</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6665,7 +6665,7 @@
         <v>44487</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6738,7 +6738,7 @@
         <v>44721</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6811,7 +6811,7 @@
         <v>44587</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6889,7 +6889,7 @@
         <v>44802</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6962,7 +6962,7 @@
         <v>44509</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7035,7 +7035,7 @@
         <v>44739</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7108,7 +7108,7 @@
         <v>44463</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7181,7 +7181,7 @@
         <v>44733</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7254,7 +7254,7 @@
         <v>44551</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7327,7 +7327,7 @@
         <v>44621</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7400,7 +7400,7 @@
         <v>44854</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7473,7 +7473,7 @@
         <v>44854</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7546,7 +7546,7 @@
         <v>44524</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7619,7 +7619,7 @@
         <v>44680</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7692,7 +7692,7 @@
         <v>44690</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7765,7 +7765,7 @@
         <v>44690</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7838,7 +7838,7 @@
         <v>44460</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7911,7 +7911,7 @@
         <v>44477</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7984,7 +7984,7 @@
         <v>44865</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8057,7 +8057,7 @@
         <v>44496</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8130,7 +8130,7 @@
         <v>44721</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8203,7 +8203,7 @@
         <v>44525</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8276,7 +8276,7 @@
         <v>44685</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8349,7 +8349,7 @@
         <v>44474</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8422,7 +8422,7 @@
         <v>44596</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8495,7 +8495,7 @@
         <v>44643</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8568,7 +8568,7 @@
         <v>44510</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8641,7 +8641,7 @@
         <v>44522</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8714,7 +8714,7 @@
         <v>44636</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         <v>44657</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8860,7 +8860,7 @@
         <v>44491</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8933,7 +8933,7 @@
         <v>44831</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9006,7 +9006,7 @@
         <v>44831</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9079,7 +9079,7 @@
         <v>45433</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9152,7 +9152,7 @@
         <v>45244</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9225,7 +9225,7 @@
         <v>45209</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9298,7 +9298,7 @@
         <v>45062</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9371,7 +9371,7 @@
         <v>45098</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9464,7 +9464,7 @@
         <v>45348</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9537,7 +9537,7 @@
         <v>45734</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9610,7 +9610,7 @@
         <v>45457</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9683,7 +9683,7 @@
         <v>45735</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9756,7 +9756,7 @@
         <v>45735</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9829,7 +9829,7 @@
         <v>44496</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9902,7 +9902,7 @@
         <v>45610</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9975,7 +9975,7 @@
         <v>44826</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10048,7 +10048,7 @@
         <v>44962</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10121,7 +10121,7 @@
         <v>44610</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10194,7 +10194,7 @@
         <v>45254</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10267,7 +10267,7 @@
         <v>45469</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10340,7 +10340,7 @@
         <v>45554</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10413,7 +10413,7 @@
         <v>45543</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10486,7 +10486,7 @@
         <v>45578</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10559,7 +10559,7 @@
         <v>45049</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10632,7 +10632,7 @@
         <v>45457</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10705,7 +10705,7 @@
         <v>45457</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10778,7 +10778,7 @@
         <v>45133</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10851,7 +10851,7 @@
         <v>44473</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10924,7 +10924,7 @@
         <v>45359</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10997,7 +10997,7 @@
         <v>45737</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11070,7 +11070,7 @@
         <v>44496</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11143,7 +11143,7 @@
         <v>45469</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11221,7 +11221,7 @@
         <v>45720</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11294,7 +11294,7 @@
         <v>45133</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11367,7 +11367,7 @@
         <v>45575</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11440,7 +11440,7 @@
         <v>45175</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11513,7 +11513,7 @@
         <v>45566</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11586,7 +11586,7 @@
         <v>45222</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11659,7 +11659,7 @@
         <v>45222</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11732,7 +11732,7 @@
         <v>45309</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11805,7 +11805,7 @@
         <v>44876</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11878,7 +11878,7 @@
         <v>44686</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11951,7 +11951,7 @@
         <v>44994</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12024,7 +12024,7 @@
         <v>45638</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12097,7 +12097,7 @@
         <v>45638</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12170,7 +12170,7 @@
         <v>45051</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12243,7 +12243,7 @@
         <v>45103</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12316,7 +12316,7 @@
         <v>45187</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12389,7 +12389,7 @@
         <v>44817</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12462,7 +12462,7 @@
         <v>45240</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12540,7 +12540,7 @@
         <v>45315</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12613,7 +12613,7 @@
         <v>45350</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12686,7 +12686,7 @@
         <v>45693</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12759,7 +12759,7 @@
         <v>44853</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12832,7 +12832,7 @@
         <v>45303</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12905,7 +12905,7 @@
         <v>45443</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12978,7 +12978,7 @@
         <v>45290</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13051,7 +13051,7 @@
         <v>44935</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13124,7 +13124,7 @@
         <v>45586</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13197,7 +13197,7 @@
         <v>45180</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13270,7 +13270,7 @@
         <v>44979</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13343,7 +13343,7 @@
         <v>44859</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13416,7 +13416,7 @@
         <v>45771</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13489,7 +13489,7 @@
         <v>45015</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13562,7 +13562,7 @@
         <v>44958</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13635,7 +13635,7 @@
         <v>44861</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13708,7 +13708,7 @@
         <v>45062</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13781,7 +13781,7 @@
         <v>45414</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13854,7 +13854,7 @@
         <v>45681</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13927,7 +13927,7 @@
         <v>45460</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14000,7 +14000,7 @@
         <v>45090</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14073,7 +14073,7 @@
         <v>44994</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14146,7 +14146,7 @@
         <v>44994</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14219,7 +14219,7 @@
         <v>45042</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14292,7 +14292,7 @@
         <v>44897</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14365,7 +14365,7 @@
         <v>45373</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14443,7 +14443,7 @@
         <v>45680</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14516,7 +14516,7 @@
         <v>44921</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14589,7 +14589,7 @@
         <v>45715</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14662,7 +14662,7 @@
         <v>45078</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14735,7 +14735,7 @@
         <v>45145</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14808,7 +14808,7 @@
         <v>45352</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14886,7 +14886,7 @@
         <v>45228</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14959,7 +14959,7 @@
         <v>45681</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15032,7 +15032,7 @@
         <v>45068</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15105,7 +15105,7 @@
         <v>45258</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15178,7 +15178,7 @@
         <v>44914</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15251,7 +15251,7 @@
         <v>45608</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15324,7 +15324,7 @@
         <v>45538</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15397,7 +15397,7 @@
         <v>44743</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15470,7 +15470,7 @@
         <v>44503</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15543,7 +15543,7 @@
         <v>45317</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15616,7 +15616,7 @@
         <v>45559</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15689,7 +15689,7 @@
         <v>45547</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15762,7 +15762,7 @@
         <v>45078</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15835,7 +15835,7 @@
         <v>45078</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15908,7 +15908,7 @@
         <v>45254</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15981,7 +15981,7 @@
         <v>45716</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16054,7 +16054,7 @@
         <v>45167</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16127,7 +16127,7 @@
         <v>45817</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16200,7 +16200,7 @@
         <v>45722</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16273,7 +16273,7 @@
         <v>45328</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16346,7 +16346,7 @@
         <v>45930</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16419,7 +16419,7 @@
         <v>45716</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16492,7 +16492,7 @@
         <v>45716</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16570,7 +16570,7 @@
         <v>45630</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16643,7 +16643,7 @@
         <v>45286</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16716,7 +16716,7 @@
         <v>45372</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16789,7 +16789,7 @@
         <v>45251</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16862,7 +16862,7 @@
         <v>44998</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16940,7 +16940,7 @@
         <v>45440</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17013,7 +17013,7 @@
         <v>45884</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17086,7 +17086,7 @@
         <v>44545</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17159,7 +17159,7 @@
         <v>45140</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17232,7 +17232,7 @@
         <v>45733</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17305,7 +17305,7 @@
         <v>45181</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17378,7 +17378,7 @@
         <v>45637</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17451,7 +17451,7 @@
         <v>45887</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17524,7 +17524,7 @@
         <v>45888</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17597,7 +17597,7 @@
         <v>45537</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17670,7 +17670,7 @@
         <v>45111</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17743,7 +17743,7 @@
         <v>45348</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17816,7 +17816,7 @@
         <v>45233</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17889,7 +17889,7 @@
         <v>45233</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17962,7 +17962,7 @@
         <v>45531</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18040,7 +18040,7 @@
         <v>45883</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18113,7 +18113,7 @@
         <v>44523</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18186,7 +18186,7 @@
         <v>45211</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18259,7 +18259,7 @@
         <v>45215</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18332,7 +18332,7 @@
         <v>45911</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18405,7 +18405,7 @@
         <v>45629</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18478,7 +18478,7 @@
         <v>45170</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18551,7 +18551,7 @@
         <v>45897</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18624,7 +18624,7 @@
         <v>45887</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18697,7 +18697,7 @@
         <v>45898</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18770,7 +18770,7 @@
         <v>45531</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18843,7 +18843,7 @@
         <v>45252</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18916,7 +18916,7 @@
         <v>45748</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18989,7 +18989,7 @@
         <v>45006</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19067,7 +19067,7 @@
         <v>45938</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19140,7 +19140,7 @@
         <v>45089</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19213,7 +19213,7 @@
         <v>45608</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19286,7 +19286,7 @@
         <v>45734</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19359,7 +19359,7 @@
         <v>45211</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19432,7 +19432,7 @@
         <v>46140</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19510,7 +19510,7 @@
         <v>45911</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19583,7 +19583,7 @@
         <v>45915</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19661,7 +19661,7 @@
         <v>45215</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19734,7 +19734,7 @@
         <v>45376</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19807,7 +19807,7 @@
         <v>45134</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19880,7 +19880,7 @@
         <v>45917</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19958,7 +19958,7 @@
         <v>45917</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20036,7 +20036,7 @@
         <v>45917</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20114,7 +20114,7 @@
         <v>45916</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20187,7 +20187,7 @@
         <v>45916</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20260,7 +20260,7 @@
         <v>44784</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20338,7 +20338,7 @@
         <v>45373</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20416,7 +20416,7 @@
         <v>45373</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20494,7 +20494,7 @@
         <v>45084</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20567,7 +20567,7 @@
         <v>45010</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20640,7 +20640,7 @@
         <v>45929</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20713,7 +20713,7 @@
         <v>45930</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20786,7 +20786,7 @@
         <v>45930</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20859,7 +20859,7 @@
         <v>45631</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20932,7 +20932,7 @@
         <v>45355</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21005,7 +21005,7 @@
         <v>45355</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21083,7 +21083,7 @@
         <v>45529</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21156,7 +21156,7 @@
         <v>46147</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21229,7 +21229,7 @@
         <v>44943</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21302,7 +21302,7 @@
         <v>45589</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21375,7 +21375,7 @@
         <v>45010</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21448,7 +21448,7 @@
         <v>45271</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21521,7 +21521,7 @@
         <v>45944</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21594,7 +21594,7 @@
         <v>45945</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21667,7 +21667,7 @@
         <v>45947</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21740,7 +21740,7 @@
         <v>45916</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21818,7 +21818,7 @@
         <v>45952</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21891,7 +21891,7 @@
         <v>46141</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21964,7 +21964,7 @@
         <v>45085</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22037,7 +22037,7 @@
         <v>44543</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22110,7 +22110,7 @@
         <v>44865</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22183,7 +22183,7 @@
         <v>45959</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22256,7 +22256,7 @@
         <v>45048</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22329,7 +22329,7 @@
         <v>46155</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22402,7 +22402,7 @@
         <v>45533</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22475,7 +22475,7 @@
         <v>45001</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22548,7 +22548,7 @@
         <v>45282</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22621,7 +22621,7 @@
         <v>46155</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22694,7 +22694,7 @@
         <v>45966</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22767,7 +22767,7 @@
         <v>45966</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22840,7 +22840,7 @@
         <v>45967</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22913,7 +22913,7 @@
         <v>45273</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22986,7 +22986,7 @@
         <v>45273</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23059,7 +23059,7 @@
         <v>45966</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23132,7 +23132,7 @@
         <v>45706</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23205,7 +23205,7 @@
         <v>45969</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23278,7 +23278,7 @@
         <v>45969</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23351,7 +23351,7 @@
         <v>45612</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23424,7 +23424,7 @@
         <v>45615</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23497,7 +23497,7 @@
         <v>45250</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23570,7 +23570,7 @@
         <v>45250</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23643,7 +23643,7 @@
         <v>45251</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23716,7 +23716,7 @@
         <v>45546</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23789,7 +23789,7 @@
         <v>45180</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23862,7 +23862,7 @@
         <v>45539</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23935,7 +23935,7 @@
         <v>45311</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24008,7 +24008,7 @@
         <v>45308</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24081,7 +24081,7 @@
         <v>45384</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24154,7 +24154,7 @@
         <v>46154</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24227,7 +24227,7 @@
         <v>45374</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24300,7 +24300,7 @@
         <v>45706</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24373,7 +24373,7 @@
         <v>45211</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24446,7 +24446,7 @@
         <v>45012</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24519,7 +24519,7 @@
         <v>45314</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24592,7 +24592,7 @@
         <v>45707</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24665,7 +24665,7 @@
         <v>45303</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24738,7 +24738,7 @@
         <v>45653</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24811,7 +24811,7 @@
         <v>45653</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24884,7 +24884,7 @@
         <v>45187</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24957,7 +24957,7 @@
         <v>45716</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25035,7 +25035,7 @@
         <v>45986</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25113,7 +25113,7 @@
         <v>44973</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25186,7 +25186,7 @@
         <v>44942</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25259,7 +25259,7 @@
         <v>45818</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25332,7 +25332,7 @@
         <v>45700</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25405,7 +25405,7 @@
         <v>45061</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25478,7 +25478,7 @@
         <v>45992</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25556,7 +25556,7 @@
         <v>45992</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25634,7 +25634,7 @@
         <v>46076</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25707,7 +25707,7 @@
         <v>44897</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25780,7 +25780,7 @@
         <v>44977</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25853,7 +25853,7 @@
         <v>45628</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25926,7 +25926,7 @@
         <v>45352</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26004,7 +26004,7 @@
         <v>45513</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26077,7 +26077,7 @@
         <v>45992</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26155,7 +26155,7 @@
         <v>45992</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26233,7 +26233,7 @@
         <v>46163</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26306,7 +26306,7 @@
         <v>45166</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26379,7 +26379,7 @@
         <v>45680</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26452,7 +26452,7 @@
         <v>45191</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26525,7 +26525,7 @@
         <v>45999</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26603,7 +26603,7 @@
         <v>44853</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26676,7 +26676,7 @@
         <v>45251</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26749,7 +26749,7 @@
         <v>45999</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26827,7 +26827,7 @@
         <v>46000</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26905,7 +26905,7 @@
         <v>45589</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -26978,7 +26978,7 @@
         <v>44855</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27051,7 +27051,7 @@
         <v>44942</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27124,7 +27124,7 @@
         <v>45680</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27197,7 +27197,7 @@
         <v>45728</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27270,7 +27270,7 @@
         <v>45462</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27343,7 +27343,7 @@
         <v>45412</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27416,7 +27416,7 @@
         <v>46005</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27489,7 +27489,7 @@
         <v>45113</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27562,7 +27562,7 @@
         <v>45421</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27635,7 +27635,7 @@
         <v>45558</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27708,7 +27708,7 @@
         <v>45812</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27781,7 +27781,7 @@
         <v>45090</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27854,7 +27854,7 @@
         <v>45567</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -27927,7 +27927,7 @@
         <v>46168</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28000,7 +28000,7 @@
         <v>45268</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28073,7 +28073,7 @@
         <v>46016</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28146,7 +28146,7 @@
         <v>44930</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28219,7 +28219,7 @@
         <v>44476</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28292,7 +28292,7 @@
         <v>45698</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28365,7 +28365,7 @@
         <v>45177</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28438,7 +28438,7 @@
         <v>44986</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28516,7 +28516,7 @@
         <v>46030</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28589,7 +28589,7 @@
         <v>46035</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28662,7 +28662,7 @@
         <v>45175</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28735,7 +28735,7 @@
         <v>45677</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -28808,7 +28808,7 @@
         <v>45462</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -28881,7 +28881,7 @@
         <v>45081</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -28954,7 +28954,7 @@
         <v>45946</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29027,7 +29027,7 @@
         <v>46037</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29100,7 +29100,7 @@
         <v>46037</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29173,7 +29173,7 @@
         <v>45166</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29246,7 +29246,7 @@
         <v>45595</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29319,7 +29319,7 @@
         <v>44942</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29392,7 +29392,7 @@
         <v>45391</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29465,7 +29465,7 @@
         <v>46038</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29538,7 +29538,7 @@
         <v>45373</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29616,7 +29616,7 @@
         <v>45373</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -29694,7 +29694,7 @@
         <v>45155</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -29767,7 +29767,7 @@
         <v>45911</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -29840,7 +29840,7 @@
         <v>46045</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -29913,7 +29913,7 @@
         <v>45564</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -29986,7 +29986,7 @@
         <v>45010</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30059,7 +30059,7 @@
         <v>46052</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30132,7 +30132,7 @@
         <v>46052</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30205,7 +30205,7 @@
         <v>45113</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30278,7 +30278,7 @@
         <v>45214</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30351,7 +30351,7 @@
         <v>45217</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30424,7 +30424,7 @@
         <v>45156</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30497,7 +30497,7 @@
         <v>44942</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30570,7 +30570,7 @@
         <v>46063</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30643,7 +30643,7 @@
         <v>45539</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -30716,7 +30716,7 @@
         <v>46062</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -30789,7 +30789,7 @@
         <v>45355</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -30867,7 +30867,7 @@
         <v>46061</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -30940,7 +30940,7 @@
         <v>44882</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31013,7 +31013,7 @@
         <v>45175</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31086,7 +31086,7 @@
         <v>45175</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31159,7 +31159,7 @@
         <v>46065</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31232,7 +31232,7 @@
         <v>46066</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31305,7 +31305,7 @@
         <v>45076</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31378,7 +31378,7 @@
         <v>45076</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31451,7 +31451,7 @@
         <v>45653</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31524,7 +31524,7 @@
         <v>44526</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31597,7 +31597,7 @@
         <v>45612</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -31670,7 +31670,7 @@
         <v>46076</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -31743,7 +31743,7 @@
         <v>46184</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -31816,7 +31816,7 @@
         <v>46184</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -31889,7 +31889,7 @@
         <v>45625</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -31962,7 +31962,7 @@
         <v>45827</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32035,7 +32035,7 @@
         <v>44816</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32108,7 +32108,7 @@
         <v>45222</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32181,7 +32181,7 @@
         <v>45211</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32254,7 +32254,7 @@
         <v>45435</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32327,7 +32327,7 @@
         <v>45435</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32400,7 +32400,7 @@
         <v>45435</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32473,7 +32473,7 @@
         <v>44911</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32546,7 +32546,7 @@
         <v>45748</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -32619,7 +32619,7 @@
         <v>45378</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -32692,7 +32692,7 @@
         <v>45141</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -32765,7 +32765,7 @@
         <v>44992</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -32838,7 +32838,7 @@
         <v>44992</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -32911,7 +32911,7 @@
         <v>45202</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -32984,7 +32984,7 @@
         <v>46092</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33057,7 +33057,7 @@
         <v>46093</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33130,7 +33130,7 @@
         <v>45588</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33203,7 +33203,7 @@
         <v>45246</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33276,7 +33276,7 @@
         <v>45792</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33349,7 +33349,7 @@
         <v>44865</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33422,7 +33422,7 @@
         <v>44698</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33495,7 +33495,7 @@
         <v>45189</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33568,7 +33568,7 @@
         <v>46198</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -33641,7 +33641,7 @@
         <v>46105</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -33719,7 +33719,7 @@
         <v>46198</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -33792,7 +33792,7 @@
         <v>46105</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -33870,7 +33870,7 @@
         <v>46105</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -33948,7 +33948,7 @@
         <v>46198</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34021,7 +34021,7 @@
         <v>46105</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34099,7 +34099,7 @@
         <v>46106</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34177,7 +34177,7 @@
         <v>46105</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34255,7 +34255,7 @@
         <v>46105</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34333,7 +34333,7 @@
         <v>46105</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34411,7 +34411,7 @@
         <v>46198</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34484,7 +34484,7 @@
         <v>46107</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34557,7 +34557,7 @@
         <v>45352</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -34635,7 +34635,7 @@
         <v>44687</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -34708,7 +34708,7 @@
         <v>46108</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -34781,7 +34781,7 @@
         <v>46190</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -34859,7 +34859,7 @@
         <v>45467</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -34932,7 +34932,7 @@
         <v>46108</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35005,7 +35005,7 @@
         <v>45211</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35078,7 +35078,7 @@
         <v>45187</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35151,7 +35151,7 @@
         <v>45450</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35224,7 +35224,7 @@
         <v>45253</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35297,7 +35297,7 @@
         <v>45051</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35370,7 +35370,7 @@
         <v>45215</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35443,7 +35443,7 @@
         <v>46202</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35516,7 +35516,7 @@
         <v>46245</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -35589,7 +35589,7 @@
         <v>46125</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -35662,7 +35662,7 @@
         <v>45078</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -35735,7 +35735,7 @@
         <v>45574</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -35808,7 +35808,7 @@
         <v>46245</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -35881,7 +35881,7 @@
         <v>46128</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -35954,7 +35954,7 @@
         <v>44992</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36027,7 +36027,7 @@
         <v>46204</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36100,7 +36100,7 @@
         <v>45244</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36173,7 +36173,7 @@
         <v>45687</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36246,7 +36246,7 @@
         <v>44858</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36319,7 +36319,7 @@
         <v>45539</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36392,7 +36392,7 @@
         <v>45609</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36465,7 +36465,7 @@
         <v>44531</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36538,7 +36538,7 @@
         <v>46204</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -36611,7 +36611,7 @@
         <v>45049</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -36684,7 +36684,7 @@
         <v>45835</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -36757,7 +36757,7 @@
         <v>45679</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -36830,7 +36830,7 @@
         <v>44859</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -36903,7 +36903,7 @@
         <v>44531</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -36976,7 +36976,7 @@
         <v>46204</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37049,7 +37049,7 @@
         <v>46000</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37127,7 +37127,7 @@
         <v>46204</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37200,7 +37200,7 @@
         <v>46247</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37273,7 +37273,7 @@
         <v>45446</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37346,7 +37346,7 @@
         <v>46246</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37419,7 +37419,7 @@
         <v>46247</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -37492,7 +37492,7 @@
         <v>45616</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -37565,7 +37565,7 @@
         <v>46204</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -37638,7 +37638,7 @@
         <v>46204</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -37711,7 +37711,7 @@
         <v>46204</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -37784,7 +37784,7 @@
         <v>46248</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -37857,7 +37857,7 @@
         <v>44587</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -37930,7 +37930,7 @@
         <v>45770</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38003,7 +38003,7 @@
         <v>44582</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38076,7 +38076,7 @@
         <v>45759</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38149,7 +38149,7 @@
         <v>46206</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38222,7 +38222,7 @@
         <v>45531</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38295,7 +38295,7 @@
         <v>46251</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38368,7 +38368,7 @@
         <v>44897</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38441,7 +38441,7 @@
         <v>46251</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -38514,7 +38514,7 @@
         <v>45583</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -38587,7 +38587,7 @@
         <v>46248</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -38660,7 +38660,7 @@
         <v>46206</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -38733,7 +38733,7 @@
         <v>45594</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -38806,7 +38806,7 @@
         <v>46251</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -38884,7 +38884,7 @@
         <v>45469</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -38962,7 +38962,7 @@
         <v>45401</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39035,7 +39035,7 @@
         <v>45092</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39108,7 +39108,7 @@
         <v>45092</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39181,7 +39181,7 @@
         <v>45103</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39254,7 +39254,7 @@
         <v>44760</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39327,7 +39327,7 @@
         <v>46254</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39400,7 +39400,7 @@
         <v>44526</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39473,7 +39473,7 @@
         <v>45268</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -39546,7 +39546,7 @@
         <v>45440</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -39619,7 +39619,7 @@
         <v>46254</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -39692,7 +39692,7 @@
         <v>45244</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -39765,7 +39765,7 @@
         <v>46257</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -39838,7 +39838,7 @@
         <v>46258</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -39911,7 +39911,7 @@
         <v>46258</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -39984,7 +39984,7 @@
         <v>45051</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40057,7 +40057,7 @@
         <v>45176</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40130,7 +40130,7 @@
         <v>46216</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40208,7 +40208,7 @@
         <v>46216</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40286,7 +40286,7 @@
         <v>46216</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40364,7 +40364,7 @@
         <v>44921</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40437,7 +40437,7 @@
         <v>44928</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -40510,7 +40510,7 @@
         <v>46216</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -40588,7 +40588,7 @@
         <v>46216</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -40666,7 +40666,7 @@
         <v>46216</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -40744,7 +40744,7 @@
         <v>44568</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -40817,7 +40817,7 @@
         <v>44634</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -40890,7 +40890,7 @@
         <v>44592</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -40963,7 +40963,7 @@
         <v>44777</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41036,7 +41036,7 @@
         <v>44942</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41109,7 +41109,7 @@
         <v>44942</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41182,7 +41182,7 @@
         <v>45273</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41255,7 +41255,7 @@
         <v>45497</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41328,7 +41328,7 @@
         <v>45217</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41401,7 +41401,7 @@
         <v>44621</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41474,7 +41474,7 @@
         <v>44922</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -41547,7 +41547,7 @@
         <v>46261</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -41620,7 +41620,7 @@
         <v>45169</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -41693,7 +41693,7 @@
         <v>44860</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -41766,7 +41766,7 @@
         <v>45154</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -41839,7 +41839,7 @@
         <v>44636</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -41912,7 +41912,7 @@
         <v>44529</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -41985,7 +41985,7 @@
         <v>46267</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42058,7 +42058,7 @@
         <v>44508</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42131,7 +42131,7 @@
         <v>46268</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42204,7 +42204,7 @@
         <v>44858</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42277,7 +42277,7 @@
         <v>46226</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42350,7 +42350,7 @@
         <v>45776</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42423,7 +42423,7 @@
         <v>46226</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -42496,7 +42496,7 @@
         <v>46226</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -42569,7 +42569,7 @@
         <v>45663</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -42642,7 +42642,7 @@
         <v>45624</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -42715,7 +42715,7 @@
         <v>45781</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -42788,7 +42788,7 @@
         <v>45407</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -42861,7 +42861,7 @@
         <v>46227</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -42934,7 +42934,7 @@
         <v>46227</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43007,7 +43007,7 @@
         <v>46234</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43085,7 +43085,7 @@
         <v>45719</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43158,7 +43158,7 @@
         <v>45527</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43231,7 +43231,7 @@
         <v>45638</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43304,7 +43304,7 @@
         <v>46279</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43377,7 +43377,7 @@
         <v>46280</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43450,7 +43450,7 @@
         <v>46240</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -43528,7 +43528,7 @@
         <v>45799</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -43601,7 +43601,7 @@
         <v>46262</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -43674,7 +43674,7 @@
         <v>46240</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -43752,7 +43752,7 @@
         <v>46240</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -43830,7 +43830,7 @@
         <v>45405</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -43903,7 +43903,7 @@
         <v>44511</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -43976,7 +43976,7 @@
         <v>44511</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44049,7 +44049,7 @@
         <v>45702</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44122,7 +44122,7 @@
         <v>45589</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44195,7 +44195,7 @@
         <v>45460</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44268,7 +44268,7 @@
         <v>45663</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44341,7 +44341,7 @@
         <v>45804</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44414,7 +44414,7 @@
         <v>45612</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44487,7 +44487,7 @@
         <v>45548</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -44560,7 +44560,7 @@
         <v>45818</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -44633,7 +44633,7 @@
         <v>45695</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -44706,7 +44706,7 @@
         <v>45441</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -44779,7 +44779,7 @@
         <v>45335</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -44852,7 +44852,7 @@
         <v>45334</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -44925,7 +44925,7 @@
         <v>45835</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -44998,7 +44998,7 @@
         <v>45834</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45071,7 +45071,7 @@
         <v>45839</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45144,7 +45144,7 @@
         <v>44641</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45217,7 +45217,7 @@
         <v>45841</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45290,7 +45290,7 @@
         <v>45842</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45363,7 +45363,7 @@
         <v>45842</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45436,7 +45436,7 @@
         <v>45842</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -45509,7 +45509,7 @@
         <v>45529</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -45582,7 +45582,7 @@
         <v>45845</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -45655,7 +45655,7 @@
         <v>45846</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -45728,7 +45728,7 @@
         <v>45726</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -45801,7 +45801,7 @@
         <v>45726</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -45874,7 +45874,7 @@
         <v>45854</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -45947,7 +45947,7 @@
         <v>44979</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46020,7 +46020,7 @@
         <v>45819</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46093,7 +46093,7 @@
         <v>45581</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46166,7 +46166,7 @@
         <v>45763</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46239,7 +46239,7 @@
         <v>45763</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46312,7 +46312,7 @@
         <v>45812</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46385,7 +46385,7 @@
         <v>45631</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -46458,7 +46458,7 @@
         <v>45581</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -46531,7 +46531,7 @@
         <v>45867</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -46604,7 +46604,7 @@
         <v>45726</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -46677,7 +46677,7 @@
         <v>45476</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -46750,7 +46750,7 @@
         <v>44634</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -46823,7 +46823,7 @@
         <v>44658</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -46896,7 +46896,7 @@
         <v>44621</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -46969,7 +46969,7 @@
         <v>44474</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47042,7 +47042,7 @@
         <v>44607</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47115,7 +47115,7 @@
         <v>44733</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47193,7 +47193,7 @@
         <v>45302</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47266,7 +47266,7 @@
         <v>45476</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -47339,7 +47339,7 @@
         <v>45649</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -47412,7 +47412,7 @@
         <v>45728</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -47485,7 +47485,7 @@
         <v>45953</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -47558,7 +47558,7 @@
         <v>45967</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -47631,7 +47631,7 @@
         <v>46010</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -47704,7 +47704,7 @@
         <v>46010</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -47777,7 +47777,7 @@
         <v>46029</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -47855,7 +47855,7 @@
         <v>46079</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -47928,7 +47928,7 @@
         <v>46094</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48001,7 +48001,7 @@
         <v>46119</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48074,7 +48074,7 @@
         <v>46182</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>

--- a/Översikt ÄLMHULT.xlsx
+++ b/Översikt ÄLMHULT.xlsx
@@ -601,7 +601,7 @@
         <v>46209</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>45786</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
         <v>46041</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
         <v>45945</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>44883</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>45215</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>45645</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>46211</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>44883</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         <v>45183</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>44889</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>45818</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1919,7 +1919,7 @@
         <v>44830</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         <v>46171</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>45012</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>45050</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>45908</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2454,7 +2454,7 @@
         <v>45386</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2559,7 +2559,7 @@
         <v>45888</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
         <v>45560</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2773,7 +2773,7 @@
         <v>45932</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
         <v>46129</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         <v>45769</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3092,7 +3092,7 @@
         <v>45763</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
         <v>45856</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3306,7 +3306,7 @@
         <v>45631</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3411,7 +3411,7 @@
         <v>45218</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3516,7 +3516,7 @@
         <v>46204</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3621,7 +3621,7 @@
         <v>44882</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3726,7 +3726,7 @@
         <v>45719</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3831,7 +3831,7 @@
         <v>45280</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3936,7 +3936,7 @@
         <v>44869</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4041,7 +4041,7 @@
         <v>45786</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4146,7 +4146,7 @@
         <v>46043</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4251,7 +4251,7 @@
         <v>44609</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4324,7 +4324,7 @@
         <v>44525</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4397,7 +4397,7 @@
         <v>44785</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4470,7 +4470,7 @@
         <v>44785</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4543,7 +4543,7 @@
         <v>44785</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4616,7 +4616,7 @@
         <v>44477</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4689,7 +4689,7 @@
         <v>44473</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4762,7 +4762,7 @@
         <v>44515</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4835,7 +4835,7 @@
         <v>44802</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4908,7 +4908,7 @@
         <v>44785</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4981,7 +4981,7 @@
         <v>44802</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5054,7 +5054,7 @@
         <v>44749</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5127,7 +5127,7 @@
         <v>44474</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5200,7 +5200,7 @@
         <v>44798</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5273,7 +5273,7 @@
         <v>44523</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5346,7 +5346,7 @@
         <v>44503</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5419,7 +5419,7 @@
         <v>44503</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5492,7 +5492,7 @@
         <v>44785</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5565,7 +5565,7 @@
         <v>44665</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5643,7 +5643,7 @@
         <v>44846</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5716,7 +5716,7 @@
         <v>44847</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5789,7 +5789,7 @@
         <v>44498</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5862,7 +5862,7 @@
         <v>44690</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5935,7 +5935,7 @@
         <v>44812</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6008,7 +6008,7 @@
         <v>44504</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         <v>44602</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6154,7 +6154,7 @@
         <v>44621</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6227,7 +6227,7 @@
         <v>44512</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6300,7 +6300,7 @@
         <v>44609</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6373,7 +6373,7 @@
         <v>44487</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6446,7 +6446,7 @@
         <v>44721</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6519,7 +6519,7 @@
         <v>44587</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6597,7 +6597,7 @@
         <v>44802</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6670,7 +6670,7 @@
         <v>44509</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         <v>44739</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6816,7 +6816,7 @@
         <v>44551</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6889,7 +6889,7 @@
         <v>44733</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6962,7 +6962,7 @@
         <v>44621</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7035,7 +7035,7 @@
         <v>44854</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7108,7 +7108,7 @@
         <v>44854</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7181,7 +7181,7 @@
         <v>44680</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7254,7 +7254,7 @@
         <v>44524</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7327,7 +7327,7 @@
         <v>44690</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7400,7 +7400,7 @@
         <v>44690</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7473,7 +7473,7 @@
         <v>44477</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7546,7 +7546,7 @@
         <v>44865</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7619,7 +7619,7 @@
         <v>44496</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7692,7 +7692,7 @@
         <v>44721</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7765,7 +7765,7 @@
         <v>44525</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7838,7 +7838,7 @@
         <v>44685</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7911,7 +7911,7 @@
         <v>44474</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7984,7 +7984,7 @@
         <v>44643</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8057,7 +8057,7 @@
         <v>44596</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8130,7 +8130,7 @@
         <v>44510</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8203,7 +8203,7 @@
         <v>44522</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8276,7 +8276,7 @@
         <v>44636</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8349,7 +8349,7 @@
         <v>44657</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8422,7 +8422,7 @@
         <v>44831</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8495,7 +8495,7 @@
         <v>44831</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8568,7 +8568,7 @@
         <v>44491</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8641,7 +8641,7 @@
         <v>44816</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8714,7 +8714,7 @@
         <v>45716</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         <v>45222</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8860,7 +8860,7 @@
         <v>45222</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8933,7 +8933,7 @@
         <v>45497</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9006,7 +9006,7 @@
         <v>45268</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9079,7 +9079,7 @@
         <v>45211</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9152,7 +9152,7 @@
         <v>44855</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9225,7 +9225,7 @@
         <v>45348</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9298,7 +9298,7 @@
         <v>45215</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9371,7 +9371,7 @@
         <v>45401</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9444,7 +9444,7 @@
         <v>45440</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9517,7 +9517,7 @@
         <v>45254</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9590,7 +9590,7 @@
         <v>45217</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9663,7 +9663,7 @@
         <v>44853</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9736,7 +9736,7 @@
         <v>45539</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9809,7 +9809,7 @@
         <v>45384</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9882,7 +9882,7 @@
         <v>45317</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9955,7 +9955,7 @@
         <v>45457</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10028,7 +10028,7 @@
         <v>45529</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10101,7 +10101,7 @@
         <v>44986</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10179,7 +10179,7 @@
         <v>44865</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10252,7 +10252,7 @@
         <v>45089</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10325,7 +10325,7 @@
         <v>45251</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10398,7 +10398,7 @@
         <v>45309</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10471,7 +10471,7 @@
         <v>44897</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10544,7 +10544,7 @@
         <v>45078</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10617,7 +10617,7 @@
         <v>45078</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10690,7 +10690,7 @@
         <v>45533</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10763,7 +10763,7 @@
         <v>44962</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10836,7 +10836,7 @@
         <v>44973</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10909,7 +10909,7 @@
         <v>45457</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10982,7 +10982,7 @@
         <v>45457</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11055,7 +11055,7 @@
         <v>45140</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11128,7 +11128,7 @@
         <v>46016</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11201,7 +11201,7 @@
         <v>44998</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11279,7 +11279,7 @@
         <v>44582</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11352,7 +11352,7 @@
         <v>44942</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11425,7 +11425,7 @@
         <v>45113</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11498,7 +11498,7 @@
         <v>44545</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11571,7 +11571,7 @@
         <v>45169</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11644,7 +11644,7 @@
         <v>45884</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11717,7 +11717,7 @@
         <v>44943</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11790,7 +11790,7 @@
         <v>45888</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11863,7 +11863,7 @@
         <v>45887</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11936,7 +11936,7 @@
         <v>44930</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12009,7 +12009,7 @@
         <v>46035</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12082,7 +12082,7 @@
         <v>45181</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12155,7 +12155,7 @@
         <v>45637</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12228,7 +12228,7 @@
         <v>45373</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12306,7 +12306,7 @@
         <v>45589</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12379,7 +12379,7 @@
         <v>45373</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12457,7 +12457,7 @@
         <v>45435</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12530,7 +12530,7 @@
         <v>45435</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12603,7 +12603,7 @@
         <v>45435</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12676,7 +12676,7 @@
         <v>44853</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12749,7 +12749,7 @@
         <v>45799</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12822,7 +12822,7 @@
         <v>46038</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12895,7 +12895,7 @@
         <v>46037</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12968,7 +12968,7 @@
         <v>45460</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13041,7 +13041,7 @@
         <v>44994</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13114,7 +13114,7 @@
         <v>44994</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13187,7 +13187,7 @@
         <v>44531</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13260,7 +13260,7 @@
         <v>45373</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13338,7 +13338,7 @@
         <v>44911</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13411,7 +13411,7 @@
         <v>45405</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13484,7 +13484,7 @@
         <v>45702</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13557,7 +13557,7 @@
         <v>45538</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13630,7 +13630,7 @@
         <v>45898</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13703,7 +13703,7 @@
         <v>45897</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13776,7 +13776,7 @@
         <v>45663</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13849,7 +13849,7 @@
         <v>45175</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13922,7 +13922,7 @@
         <v>44503</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13995,7 +13995,7 @@
         <v>44859</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14068,7 +14068,7 @@
         <v>45748</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14141,7 +14141,7 @@
         <v>46045</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14214,7 +14214,7 @@
         <v>44914</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14287,7 +14287,7 @@
         <v>45574</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14360,7 +14360,7 @@
         <v>46052</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14433,7 +14433,7 @@
         <v>45559</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14506,7 +14506,7 @@
         <v>46052</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14579,7 +14579,7 @@
         <v>44511</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14652,7 +14652,7 @@
         <v>44511</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14725,7 +14725,7 @@
         <v>45916</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14798,7 +14798,7 @@
         <v>45681</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14871,7 +14871,7 @@
         <v>45915</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14949,7 +14949,7 @@
         <v>46061</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15022,7 +15022,7 @@
         <v>45917</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15100,7 +15100,7 @@
         <v>45917</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15178,7 +15178,7 @@
         <v>45917</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15256,7 +15256,7 @@
         <v>46063</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15329,7 +15329,7 @@
         <v>46065</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15402,7 +15402,7 @@
         <v>45804</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15475,7 +15475,7 @@
         <v>45687</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15548,7 +15548,7 @@
         <v>45543</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15621,7 +15621,7 @@
         <v>45513</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15694,7 +15694,7 @@
         <v>46076</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15767,7 +15767,7 @@
         <v>45827</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15840,7 +15840,7 @@
         <v>45929</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15913,7 +15913,7 @@
         <v>45554</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15986,7 +15986,7 @@
         <v>45930</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16059,7 +16059,7 @@
         <v>45564</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16132,7 +16132,7 @@
         <v>45254</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16205,7 +16205,7 @@
         <v>45930</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16278,7 +16278,7 @@
         <v>44994</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16351,7 +16351,7 @@
         <v>46093</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16424,7 +16424,7 @@
         <v>45944</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16497,7 +16497,7 @@
         <v>45446</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16570,7 +16570,7 @@
         <v>45945</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16643,7 +16643,7 @@
         <v>46105</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16721,7 +16721,7 @@
         <v>46105</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16799,7 +16799,7 @@
         <v>46105</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16877,7 +16877,7 @@
         <v>46105</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16955,7 +16955,7 @@
         <v>46105</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17033,7 +17033,7 @@
         <v>45947</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17106,7 +17106,7 @@
         <v>45170</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17179,7 +17179,7 @@
         <v>45916</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17257,7 +17257,7 @@
         <v>46105</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17335,7 +17335,7 @@
         <v>46105</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17413,7 +17413,7 @@
         <v>46107</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17486,7 +17486,7 @@
         <v>45952</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17559,7 +17559,7 @@
         <v>46106</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17637,7 +17637,7 @@
         <v>45594</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17710,7 +17710,7 @@
         <v>45588</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17783,7 +17783,7 @@
         <v>45462</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17856,7 +17856,7 @@
         <v>46108</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17929,7 +17929,7 @@
         <v>45258</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18002,7 +18002,7 @@
         <v>46108</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18075,7 +18075,7 @@
         <v>45959</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18148,7 +18148,7 @@
         <v>45578</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18221,7 +18221,7 @@
         <v>45308</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18294,7 +18294,7 @@
         <v>45372</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18367,7 +18367,7 @@
         <v>45629</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18440,7 +18440,7 @@
         <v>45966</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18513,7 +18513,7 @@
         <v>45966</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18586,7 +18586,7 @@
         <v>46125</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18659,7 +18659,7 @@
         <v>45966</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18732,7 +18732,7 @@
         <v>45967</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18805,7 +18805,7 @@
         <v>45969</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18878,7 +18878,7 @@
         <v>45969</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18951,7 +18951,7 @@
         <v>45145</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19024,7 +19024,7 @@
         <v>45548</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19097,7 +19097,7 @@
         <v>45818</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19170,7 +19170,7 @@
         <v>45695</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19243,7 +19243,7 @@
         <v>46128</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19316,7 +19316,7 @@
         <v>45612</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19389,7 +19389,7 @@
         <v>45680</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19462,7 +19462,7 @@
         <v>45469</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19540,7 +19540,7 @@
         <v>45078</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19613,7 +19613,7 @@
         <v>45715</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19686,7 +19686,7 @@
         <v>45631</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19759,7 +19759,7 @@
         <v>45167</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19832,7 +19832,7 @@
         <v>45051</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19905,7 +19905,7 @@
         <v>45986</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19983,7 +19983,7 @@
         <v>45154</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20056,7 +20056,7 @@
         <v>45938</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20129,7 +20129,7 @@
         <v>45722</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20202,7 +20202,7 @@
         <v>44760</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20275,7 +20275,7 @@
         <v>45992</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20353,7 +20353,7 @@
         <v>45610</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20426,7 +20426,7 @@
         <v>45992</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20504,7 +20504,7 @@
         <v>45992</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20582,7 +20582,7 @@
         <v>45835</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20655,7 +20655,7 @@
         <v>44526</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20728,7 +20728,7 @@
         <v>45992</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20806,7 +20806,7 @@
         <v>45531</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20884,7 +20884,7 @@
         <v>45076</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20957,7 +20957,7 @@
         <v>45076</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21030,7 +21030,7 @@
         <v>45911</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21103,7 +21103,7 @@
         <v>45887</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21176,7 +21176,7 @@
         <v>45883</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21249,7 +21249,7 @@
         <v>45817</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21322,7 +21322,7 @@
         <v>45733</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21395,7 +21395,7 @@
         <v>46000</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21473,7 +21473,7 @@
         <v>44826</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21546,7 +21546,7 @@
         <v>45062</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21619,7 +21619,7 @@
         <v>44496</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21692,7 +21692,7 @@
         <v>45537</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21765,7 +21765,7 @@
         <v>46005</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21838,7 +21838,7 @@
         <v>44568</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21911,7 +21911,7 @@
         <v>45531</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21984,7 +21984,7 @@
         <v>46000</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22062,7 +22062,7 @@
         <v>45328</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22135,7 +22135,7 @@
         <v>45748</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22208,7 +22208,7 @@
         <v>45716</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22286,7 +22286,7 @@
         <v>45812</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22359,7 +22359,7 @@
         <v>45176</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22432,7 +22432,7 @@
         <v>44784</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22510,7 +22510,7 @@
         <v>45348</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22583,7 +22583,7 @@
         <v>45930</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22656,7 +22656,7 @@
         <v>45244</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22729,7 +22729,7 @@
         <v>45630</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22802,7 +22802,7 @@
         <v>45735</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22875,7 +22875,7 @@
         <v>45735</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22948,7 +22948,7 @@
         <v>45273</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23021,7 +23021,7 @@
         <v>45273</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23094,7 +23094,7 @@
         <v>44865</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23167,7 +23167,7 @@
         <v>45335</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23240,7 +23240,7 @@
         <v>45441</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23313,7 +23313,7 @@
         <v>45334</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23386,7 +23386,7 @@
         <v>45078</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23459,7 +23459,7 @@
         <v>45113</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23532,7 +23532,7 @@
         <v>46140</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23610,7 +23610,7 @@
         <v>45180</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23683,7 +23683,7 @@
         <v>45583</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23756,7 +23756,7 @@
         <v>44529</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23829,7 +23829,7 @@
         <v>45090</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23902,7 +23902,7 @@
         <v>45133</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23975,7 +23975,7 @@
         <v>46147</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24048,7 +24048,7 @@
         <v>44882</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24121,7 +24121,7 @@
         <v>45467</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24194,7 +24194,7 @@
         <v>44897</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24267,7 +24267,7 @@
         <v>46141</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24340,7 +24340,7 @@
         <v>45834</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24413,7 +24413,7 @@
         <v>44858</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24486,7 +24486,7 @@
         <v>45835</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24559,7 +24559,7 @@
         <v>46155</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24632,7 +24632,7 @@
         <v>46155</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24705,7 +24705,7 @@
         <v>45374</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24778,7 +24778,7 @@
         <v>44641</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24851,7 +24851,7 @@
         <v>45433</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24924,7 +24924,7 @@
         <v>46076</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24997,7 +24997,7 @@
         <v>44897</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25070,7 +25070,7 @@
         <v>45737</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25143,7 +25143,7 @@
         <v>44942</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25216,7 +25216,7 @@
         <v>45839</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25289,7 +25289,7 @@
         <v>45103</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25362,7 +25362,7 @@
         <v>45251</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25435,7 +25435,7 @@
         <v>45251</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25508,7 +25508,7 @@
         <v>45049</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25581,7 +25581,7 @@
         <v>45842</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25654,7 +25654,7 @@
         <v>44508</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25727,7 +25727,7 @@
         <v>45566</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25800,7 +25800,7 @@
         <v>45842</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25873,7 +25873,7 @@
         <v>45818</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25946,7 +25946,7 @@
         <v>45842</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26019,7 +26019,7 @@
         <v>45841</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26092,7 +26092,7 @@
         <v>45529</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26165,7 +26165,7 @@
         <v>45846</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26238,7 +26238,7 @@
         <v>45845</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26311,7 +26311,7 @@
         <v>45001</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26384,7 +26384,7 @@
         <v>46163</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26457,7 +26457,7 @@
         <v>45352</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26535,7 +26535,7 @@
         <v>45728</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26608,7 +26608,7 @@
         <v>44935</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26681,7 +26681,7 @@
         <v>45726</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26754,7 +26754,7 @@
         <v>45726</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26827,7 +26827,7 @@
         <v>44992</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26900,7 +26900,7 @@
         <v>45854</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -26973,7 +26973,7 @@
         <v>45763</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27046,7 +27046,7 @@
         <v>45763</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27119,7 +27119,7 @@
         <v>45581</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27192,7 +27192,7 @@
         <v>45819</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27265,7 +27265,7 @@
         <v>44979</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27338,7 +27338,7 @@
         <v>45352</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27416,7 +27416,7 @@
         <v>45812</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27489,7 +27489,7 @@
         <v>45946</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27562,7 +27562,7 @@
         <v>45631</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27635,7 +27635,7 @@
         <v>45911</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27708,7 +27708,7 @@
         <v>45092</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27781,7 +27781,7 @@
         <v>45006</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27859,7 +27859,7 @@
         <v>45092</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -27932,7 +27932,7 @@
         <v>45166</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28005,7 +28005,7 @@
         <v>45376</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28078,7 +28078,7 @@
         <v>44942</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28151,7 +28151,7 @@
         <v>45015</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28224,7 +28224,7 @@
         <v>44543</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28297,7 +28297,7 @@
         <v>45726</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28370,7 +28370,7 @@
         <v>45155</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28443,7 +28443,7 @@
         <v>45450</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28516,7 +28516,7 @@
         <v>44523</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28589,7 +28589,7 @@
         <v>44476</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28662,7 +28662,7 @@
         <v>45586</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28735,7 +28735,7 @@
         <v>45867</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -28808,7 +28808,7 @@
         <v>44473</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -28881,7 +28881,7 @@
         <v>45581</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -28954,7 +28954,7 @@
         <v>45615</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29027,7 +29027,7 @@
         <v>44958</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29100,7 +29100,7 @@
         <v>45098</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29193,7 +29193,7 @@
         <v>45608</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29266,7 +29266,7 @@
         <v>45156</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29339,7 +29339,7 @@
         <v>45558</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29412,7 +29412,7 @@
         <v>46184</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29485,7 +29485,7 @@
         <v>45539</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29558,7 +29558,7 @@
         <v>46184</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29631,7 +29631,7 @@
         <v>45133</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -29704,7 +29704,7 @@
         <v>45355</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -29777,7 +29777,7 @@
         <v>45355</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -29855,7 +29855,7 @@
         <v>44979</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -29928,7 +29928,7 @@
         <v>45189</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30001,7 +30001,7 @@
         <v>45010</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30074,7 +30074,7 @@
         <v>45539</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30147,7 +30147,7 @@
         <v>45355</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30225,7 +30225,7 @@
         <v>45792</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30298,7 +30298,7 @@
         <v>46190</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30376,7 +30376,7 @@
         <v>45720</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30449,7 +30449,7 @@
         <v>45462</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30522,7 +30522,7 @@
         <v>46198</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30595,7 +30595,7 @@
         <v>45476</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30668,7 +30668,7 @@
         <v>46198</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -30741,7 +30741,7 @@
         <v>46198</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -30814,7 +30814,7 @@
         <v>46198</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -30887,7 +30887,7 @@
         <v>45049</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -30960,7 +30960,7 @@
         <v>45706</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31033,7 +31033,7 @@
         <v>46202</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31106,7 +31106,7 @@
         <v>45282</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31179,7 +31179,7 @@
         <v>44686</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31252,7 +31252,7 @@
         <v>45350</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31325,7 +31325,7 @@
         <v>45616</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31398,7 +31398,7 @@
         <v>46204</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31471,7 +31471,7 @@
         <v>46204</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31544,7 +31544,7 @@
         <v>46204</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31617,7 +31617,7 @@
         <v>45286</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -31690,7 +31690,7 @@
         <v>44636</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -31763,7 +31763,7 @@
         <v>46206</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -31836,7 +31836,7 @@
         <v>46204</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -31909,7 +31909,7 @@
         <v>46204</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -31982,7 +31982,7 @@
         <v>46204</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32055,7 +32055,7 @@
         <v>46204</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32128,7 +32128,7 @@
         <v>46206</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32201,7 +32201,7 @@
         <v>46251</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32274,7 +32274,7 @@
         <v>45191</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32347,7 +32347,7 @@
         <v>45716</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32425,7 +32425,7 @@
         <v>44531</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32498,7 +32498,7 @@
         <v>46251</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32576,7 +32576,7 @@
         <v>44587</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -32649,7 +32649,7 @@
         <v>45062</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -32722,7 +32722,7 @@
         <v>46251</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -32795,7 +32795,7 @@
         <v>45677</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -32868,7 +32868,7 @@
         <v>45222</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -32941,7 +32941,7 @@
         <v>44592</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33014,7 +33014,7 @@
         <v>45215</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33087,7 +33087,7 @@
         <v>45653</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33160,7 +33160,7 @@
         <v>44859</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33233,7 +33233,7 @@
         <v>44634</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33306,7 +33306,7 @@
         <v>44861</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33379,7 +33379,7 @@
         <v>45625</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33452,7 +33452,7 @@
         <v>45716</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33525,7 +33525,7 @@
         <v>44698</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33598,7 +33598,7 @@
         <v>46254</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -33671,7 +33671,7 @@
         <v>45771</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -33744,7 +33744,7 @@
         <v>46257</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -33817,7 +33817,7 @@
         <v>46254</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -33890,7 +33890,7 @@
         <v>45240</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -33968,7 +33968,7 @@
         <v>45166</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34041,7 +34041,7 @@
         <v>46258</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34114,7 +34114,7 @@
         <v>46258</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34187,7 +34187,7 @@
         <v>46216</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34265,7 +34265,7 @@
         <v>45460</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34338,7 +34338,7 @@
         <v>45693</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34411,7 +34411,7 @@
         <v>45698</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34484,7 +34484,7 @@
         <v>46216</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34562,7 +34562,7 @@
         <v>46216</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -34640,7 +34640,7 @@
         <v>45202</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -34713,7 +34713,7 @@
         <v>46216</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -34791,7 +34791,7 @@
         <v>46216</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -34869,7 +34869,7 @@
         <v>46216</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -34947,7 +34947,7 @@
         <v>45180</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35020,7 +35020,7 @@
         <v>45211</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35093,7 +35093,7 @@
         <v>45214</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35166,7 +35166,7 @@
         <v>45175</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35239,7 +35239,7 @@
         <v>45175</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35312,7 +35312,7 @@
         <v>45187</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35385,7 +35385,7 @@
         <v>46261</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35458,7 +35458,7 @@
         <v>45681</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35531,7 +35531,7 @@
         <v>45233</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -35604,7 +35604,7 @@
         <v>45233</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -35677,7 +35677,7 @@
         <v>45612</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -35750,7 +35750,7 @@
         <v>45770</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -35823,7 +35823,7 @@
         <v>45246</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -35896,7 +35896,7 @@
         <v>45679</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -35969,7 +35969,7 @@
         <v>45531</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36042,7 +36042,7 @@
         <v>46268</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36115,7 +36115,7 @@
         <v>46267</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36188,7 +36188,7 @@
         <v>45352</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36266,7 +36266,7 @@
         <v>46227</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36339,7 +36339,7 @@
         <v>46226</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36412,7 +36412,7 @@
         <v>46227</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36485,7 +36485,7 @@
         <v>46226</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36558,7 +36558,7 @@
         <v>46226</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -36631,7 +36631,7 @@
         <v>45250</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -36704,7 +36704,7 @@
         <v>45250</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -36777,7 +36777,7 @@
         <v>45253</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -36850,7 +36850,7 @@
         <v>45421</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -36923,7 +36923,7 @@
         <v>45211</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -36996,7 +36996,7 @@
         <v>45084</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37069,7 +37069,7 @@
         <v>44496</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37142,7 +37142,7 @@
         <v>46280</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37215,7 +37215,7 @@
         <v>45051</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37288,7 +37288,7 @@
         <v>46279</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37361,7 +37361,7 @@
         <v>45268</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37434,7 +37434,7 @@
         <v>46234</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -37512,7 +37512,7 @@
         <v>45469</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -37585,7 +37585,7 @@
         <v>46262</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -37658,7 +37658,7 @@
         <v>45175</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -37731,7 +37731,7 @@
         <v>44876</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -37804,7 +37804,7 @@
         <v>46240</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -37882,7 +37882,7 @@
         <v>45440</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -37955,7 +37955,7 @@
         <v>46240</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38033,7 +38033,7 @@
         <v>46240</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38111,7 +38111,7 @@
         <v>44921</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38184,7 +38184,7 @@
         <v>45734</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38257,7 +38257,7 @@
         <v>45608</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38330,7 +38330,7 @@
         <v>45546</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38403,7 +38403,7 @@
         <v>44621</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38476,7 +38476,7 @@
         <v>46287</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -38549,7 +38549,7 @@
         <v>44858</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -38622,7 +38622,7 @@
         <v>45187</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -38695,7 +38695,7 @@
         <v>45412</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -38768,7 +38768,7 @@
         <v>45414</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -38841,7 +38841,7 @@
         <v>44992</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -38914,7 +38914,7 @@
         <v>46092</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -38987,7 +38987,7 @@
         <v>44610</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39060,7 +39060,7 @@
         <v>46287</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39133,7 +39133,7 @@
         <v>45911</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39206,7 +39206,7 @@
         <v>44992</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39279,7 +39279,7 @@
         <v>46066</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39352,7 +39352,7 @@
         <v>46245</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39425,7 +39425,7 @@
         <v>46283</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39498,7 +39498,7 @@
         <v>46287</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -39571,7 +39571,7 @@
         <v>45575</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -39644,7 +39644,7 @@
         <v>46245</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -39717,7 +39717,7 @@
         <v>46247</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -39790,7 +39790,7 @@
         <v>46248</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -39863,7 +39863,7 @@
         <v>46168</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -39936,7 +39936,7 @@
         <v>44942</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40009,7 +40009,7 @@
         <v>46247</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40082,7 +40082,7 @@
         <v>45085</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40155,7 +40155,7 @@
         <v>46154</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40228,7 +40228,7 @@
         <v>44942</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40301,7 +40301,7 @@
         <v>44860</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40374,7 +40374,7 @@
         <v>46246</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40447,7 +40447,7 @@
         <v>45187</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -40520,7 +40520,7 @@
         <v>46287</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -40593,7 +40593,7 @@
         <v>46287</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -40666,7 +40666,7 @@
         <v>46290</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -40739,7 +40739,7 @@
         <v>45290</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -40812,7 +40812,7 @@
         <v>45609</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -40885,7 +40885,7 @@
         <v>45217</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -40958,7 +40958,7 @@
         <v>45244</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41031,7 +41031,7 @@
         <v>45111</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41104,7 +41104,7 @@
         <v>44526</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41177,7 +41177,7 @@
         <v>45141</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41250,7 +41250,7 @@
         <v>45359</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41323,7 +41323,7 @@
         <v>46030</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41396,7 +41396,7 @@
         <v>46248</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41469,7 +41469,7 @@
         <v>46290</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -41542,7 +41542,7 @@
         <v>46287</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -41615,7 +41615,7 @@
         <v>45916</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -41688,7 +41688,7 @@
         <v>45012</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -41761,7 +41761,7 @@
         <v>44687</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -41834,7 +41834,7 @@
         <v>45081</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -41907,7 +41907,7 @@
         <v>45068</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -41980,7 +41980,7 @@
         <v>45010</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42053,7 +42053,7 @@
         <v>45048</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42126,7 +42126,7 @@
         <v>45177</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42199,7 +42199,7 @@
         <v>45042</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42272,7 +42272,7 @@
         <v>45273</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42345,7 +42345,7 @@
         <v>45391</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42418,7 +42418,7 @@
         <v>45134</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -42491,7 +42491,7 @@
         <v>44743</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -42564,7 +42564,7 @@
         <v>45469</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -42642,7 +42642,7 @@
         <v>44977</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -42715,7 +42715,7 @@
         <v>45373</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -42793,7 +42793,7 @@
         <v>45373</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -42871,7 +42871,7 @@
         <v>45628</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -42944,7 +42944,7 @@
         <v>45311</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43017,7 +43017,7 @@
         <v>45061</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43090,7 +43090,7 @@
         <v>45638</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43163,7 +43163,7 @@
         <v>45638</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43236,7 +43236,7 @@
         <v>45090</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43309,7 +43309,7 @@
         <v>45612</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43382,7 +43382,7 @@
         <v>45051</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43455,7 +43455,7 @@
         <v>44942</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -43528,7 +43528,7 @@
         <v>45700</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -43601,7 +43601,7 @@
         <v>45653</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -43674,7 +43674,7 @@
         <v>45303</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -43747,7 +43747,7 @@
         <v>45211</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -43820,7 +43820,7 @@
         <v>45010</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -43893,7 +43893,7 @@
         <v>45707</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -43966,7 +43966,7 @@
         <v>45595</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44039,7 +44039,7 @@
         <v>45271</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44112,7 +44112,7 @@
         <v>45547</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44185,7 +44185,7 @@
         <v>45244</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44258,7 +44258,7 @@
         <v>45228</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44331,7 +44331,7 @@
         <v>45252</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44404,7 +44404,7 @@
         <v>44922</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44477,7 +44477,7 @@
         <v>45680</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -44550,7 +44550,7 @@
         <v>45215</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -44623,7 +44623,7 @@
         <v>45303</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -44696,7 +44696,7 @@
         <v>45211</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -44769,7 +44769,7 @@
         <v>45589</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -44842,7 +44842,7 @@
         <v>45103</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -44915,7 +44915,7 @@
         <v>44777</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -44988,7 +44988,7 @@
         <v>45653</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45061,7 +45061,7 @@
         <v>45706</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45134,7 +45134,7 @@
         <v>45443</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45207,7 +45207,7 @@
         <v>45734</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45280,7 +45280,7 @@
         <v>44921</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45353,7 +45353,7 @@
         <v>45378</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45426,7 +45426,7 @@
         <v>44817</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -45499,7 +45499,7 @@
         <v>45759</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -45572,7 +45572,7 @@
         <v>45314</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -45645,7 +45645,7 @@
         <v>45589</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -45718,7 +45718,7 @@
         <v>45567</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -45791,7 +45791,7 @@
         <v>45315</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -45864,7 +45864,7 @@
         <v>44928</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -45937,7 +45937,7 @@
         <v>45209</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46010,7 +46010,7 @@
         <v>45680</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46083,7 +46083,7 @@
         <v>45663</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46156,7 +46156,7 @@
         <v>45776</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46229,7 +46229,7 @@
         <v>45781</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46302,7 +46302,7 @@
         <v>45624</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46375,7 +46375,7 @@
         <v>45638</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -46448,7 +46448,7 @@
         <v>45407</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -46521,7 +46521,7 @@
         <v>45527</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -46594,7 +46594,7 @@
         <v>45719</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -46667,7 +46667,7 @@
         <v>44634</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -46740,7 +46740,7 @@
         <v>44658</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -46813,7 +46813,7 @@
         <v>44621</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -46886,7 +46886,7 @@
         <v>44607</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -46959,7 +46959,7 @@
         <v>44733</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47037,7 +47037,7 @@
         <v>44474</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47110,7 +47110,7 @@
         <v>45302</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47183,7 +47183,7 @@
         <v>45476</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47256,7 +47256,7 @@
         <v>45649</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -47329,7 +47329,7 @@
         <v>45728</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -47402,7 +47402,7 @@
         <v>45953</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -47475,7 +47475,7 @@
         <v>45967</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -47548,7 +47548,7 @@
         <v>46010</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -47621,7 +47621,7 @@
         <v>46010</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -47694,7 +47694,7 @@
         <v>46029</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -47772,7 +47772,7 @@
         <v>46079</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -47845,7 +47845,7 @@
         <v>46094</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -47918,7 +47918,7 @@
         <v>46119</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -47991,7 +47991,7 @@
         <v>46182</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>

--- a/Översikt ÄLMHULT.xlsx
+++ b/Översikt ÄLMHULT.xlsx
@@ -601,7 +601,7 @@
         <v>46209</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>45786</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
         <v>46041</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
         <v>45945</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>44883</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>45215</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>45645</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>46211</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>44883</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         <v>45183</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>44889</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>45818</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1919,7 +1919,7 @@
         <v>44830</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         <v>46171</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>45012</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>45050</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>45908</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2454,7 +2454,7 @@
         <v>45386</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2559,7 +2559,7 @@
         <v>45888</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
         <v>45560</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2773,7 +2773,7 @@
         <v>45932</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
         <v>46129</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         <v>45769</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3092,7 +3092,7 @@
         <v>45763</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
         <v>45856</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3306,7 +3306,7 @@
         <v>45631</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3411,7 +3411,7 @@
         <v>45218</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3516,7 +3516,7 @@
         <v>46204</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3621,7 +3621,7 @@
         <v>44882</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3726,7 +3726,7 @@
         <v>45719</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3831,7 +3831,7 @@
         <v>45280</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3936,7 +3936,7 @@
         <v>44869</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4041,7 +4041,7 @@
         <v>45786</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4146,7 +4146,7 @@
         <v>46043</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4251,7 +4251,7 @@
         <v>44609</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4324,7 +4324,7 @@
         <v>44525</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4397,7 +4397,7 @@
         <v>44785</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4470,7 +4470,7 @@
         <v>44785</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4543,7 +4543,7 @@
         <v>44785</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4616,7 +4616,7 @@
         <v>44477</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4689,7 +4689,7 @@
         <v>44473</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4762,7 +4762,7 @@
         <v>44515</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4835,7 +4835,7 @@
         <v>44802</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4908,7 +4908,7 @@
         <v>44785</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4981,7 +4981,7 @@
         <v>44802</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5054,7 +5054,7 @@
         <v>44749</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5127,7 +5127,7 @@
         <v>44474</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5200,7 +5200,7 @@
         <v>44798</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5273,7 +5273,7 @@
         <v>44523</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5346,7 +5346,7 @@
         <v>44503</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5419,7 +5419,7 @@
         <v>44503</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5492,7 +5492,7 @@
         <v>44785</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5565,7 +5565,7 @@
         <v>44665</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5643,7 +5643,7 @@
         <v>44846</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5716,7 +5716,7 @@
         <v>44847</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5789,7 +5789,7 @@
         <v>44498</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5862,7 +5862,7 @@
         <v>44690</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5935,7 +5935,7 @@
         <v>44812</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6008,7 +6008,7 @@
         <v>44504</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         <v>44602</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6154,7 +6154,7 @@
         <v>44621</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6227,7 +6227,7 @@
         <v>44512</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6300,7 +6300,7 @@
         <v>44609</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6373,7 +6373,7 @@
         <v>44487</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6446,7 +6446,7 @@
         <v>44721</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6519,7 +6519,7 @@
         <v>44587</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6597,7 +6597,7 @@
         <v>44802</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6670,7 +6670,7 @@
         <v>44509</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         <v>44739</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6816,7 +6816,7 @@
         <v>44551</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6889,7 +6889,7 @@
         <v>44733</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6962,7 +6962,7 @@
         <v>44621</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7035,7 +7035,7 @@
         <v>44854</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7108,7 +7108,7 @@
         <v>44854</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7181,7 +7181,7 @@
         <v>44680</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7254,7 +7254,7 @@
         <v>44524</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7327,7 +7327,7 @@
         <v>44690</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7400,7 +7400,7 @@
         <v>44690</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7473,7 +7473,7 @@
         <v>44477</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7546,7 +7546,7 @@
         <v>44865</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7619,7 +7619,7 @@
         <v>44496</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7692,7 +7692,7 @@
         <v>44721</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7765,7 +7765,7 @@
         <v>44525</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7838,7 +7838,7 @@
         <v>44685</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7911,7 +7911,7 @@
         <v>44474</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7984,7 +7984,7 @@
         <v>44643</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8057,7 +8057,7 @@
         <v>44596</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8130,7 +8130,7 @@
         <v>44510</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8203,7 +8203,7 @@
         <v>44522</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8276,7 +8276,7 @@
         <v>44636</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8349,7 +8349,7 @@
         <v>44657</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8422,7 +8422,7 @@
         <v>44831</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8495,7 +8495,7 @@
         <v>44831</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8568,7 +8568,7 @@
         <v>44491</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8641,7 +8641,7 @@
         <v>44816</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8714,7 +8714,7 @@
         <v>45716</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         <v>45222</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8860,7 +8860,7 @@
         <v>45222</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8933,7 +8933,7 @@
         <v>45497</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9006,7 +9006,7 @@
         <v>45268</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9079,7 +9079,7 @@
         <v>45211</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9152,7 +9152,7 @@
         <v>44855</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9225,7 +9225,7 @@
         <v>45348</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9298,7 +9298,7 @@
         <v>45215</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9371,7 +9371,7 @@
         <v>45401</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9444,7 +9444,7 @@
         <v>45440</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9517,7 +9517,7 @@
         <v>45254</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9590,7 +9590,7 @@
         <v>45217</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9663,7 +9663,7 @@
         <v>44853</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9736,7 +9736,7 @@
         <v>45539</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9809,7 +9809,7 @@
         <v>45384</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9882,7 +9882,7 @@
         <v>45317</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9955,7 +9955,7 @@
         <v>45457</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10028,7 +10028,7 @@
         <v>45529</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10101,7 +10101,7 @@
         <v>44986</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10179,7 +10179,7 @@
         <v>44865</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10252,7 +10252,7 @@
         <v>45089</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10325,7 +10325,7 @@
         <v>45251</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10398,7 +10398,7 @@
         <v>45309</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10471,7 +10471,7 @@
         <v>44897</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10544,7 +10544,7 @@
         <v>45078</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10617,7 +10617,7 @@
         <v>45078</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10690,7 +10690,7 @@
         <v>45533</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10763,7 +10763,7 @@
         <v>44962</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10836,7 +10836,7 @@
         <v>44973</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10909,7 +10909,7 @@
         <v>45457</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10982,7 +10982,7 @@
         <v>45457</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11055,7 +11055,7 @@
         <v>45140</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11128,7 +11128,7 @@
         <v>46016</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11201,7 +11201,7 @@
         <v>44998</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11279,7 +11279,7 @@
         <v>44582</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11352,7 +11352,7 @@
         <v>44942</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11425,7 +11425,7 @@
         <v>45113</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11498,7 +11498,7 @@
         <v>44545</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11571,7 +11571,7 @@
         <v>45169</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11644,7 +11644,7 @@
         <v>45884</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11717,7 +11717,7 @@
         <v>44943</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11790,7 +11790,7 @@
         <v>45888</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11863,7 +11863,7 @@
         <v>45887</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11936,7 +11936,7 @@
         <v>44930</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12009,7 +12009,7 @@
         <v>46035</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12082,7 +12082,7 @@
         <v>45181</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12155,7 +12155,7 @@
         <v>45637</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12228,7 +12228,7 @@
         <v>45373</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12306,7 +12306,7 @@
         <v>45589</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12379,7 +12379,7 @@
         <v>45373</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12457,7 +12457,7 @@
         <v>45435</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12530,7 +12530,7 @@
         <v>45435</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12603,7 +12603,7 @@
         <v>45435</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12676,7 +12676,7 @@
         <v>44853</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12749,7 +12749,7 @@
         <v>45799</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12822,7 +12822,7 @@
         <v>46038</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12895,7 +12895,7 @@
         <v>46037</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12968,7 +12968,7 @@
         <v>45460</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13041,7 +13041,7 @@
         <v>44994</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13114,7 +13114,7 @@
         <v>44994</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13187,7 +13187,7 @@
         <v>44531</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13260,7 +13260,7 @@
         <v>45373</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13338,7 +13338,7 @@
         <v>44911</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13411,7 +13411,7 @@
         <v>45405</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13484,7 +13484,7 @@
         <v>45702</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13557,7 +13557,7 @@
         <v>45538</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13630,7 +13630,7 @@
         <v>45898</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13703,7 +13703,7 @@
         <v>45897</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13776,7 +13776,7 @@
         <v>45663</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13849,7 +13849,7 @@
         <v>45175</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13922,7 +13922,7 @@
         <v>44503</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13995,7 +13995,7 @@
         <v>44859</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14068,7 +14068,7 @@
         <v>45748</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14141,7 +14141,7 @@
         <v>46045</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14214,7 +14214,7 @@
         <v>44914</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14287,7 +14287,7 @@
         <v>45574</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14360,7 +14360,7 @@
         <v>46052</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14433,7 +14433,7 @@
         <v>45559</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14506,7 +14506,7 @@
         <v>46052</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14579,7 +14579,7 @@
         <v>44511</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14652,7 +14652,7 @@
         <v>44511</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14725,7 +14725,7 @@
         <v>45916</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14798,7 +14798,7 @@
         <v>45681</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14871,7 +14871,7 @@
         <v>45915</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14949,7 +14949,7 @@
         <v>46061</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15022,7 +15022,7 @@
         <v>45917</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15100,7 +15100,7 @@
         <v>45917</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15178,7 +15178,7 @@
         <v>45917</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15256,7 +15256,7 @@
         <v>46063</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15329,7 +15329,7 @@
         <v>46065</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15402,7 +15402,7 @@
         <v>45804</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15475,7 +15475,7 @@
         <v>45687</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15548,7 +15548,7 @@
         <v>45543</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15621,7 +15621,7 @@
         <v>45513</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15694,7 +15694,7 @@
         <v>46076</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15767,7 +15767,7 @@
         <v>45827</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15840,7 +15840,7 @@
         <v>45929</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15913,7 +15913,7 @@
         <v>45554</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15986,7 +15986,7 @@
         <v>45930</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16059,7 +16059,7 @@
         <v>45564</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16132,7 +16132,7 @@
         <v>45254</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16205,7 +16205,7 @@
         <v>45930</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16278,7 +16278,7 @@
         <v>44994</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16351,7 +16351,7 @@
         <v>46093</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16424,7 +16424,7 @@
         <v>45944</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16497,7 +16497,7 @@
         <v>45446</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16570,7 +16570,7 @@
         <v>45945</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16643,7 +16643,7 @@
         <v>46105</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16721,7 +16721,7 @@
         <v>46105</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16799,7 +16799,7 @@
         <v>46105</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16877,7 +16877,7 @@
         <v>46105</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16955,7 +16955,7 @@
         <v>46105</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17033,7 +17033,7 @@
         <v>45947</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17106,7 +17106,7 @@
         <v>45170</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17179,7 +17179,7 @@
         <v>45916</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17257,7 +17257,7 @@
         <v>46105</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17335,7 +17335,7 @@
         <v>46105</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17413,7 +17413,7 @@
         <v>46107</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17486,7 +17486,7 @@
         <v>45952</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17559,7 +17559,7 @@
         <v>46106</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17637,7 +17637,7 @@
         <v>45594</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17710,7 +17710,7 @@
         <v>45588</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17783,7 +17783,7 @@
         <v>45462</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17856,7 +17856,7 @@
         <v>46108</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17929,7 +17929,7 @@
         <v>45258</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18002,7 +18002,7 @@
         <v>46108</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18075,7 +18075,7 @@
         <v>45959</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18148,7 +18148,7 @@
         <v>45578</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18221,7 +18221,7 @@
         <v>45308</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18294,7 +18294,7 @@
         <v>45372</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18367,7 +18367,7 @@
         <v>45629</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18440,7 +18440,7 @@
         <v>45966</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18513,7 +18513,7 @@
         <v>45966</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18586,7 +18586,7 @@
         <v>46125</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18659,7 +18659,7 @@
         <v>45966</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18732,7 +18732,7 @@
         <v>45967</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18805,7 +18805,7 @@
         <v>45969</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18878,7 +18878,7 @@
         <v>45969</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18951,7 +18951,7 @@
         <v>45145</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19024,7 +19024,7 @@
         <v>45548</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19097,7 +19097,7 @@
         <v>45818</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19170,7 +19170,7 @@
         <v>45695</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19243,7 +19243,7 @@
         <v>46128</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19316,7 +19316,7 @@
         <v>45612</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19389,7 +19389,7 @@
         <v>45680</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19462,7 +19462,7 @@
         <v>45469</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19540,7 +19540,7 @@
         <v>45078</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19613,7 +19613,7 @@
         <v>45715</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19686,7 +19686,7 @@
         <v>45631</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19759,7 +19759,7 @@
         <v>45167</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19832,7 +19832,7 @@
         <v>45051</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19905,7 +19905,7 @@
         <v>45986</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19983,7 +19983,7 @@
         <v>45154</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20056,7 +20056,7 @@
         <v>45938</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20129,7 +20129,7 @@
         <v>45722</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20202,7 +20202,7 @@
         <v>44760</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20275,7 +20275,7 @@
         <v>45992</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20353,7 +20353,7 @@
         <v>45610</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20426,7 +20426,7 @@
         <v>45992</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20504,7 +20504,7 @@
         <v>45992</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20582,7 +20582,7 @@
         <v>45835</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20655,7 +20655,7 @@
         <v>44526</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20728,7 +20728,7 @@
         <v>45992</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20806,7 +20806,7 @@
         <v>45531</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20884,7 +20884,7 @@
         <v>45076</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20957,7 +20957,7 @@
         <v>45076</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21030,7 +21030,7 @@
         <v>45911</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21103,7 +21103,7 @@
         <v>45887</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21176,7 +21176,7 @@
         <v>45883</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21249,7 +21249,7 @@
         <v>45817</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21322,7 +21322,7 @@
         <v>45733</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21395,7 +21395,7 @@
         <v>46000</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21473,7 +21473,7 @@
         <v>44826</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21546,7 +21546,7 @@
         <v>45062</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21619,7 +21619,7 @@
         <v>44496</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21692,7 +21692,7 @@
         <v>45537</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21765,7 +21765,7 @@
         <v>46005</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21838,7 +21838,7 @@
         <v>44568</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21911,7 +21911,7 @@
         <v>45531</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21984,7 +21984,7 @@
         <v>46000</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22062,7 +22062,7 @@
         <v>45328</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22135,7 +22135,7 @@
         <v>45748</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22208,7 +22208,7 @@
         <v>45716</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22286,7 +22286,7 @@
         <v>45812</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22359,7 +22359,7 @@
         <v>45176</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22432,7 +22432,7 @@
         <v>44784</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22510,7 +22510,7 @@
         <v>45348</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22583,7 +22583,7 @@
         <v>45930</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22656,7 +22656,7 @@
         <v>45244</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22729,7 +22729,7 @@
         <v>45630</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22802,7 +22802,7 @@
         <v>45735</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22875,7 +22875,7 @@
         <v>45735</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22948,7 +22948,7 @@
         <v>45273</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23021,7 +23021,7 @@
         <v>45273</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23094,7 +23094,7 @@
         <v>44865</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23167,7 +23167,7 @@
         <v>45335</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23240,7 +23240,7 @@
         <v>45441</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23313,7 +23313,7 @@
         <v>45334</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23386,7 +23386,7 @@
         <v>45078</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23459,7 +23459,7 @@
         <v>45113</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23532,7 +23532,7 @@
         <v>46140</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23610,7 +23610,7 @@
         <v>45180</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23683,7 +23683,7 @@
         <v>45583</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23756,7 +23756,7 @@
         <v>44529</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23829,7 +23829,7 @@
         <v>45090</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23902,7 +23902,7 @@
         <v>45133</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23975,7 +23975,7 @@
         <v>46147</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24048,7 +24048,7 @@
         <v>44882</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24121,7 +24121,7 @@
         <v>45467</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24194,7 +24194,7 @@
         <v>44897</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24267,7 +24267,7 @@
         <v>46141</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24340,7 +24340,7 @@
         <v>45834</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24413,7 +24413,7 @@
         <v>44858</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24486,7 +24486,7 @@
         <v>45835</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24559,7 +24559,7 @@
         <v>46155</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24632,7 +24632,7 @@
         <v>46155</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24705,7 +24705,7 @@
         <v>45374</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24778,7 +24778,7 @@
         <v>44641</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24851,7 +24851,7 @@
         <v>45433</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24924,7 +24924,7 @@
         <v>46076</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24997,7 +24997,7 @@
         <v>44897</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25070,7 +25070,7 @@
         <v>45737</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25143,7 +25143,7 @@
         <v>44942</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25216,7 +25216,7 @@
         <v>45839</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25289,7 +25289,7 @@
         <v>45103</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25362,7 +25362,7 @@
         <v>45251</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25435,7 +25435,7 @@
         <v>45251</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25508,7 +25508,7 @@
         <v>45049</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25581,7 +25581,7 @@
         <v>45842</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25654,7 +25654,7 @@
         <v>44508</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25727,7 +25727,7 @@
         <v>45566</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25800,7 +25800,7 @@
         <v>45842</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25873,7 +25873,7 @@
         <v>45818</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25946,7 +25946,7 @@
         <v>45842</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26019,7 +26019,7 @@
         <v>45841</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26092,7 +26092,7 @@
         <v>45529</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26165,7 +26165,7 @@
         <v>45846</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26238,7 +26238,7 @@
         <v>45845</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26311,7 +26311,7 @@
         <v>45001</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26384,7 +26384,7 @@
         <v>46163</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26457,7 +26457,7 @@
         <v>45352</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26535,7 +26535,7 @@
         <v>45728</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26608,7 +26608,7 @@
         <v>44935</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26681,7 +26681,7 @@
         <v>45726</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26754,7 +26754,7 @@
         <v>45726</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26827,7 +26827,7 @@
         <v>44992</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26900,7 +26900,7 @@
         <v>45854</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -26973,7 +26973,7 @@
         <v>45763</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27046,7 +27046,7 @@
         <v>45763</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27119,7 +27119,7 @@
         <v>45581</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27192,7 +27192,7 @@
         <v>45819</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27265,7 +27265,7 @@
         <v>44979</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27338,7 +27338,7 @@
         <v>45352</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27416,7 +27416,7 @@
         <v>45812</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27489,7 +27489,7 @@
         <v>45946</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27562,7 +27562,7 @@
         <v>45631</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27635,7 +27635,7 @@
         <v>45911</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27708,7 +27708,7 @@
         <v>45092</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27781,7 +27781,7 @@
         <v>45006</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27859,7 +27859,7 @@
         <v>45092</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -27932,7 +27932,7 @@
         <v>45166</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28005,7 +28005,7 @@
         <v>45376</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28078,7 +28078,7 @@
         <v>44942</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28151,7 +28151,7 @@
         <v>45015</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28224,7 +28224,7 @@
         <v>44543</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28297,7 +28297,7 @@
         <v>45726</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28370,7 +28370,7 @@
         <v>45155</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28443,7 +28443,7 @@
         <v>45450</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28516,7 +28516,7 @@
         <v>44523</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28589,7 +28589,7 @@
         <v>44476</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28662,7 +28662,7 @@
         <v>45586</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28735,7 +28735,7 @@
         <v>45867</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -28808,7 +28808,7 @@
         <v>44473</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -28881,7 +28881,7 @@
         <v>45581</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -28954,7 +28954,7 @@
         <v>45615</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29027,7 +29027,7 @@
         <v>44958</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29100,7 +29100,7 @@
         <v>45098</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29193,7 +29193,7 @@
         <v>45608</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29266,7 +29266,7 @@
         <v>45156</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29339,7 +29339,7 @@
         <v>45558</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29412,7 +29412,7 @@
         <v>46184</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29485,7 +29485,7 @@
         <v>45539</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29558,7 +29558,7 @@
         <v>46184</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29631,7 +29631,7 @@
         <v>45133</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -29704,7 +29704,7 @@
         <v>45355</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -29777,7 +29777,7 @@
         <v>45355</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -29855,7 +29855,7 @@
         <v>44979</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -29928,7 +29928,7 @@
         <v>45189</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30001,7 +30001,7 @@
         <v>45010</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30074,7 +30074,7 @@
         <v>45539</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30147,7 +30147,7 @@
         <v>45355</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30225,7 +30225,7 @@
         <v>45792</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30298,7 +30298,7 @@
         <v>46190</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30376,7 +30376,7 @@
         <v>45720</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30449,7 +30449,7 @@
         <v>45462</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30522,7 +30522,7 @@
         <v>46198</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30595,7 +30595,7 @@
         <v>45476</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30668,7 +30668,7 @@
         <v>46198</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -30741,7 +30741,7 @@
         <v>46198</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -30814,7 +30814,7 @@
         <v>46198</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -30887,7 +30887,7 @@
         <v>45049</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -30960,7 +30960,7 @@
         <v>45706</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31033,7 +31033,7 @@
         <v>46202</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31106,7 +31106,7 @@
         <v>45282</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31179,7 +31179,7 @@
         <v>44686</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31252,7 +31252,7 @@
         <v>45350</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31325,7 +31325,7 @@
         <v>45616</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31398,7 +31398,7 @@
         <v>46204</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31471,7 +31471,7 @@
         <v>46204</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31544,7 +31544,7 @@
         <v>46204</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31617,7 +31617,7 @@
         <v>45286</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -31690,7 +31690,7 @@
         <v>44636</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -31763,7 +31763,7 @@
         <v>46206</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -31836,7 +31836,7 @@
         <v>46204</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -31909,7 +31909,7 @@
         <v>46204</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -31982,7 +31982,7 @@
         <v>46204</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32055,7 +32055,7 @@
         <v>46204</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32128,7 +32128,7 @@
         <v>46206</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32201,7 +32201,7 @@
         <v>46251</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32274,7 +32274,7 @@
         <v>45191</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32347,7 +32347,7 @@
         <v>45716</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32425,7 +32425,7 @@
         <v>44531</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32498,7 +32498,7 @@
         <v>46251</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32576,7 +32576,7 @@
         <v>44587</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -32649,7 +32649,7 @@
         <v>45062</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -32722,7 +32722,7 @@
         <v>46251</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -32795,7 +32795,7 @@
         <v>45677</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -32868,7 +32868,7 @@
         <v>45222</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -32941,7 +32941,7 @@
         <v>44592</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33014,7 +33014,7 @@
         <v>45215</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33087,7 +33087,7 @@
         <v>45653</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33160,7 +33160,7 @@
         <v>44859</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33233,7 +33233,7 @@
         <v>44634</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33306,7 +33306,7 @@
         <v>44861</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33379,7 +33379,7 @@
         <v>45625</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33452,7 +33452,7 @@
         <v>45716</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33525,7 +33525,7 @@
         <v>44698</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33598,7 +33598,7 @@
         <v>46254</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -33671,7 +33671,7 @@
         <v>45771</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -33744,7 +33744,7 @@
         <v>46257</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -33817,7 +33817,7 @@
         <v>46254</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -33890,7 +33890,7 @@
         <v>45240</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -33968,7 +33968,7 @@
         <v>45166</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34041,7 +34041,7 @@
         <v>46258</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34114,7 +34114,7 @@
         <v>46258</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34187,7 +34187,7 @@
         <v>46216</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34265,7 +34265,7 @@
         <v>45460</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34338,7 +34338,7 @@
         <v>45693</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34411,7 +34411,7 @@
         <v>45698</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34484,7 +34484,7 @@
         <v>46216</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34562,7 +34562,7 @@
         <v>46216</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -34640,7 +34640,7 @@
         <v>45202</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -34713,7 +34713,7 @@
         <v>46216</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -34791,7 +34791,7 @@
         <v>46216</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -34869,7 +34869,7 @@
         <v>46216</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -34947,7 +34947,7 @@
         <v>45180</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35020,7 +35020,7 @@
         <v>45211</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35093,7 +35093,7 @@
         <v>45214</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35166,7 +35166,7 @@
         <v>45175</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35239,7 +35239,7 @@
         <v>45175</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35312,7 +35312,7 @@
         <v>45187</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35385,7 +35385,7 @@
         <v>46261</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35458,7 +35458,7 @@
         <v>45681</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35531,7 +35531,7 @@
         <v>45233</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -35604,7 +35604,7 @@
         <v>45233</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -35677,7 +35677,7 @@
         <v>45612</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -35750,7 +35750,7 @@
         <v>45770</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -35823,7 +35823,7 @@
         <v>45246</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -35896,7 +35896,7 @@
         <v>45679</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -35969,7 +35969,7 @@
         <v>45531</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36042,7 +36042,7 @@
         <v>46268</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36115,7 +36115,7 @@
         <v>46267</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36188,7 +36188,7 @@
         <v>45352</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36266,7 +36266,7 @@
         <v>46227</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36339,7 +36339,7 @@
         <v>46226</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36412,7 +36412,7 @@
         <v>46227</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36485,7 +36485,7 @@
         <v>46226</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36558,7 +36558,7 @@
         <v>46226</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -36631,7 +36631,7 @@
         <v>45250</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -36704,7 +36704,7 @@
         <v>45250</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -36777,7 +36777,7 @@
         <v>45253</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -36850,7 +36850,7 @@
         <v>45421</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -36923,7 +36923,7 @@
         <v>45211</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -36996,7 +36996,7 @@
         <v>45084</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37069,7 +37069,7 @@
         <v>44496</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37142,7 +37142,7 @@
         <v>46280</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37215,7 +37215,7 @@
         <v>45051</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37288,7 +37288,7 @@
         <v>46279</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37361,7 +37361,7 @@
         <v>45268</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37434,7 +37434,7 @@
         <v>46234</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -37512,7 +37512,7 @@
         <v>45469</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -37585,7 +37585,7 @@
         <v>46262</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -37658,7 +37658,7 @@
         <v>45175</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -37731,7 +37731,7 @@
         <v>44876</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -37804,7 +37804,7 @@
         <v>46240</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -37882,7 +37882,7 @@
         <v>45440</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -37955,7 +37955,7 @@
         <v>46240</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38033,7 +38033,7 @@
         <v>46240</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38111,7 +38111,7 @@
         <v>44921</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38184,7 +38184,7 @@
         <v>45734</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38257,7 +38257,7 @@
         <v>45608</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38330,7 +38330,7 @@
         <v>45546</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38403,7 +38403,7 @@
         <v>44621</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38476,7 +38476,7 @@
         <v>46287</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -38549,7 +38549,7 @@
         <v>44858</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -38622,7 +38622,7 @@
         <v>45187</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -38695,7 +38695,7 @@
         <v>45412</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -38768,7 +38768,7 @@
         <v>45414</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -38841,7 +38841,7 @@
         <v>44992</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -38914,7 +38914,7 @@
         <v>46092</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -38987,7 +38987,7 @@
         <v>44610</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39060,7 +39060,7 @@
         <v>46287</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39133,7 +39133,7 @@
         <v>45911</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39206,7 +39206,7 @@
         <v>44992</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39279,7 +39279,7 @@
         <v>46066</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39352,7 +39352,7 @@
         <v>46245</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39425,7 +39425,7 @@
         <v>46283</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39498,7 +39498,7 @@
         <v>46287</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -39571,7 +39571,7 @@
         <v>45575</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -39644,7 +39644,7 @@
         <v>46245</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -39717,7 +39717,7 @@
         <v>46247</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -39790,7 +39790,7 @@
         <v>46248</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -39863,7 +39863,7 @@
         <v>46168</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -39936,7 +39936,7 @@
         <v>44942</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40009,7 +40009,7 @@
         <v>46247</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40082,7 +40082,7 @@
         <v>45085</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40155,7 +40155,7 @@
         <v>46154</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40228,7 +40228,7 @@
         <v>44942</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40301,7 +40301,7 @@
         <v>44860</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40374,7 +40374,7 @@
         <v>46246</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40447,7 +40447,7 @@
         <v>45187</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -40520,7 +40520,7 @@
         <v>46287</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -40593,7 +40593,7 @@
         <v>46287</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -40666,7 +40666,7 @@
         <v>46290</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -40739,7 +40739,7 @@
         <v>45290</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -40812,7 +40812,7 @@
         <v>45609</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -40885,7 +40885,7 @@
         <v>45217</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -40958,7 +40958,7 @@
         <v>45244</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41031,7 +41031,7 @@
         <v>45111</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41104,7 +41104,7 @@
         <v>44526</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41177,7 +41177,7 @@
         <v>45141</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41250,7 +41250,7 @@
         <v>45359</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41323,7 +41323,7 @@
         <v>46030</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41396,7 +41396,7 @@
         <v>46248</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41469,7 +41469,7 @@
         <v>46290</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -41542,7 +41542,7 @@
         <v>46287</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -41615,7 +41615,7 @@
         <v>45916</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -41688,7 +41688,7 @@
         <v>45012</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -41761,7 +41761,7 @@
         <v>44687</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -41834,7 +41834,7 @@
         <v>45081</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -41907,7 +41907,7 @@
         <v>45068</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -41980,7 +41980,7 @@
         <v>45010</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42053,7 +42053,7 @@
         <v>45048</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42126,7 +42126,7 @@
         <v>45177</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42199,7 +42199,7 @@
         <v>45042</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42272,7 +42272,7 @@
         <v>45273</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42345,7 +42345,7 @@
         <v>45391</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42418,7 +42418,7 @@
         <v>45134</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -42491,7 +42491,7 @@
         <v>44743</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -42564,7 +42564,7 @@
         <v>45469</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -42642,7 +42642,7 @@
         <v>44977</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -42715,7 +42715,7 @@
         <v>45373</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -42793,7 +42793,7 @@
         <v>45373</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -42871,7 +42871,7 @@
         <v>45628</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -42944,7 +42944,7 @@
         <v>45311</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43017,7 +43017,7 @@
         <v>45061</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43090,7 +43090,7 @@
         <v>45638</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43163,7 +43163,7 @@
         <v>45638</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43236,7 +43236,7 @@
         <v>45090</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43309,7 +43309,7 @@
         <v>45612</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43382,7 +43382,7 @@
         <v>45051</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43455,7 +43455,7 @@
         <v>44942</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -43528,7 +43528,7 @@
         <v>45700</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -43601,7 +43601,7 @@
         <v>45653</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -43674,7 +43674,7 @@
         <v>45303</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -43747,7 +43747,7 @@
         <v>45211</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -43820,7 +43820,7 @@
         <v>45010</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -43893,7 +43893,7 @@
         <v>45707</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -43966,7 +43966,7 @@
         <v>45595</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44039,7 +44039,7 @@
         <v>45271</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44112,7 +44112,7 @@
         <v>45547</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44185,7 +44185,7 @@
         <v>45244</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44258,7 +44258,7 @@
         <v>45228</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44331,7 +44331,7 @@
         <v>45252</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44404,7 +44404,7 @@
         <v>44922</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44477,7 +44477,7 @@
         <v>45680</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -44550,7 +44550,7 @@
         <v>45215</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -44623,7 +44623,7 @@
         <v>45303</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -44696,7 +44696,7 @@
         <v>45211</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -44769,7 +44769,7 @@
         <v>45589</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -44842,7 +44842,7 @@
         <v>45103</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -44915,7 +44915,7 @@
         <v>44777</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -44988,7 +44988,7 @@
         <v>45653</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45061,7 +45061,7 @@
         <v>45706</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45134,7 +45134,7 @@
         <v>45443</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45207,7 +45207,7 @@
         <v>45734</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45280,7 +45280,7 @@
         <v>44921</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45353,7 +45353,7 @@
         <v>45378</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45426,7 +45426,7 @@
         <v>44817</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -45499,7 +45499,7 @@
         <v>45759</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -45572,7 +45572,7 @@
         <v>45314</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -45645,7 +45645,7 @@
         <v>45589</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -45718,7 +45718,7 @@
         <v>45567</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -45791,7 +45791,7 @@
         <v>45315</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -45864,7 +45864,7 @@
         <v>44928</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -45937,7 +45937,7 @@
         <v>45209</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46010,7 +46010,7 @@
         <v>45680</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46083,7 +46083,7 @@
         <v>45663</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46156,7 +46156,7 @@
         <v>45776</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46229,7 +46229,7 @@
         <v>45781</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46302,7 +46302,7 @@
         <v>45624</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46375,7 +46375,7 @@
         <v>45638</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -46448,7 +46448,7 @@
         <v>45407</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -46521,7 +46521,7 @@
         <v>45527</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -46594,7 +46594,7 @@
         <v>45719</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -46667,7 +46667,7 @@
         <v>44634</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -46740,7 +46740,7 @@
         <v>44658</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -46813,7 +46813,7 @@
         <v>44621</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -46886,7 +46886,7 @@
         <v>44607</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -46959,7 +46959,7 @@
         <v>44733</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47037,7 +47037,7 @@
         <v>44474</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47110,7 +47110,7 @@
         <v>45302</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47183,7 +47183,7 @@
         <v>45476</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47256,7 +47256,7 @@
         <v>45649</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -47329,7 +47329,7 @@
         <v>45728</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -47402,7 +47402,7 @@
         <v>45953</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -47475,7 +47475,7 @@
         <v>45967</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -47548,7 +47548,7 @@
         <v>46010</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -47621,7 +47621,7 @@
         <v>46010</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -47694,7 +47694,7 @@
         <v>46029</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -47772,7 +47772,7 @@
         <v>46079</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -47845,7 +47845,7 @@
         <v>46094</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -47918,7 +47918,7 @@
         <v>46119</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -47991,7 +47991,7 @@
         <v>46182</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>

--- a/Översikt ÄLMHULT.xlsx
+++ b/Översikt ÄLMHULT.xlsx
@@ -601,7 +601,7 @@
         <v>46209</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>45786</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
         <v>46041</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
         <v>45945</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>44883</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>45215</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>45645</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>46211</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>44889</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>45012</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         <v>45183</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>45818</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1919,7 +1919,7 @@
         <v>46171</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         <v>44830</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>44883</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>45050</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>45908</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2454,7 +2454,7 @@
         <v>45560</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2563,7 +2563,7 @@
         <v>45888</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         <v>45932</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2777,7 +2777,7 @@
         <v>46129</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
         <v>45769</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         <v>45763</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3092,7 +3092,7 @@
         <v>45631</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
         <v>45218</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3302,7 +3302,7 @@
         <v>45856</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3411,7 +3411,7 @@
         <v>46204</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3516,7 +3516,7 @@
         <v>45386</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3621,7 +3621,7 @@
         <v>45719</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3726,7 +3726,7 @@
         <v>44882</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3831,7 +3831,7 @@
         <v>45280</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3936,7 +3936,7 @@
         <v>46290</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4041,7 +4041,7 @@
         <v>44869</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4146,7 +4146,7 @@
         <v>45786</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4251,7 +4251,7 @@
         <v>46043</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4356,7 +4356,7 @@
         <v>44609</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4429,7 +4429,7 @@
         <v>44525</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4502,7 +4502,7 @@
         <v>44785</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4575,7 +4575,7 @@
         <v>44785</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4648,7 +4648,7 @@
         <v>44785</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4721,7 +4721,7 @@
         <v>44473</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4794,7 +4794,7 @@
         <v>44477</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
         <v>44515</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4940,7 +4940,7 @@
         <v>44802</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5013,7 +5013,7 @@
         <v>44802</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
         <v>44785</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5159,7 +5159,7 @@
         <v>44749</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5232,7 +5232,7 @@
         <v>44474</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5305,7 +5305,7 @@
         <v>44798</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5378,7 +5378,7 @@
         <v>44523</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5451,7 +5451,7 @@
         <v>44503</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5524,7 +5524,7 @@
         <v>44503</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5597,7 +5597,7 @@
         <v>44785</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5670,7 +5670,7 @@
         <v>44665</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5748,7 +5748,7 @@
         <v>44846</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5821,7 +5821,7 @@
         <v>44847</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5894,7 +5894,7 @@
         <v>44498</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5967,7 +5967,7 @@
         <v>44690</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6040,7 +6040,7 @@
         <v>44812</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6113,7 +6113,7 @@
         <v>44504</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6186,7 +6186,7 @@
         <v>44602</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6259,7 +6259,7 @@
         <v>44512</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6332,7 +6332,7 @@
         <v>44621</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6405,7 +6405,7 @@
         <v>44609</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6478,7 +6478,7 @@
         <v>44487</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6551,7 +6551,7 @@
         <v>44721</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6624,7 +6624,7 @@
         <v>44587</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6702,7 +6702,7 @@
         <v>44802</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6775,7 +6775,7 @@
         <v>44509</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6848,7 +6848,7 @@
         <v>44739</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6921,7 +6921,7 @@
         <v>44551</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6994,7 +6994,7 @@
         <v>44733</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7067,7 +7067,7 @@
         <v>44621</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7140,7 +7140,7 @@
         <v>44854</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7213,7 +7213,7 @@
         <v>44854</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7286,7 +7286,7 @@
         <v>44680</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7359,7 +7359,7 @@
         <v>44524</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7432,7 +7432,7 @@
         <v>44690</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7505,7 +7505,7 @@
         <v>44690</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7578,7 +7578,7 @@
         <v>44477</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7651,7 +7651,7 @@
         <v>44865</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7724,7 +7724,7 @@
         <v>44496</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         <v>44721</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7870,7 +7870,7 @@
         <v>44525</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7943,7 +7943,7 @@
         <v>44685</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8016,7 +8016,7 @@
         <v>44474</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8089,7 +8089,7 @@
         <v>44596</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8162,7 +8162,7 @@
         <v>44643</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8235,7 +8235,7 @@
         <v>44510</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8308,7 +8308,7 @@
         <v>44522</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8381,7 +8381,7 @@
         <v>44636</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8454,7 +8454,7 @@
         <v>44657</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8527,7 +8527,7 @@
         <v>44491</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8600,7 +8600,7 @@
         <v>44831</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8673,7 +8673,7 @@
         <v>44831</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8746,7 +8746,7 @@
         <v>45433</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8819,7 +8819,7 @@
         <v>45209</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8892,7 +8892,7 @@
         <v>45244</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8965,7 +8965,7 @@
         <v>45348</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9038,7 +9038,7 @@
         <v>45098</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9131,7 +9131,7 @@
         <v>45062</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9204,7 +9204,7 @@
         <v>45457</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9277,7 +9277,7 @@
         <v>45734</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9350,7 +9350,7 @@
         <v>45735</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9423,7 +9423,7 @@
         <v>45735</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9496,7 +9496,7 @@
         <v>44496</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9569,7 +9569,7 @@
         <v>45610</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9642,7 +9642,7 @@
         <v>44826</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9715,7 +9715,7 @@
         <v>45469</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9788,7 +9788,7 @@
         <v>44610</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9861,7 +9861,7 @@
         <v>44962</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9934,7 +9934,7 @@
         <v>45457</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10007,7 +10007,7 @@
         <v>45457</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10080,7 +10080,7 @@
         <v>45543</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10153,7 +10153,7 @@
         <v>45527</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10226,7 +10226,7 @@
         <v>45638</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10299,7 +10299,7 @@
         <v>45578</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10372,7 +10372,7 @@
         <v>45254</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10445,7 +10445,7 @@
         <v>45133</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10518,7 +10518,7 @@
         <v>45575</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10591,7 +10591,7 @@
         <v>45554</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10664,7 +10664,7 @@
         <v>45049</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10737,7 +10737,7 @@
         <v>44473</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10810,7 +10810,7 @@
         <v>45359</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10883,7 +10883,7 @@
         <v>45133</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10956,7 +10956,7 @@
         <v>45737</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11029,7 +11029,7 @@
         <v>46005</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11102,7 +11102,7 @@
         <v>45175</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11175,7 +11175,7 @@
         <v>44496</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11248,7 +11248,7 @@
         <v>45469</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11326,7 +11326,7 @@
         <v>45720</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11399,7 +11399,7 @@
         <v>45812</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11472,7 +11472,7 @@
         <v>44998</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11550,7 +11550,7 @@
         <v>45884</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11623,7 +11623,7 @@
         <v>46016</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11696,7 +11696,7 @@
         <v>45637</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11769,7 +11769,7 @@
         <v>45566</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11842,7 +11842,7 @@
         <v>45222</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11915,7 +11915,7 @@
         <v>45222</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11988,7 +11988,7 @@
         <v>45888</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12061,7 +12061,7 @@
         <v>45309</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12134,7 +12134,7 @@
         <v>44876</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12207,7 +12207,7 @@
         <v>45897</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12280,7 +12280,7 @@
         <v>45898</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12353,7 +12353,7 @@
         <v>44686</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12426,7 +12426,7 @@
         <v>44994</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12499,7 +12499,7 @@
         <v>46035</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12572,7 +12572,7 @@
         <v>45051</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12645,7 +12645,7 @@
         <v>45103</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12718,7 +12718,7 @@
         <v>45638</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12791,7 +12791,7 @@
         <v>45638</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12864,7 +12864,7 @@
         <v>45748</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12937,7 +12937,7 @@
         <v>45187</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13010,7 +13010,7 @@
         <v>46037</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13083,7 +13083,7 @@
         <v>46038</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13156,7 +13156,7 @@
         <v>45315</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13229,7 +13229,7 @@
         <v>46045</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13302,7 +13302,7 @@
         <v>45915</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13380,7 +13380,7 @@
         <v>44817</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13453,7 +13453,7 @@
         <v>45917</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13531,7 +13531,7 @@
         <v>45799</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13604,7 +13604,7 @@
         <v>45917</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13682,7 +13682,7 @@
         <v>45917</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13760,7 +13760,7 @@
         <v>45916</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13833,7 +13833,7 @@
         <v>45405</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13906,7 +13906,7 @@
         <v>44511</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13979,7 +13979,7 @@
         <v>44511</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14052,7 +14052,7 @@
         <v>45702</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14125,7 +14125,7 @@
         <v>45589</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14198,7 +14198,7 @@
         <v>45460</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14271,7 +14271,7 @@
         <v>45663</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14344,7 +14344,7 @@
         <v>45240</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14422,7 +14422,7 @@
         <v>45804</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14495,7 +14495,7 @@
         <v>45350</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14568,7 +14568,7 @@
         <v>46052</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14641,7 +14641,7 @@
         <v>45693</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14714,7 +14714,7 @@
         <v>44853</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14787,7 +14787,7 @@
         <v>45303</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14860,7 +14860,7 @@
         <v>46052</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14933,7 +14933,7 @@
         <v>45290</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15006,7 +15006,7 @@
         <v>45180</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15079,7 +15079,7 @@
         <v>45586</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15152,7 +15152,7 @@
         <v>45929</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15225,7 +15225,7 @@
         <v>45443</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15298,7 +15298,7 @@
         <v>44935</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15371,7 +15371,7 @@
         <v>44979</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15444,7 +15444,7 @@
         <v>44859</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15517,7 +15517,7 @@
         <v>46063</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15590,7 +15590,7 @@
         <v>45930</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15663,7 +15663,7 @@
         <v>45930</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15736,7 +15736,7 @@
         <v>46061</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15809,7 +15809,7 @@
         <v>46065</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15882,7 +15882,7 @@
         <v>45771</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15955,7 +15955,7 @@
         <v>45015</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16028,7 +16028,7 @@
         <v>45944</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16101,7 +16101,7 @@
         <v>45945</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16174,7 +16174,7 @@
         <v>44958</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16247,7 +16247,7 @@
         <v>46076</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16320,7 +16320,7 @@
         <v>45947</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16393,7 +16393,7 @@
         <v>44861</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16466,7 +16466,7 @@
         <v>45916</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16544,7 +16544,7 @@
         <v>45827</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16617,7 +16617,7 @@
         <v>45062</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16690,7 +16690,7 @@
         <v>45414</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16763,7 +16763,7 @@
         <v>45952</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16836,7 +16836,7 @@
         <v>45681</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16909,7 +16909,7 @@
         <v>45460</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16982,7 +16982,7 @@
         <v>45959</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17055,7 +17055,7 @@
         <v>45612</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17128,7 +17128,7 @@
         <v>45090</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17201,7 +17201,7 @@
         <v>44994</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17274,7 +17274,7 @@
         <v>44994</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17347,7 +17347,7 @@
         <v>45042</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17420,7 +17420,7 @@
         <v>45680</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17493,7 +17493,7 @@
         <v>44897</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17566,7 +17566,7 @@
         <v>45373</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17644,7 +17644,7 @@
         <v>46093</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17717,7 +17717,7 @@
         <v>45078</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17790,7 +17790,7 @@
         <v>45966</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17863,7 +17863,7 @@
         <v>45681</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17936,7 +17936,7 @@
         <v>45966</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18009,7 +18009,7 @@
         <v>45967</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18082,7 +18082,7 @@
         <v>45068</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18155,7 +18155,7 @@
         <v>45966</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18228,7 +18228,7 @@
         <v>45715</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18301,7 +18301,7 @@
         <v>44921</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18374,7 +18374,7 @@
         <v>45969</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18447,7 +18447,7 @@
         <v>45969</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18520,7 +18520,7 @@
         <v>45145</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18593,7 +18593,7 @@
         <v>45352</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18671,7 +18671,7 @@
         <v>45228</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18744,7 +18744,7 @@
         <v>45608</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18817,7 +18817,7 @@
         <v>45258</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18890,7 +18890,7 @@
         <v>44914</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18963,7 +18963,7 @@
         <v>45538</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19036,7 +19036,7 @@
         <v>46105</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19114,7 +19114,7 @@
         <v>46105</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19192,7 +19192,7 @@
         <v>46105</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19270,7 +19270,7 @@
         <v>46105</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19348,7 +19348,7 @@
         <v>46106</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19426,7 +19426,7 @@
         <v>45548</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19499,7 +19499,7 @@
         <v>45818</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19572,7 +19572,7 @@
         <v>44743</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19645,7 +19645,7 @@
         <v>44503</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19718,7 +19718,7 @@
         <v>45695</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19791,7 +19791,7 @@
         <v>46105</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19869,7 +19869,7 @@
         <v>46105</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19947,7 +19947,7 @@
         <v>46105</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20025,7 +20025,7 @@
         <v>46107</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20098,7 +20098,7 @@
         <v>46108</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20171,7 +20171,7 @@
         <v>46108</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20244,7 +20244,7 @@
         <v>45559</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20317,7 +20317,7 @@
         <v>45547</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20390,7 +20390,7 @@
         <v>45317</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20463,7 +20463,7 @@
         <v>45986</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20541,7 +20541,7 @@
         <v>45078</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20614,7 +20614,7 @@
         <v>45078</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20687,7 +20687,7 @@
         <v>45254</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20760,7 +20760,7 @@
         <v>45992</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20838,7 +20838,7 @@
         <v>45716</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20911,7 +20911,7 @@
         <v>45992</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20989,7 +20989,7 @@
         <v>46125</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21062,7 +21062,7 @@
         <v>45992</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21140,7 +21140,7 @@
         <v>45992</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21218,7 +21218,7 @@
         <v>45441</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21291,7 +21291,7 @@
         <v>45716</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21364,7 +21364,7 @@
         <v>45716</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21442,7 +21442,7 @@
         <v>45335</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21515,7 +21515,7 @@
         <v>45372</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21588,7 +21588,7 @@
         <v>45251</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21661,7 +21661,7 @@
         <v>45334</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21734,7 +21734,7 @@
         <v>46128</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21807,7 +21807,7 @@
         <v>46000</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21885,7 +21885,7 @@
         <v>45440</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21958,7 +21958,7 @@
         <v>44545</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22031,7 +22031,7 @@
         <v>45140</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22104,7 +22104,7 @@
         <v>45111</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22177,7 +22177,7 @@
         <v>45348</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22250,7 +22250,7 @@
         <v>45233</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22323,7 +22323,7 @@
         <v>45233</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22396,7 +22396,7 @@
         <v>45835</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22469,7 +22469,7 @@
         <v>45834</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22542,7 +22542,7 @@
         <v>44523</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22615,7 +22615,7 @@
         <v>45211</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22688,7 +22688,7 @@
         <v>45215</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22761,7 +22761,7 @@
         <v>45839</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22834,7 +22834,7 @@
         <v>45629</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22907,7 +22907,7 @@
         <v>45170</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22980,7 +22980,7 @@
         <v>44641</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23053,7 +23053,7 @@
         <v>45835</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23126,7 +23126,7 @@
         <v>46000</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23204,7 +23204,7 @@
         <v>45841</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23277,7 +23277,7 @@
         <v>45252</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23350,7 +23350,7 @@
         <v>45842</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23423,7 +23423,7 @@
         <v>45842</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23496,7 +23496,7 @@
         <v>45006</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23574,7 +23574,7 @@
         <v>45842</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23647,7 +23647,7 @@
         <v>45089</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23720,7 +23720,7 @@
         <v>45529</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23793,7 +23793,7 @@
         <v>45167</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23866,7 +23866,7 @@
         <v>45608</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23939,7 +23939,7 @@
         <v>45817</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24012,7 +24012,7 @@
         <v>45722</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24085,7 +24085,7 @@
         <v>45328</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24158,7 +24158,7 @@
         <v>45845</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24231,7 +24231,7 @@
         <v>45930</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24304,7 +24304,7 @@
         <v>45846</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24377,7 +24377,7 @@
         <v>45630</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24450,7 +24450,7 @@
         <v>45734</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24523,7 +24523,7 @@
         <v>45211</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24596,7 +24596,7 @@
         <v>45726</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24669,7 +24669,7 @@
         <v>45215</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24742,7 +24742,7 @@
         <v>45733</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24815,7 +24815,7 @@
         <v>45376</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24888,7 +24888,7 @@
         <v>45134</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24961,7 +24961,7 @@
         <v>45726</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25034,7 +25034,7 @@
         <v>45854</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25107,7 +25107,7 @@
         <v>45537</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25180,7 +25180,7 @@
         <v>45531</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25258,7 +25258,7 @@
         <v>45883</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25331,7 +25331,7 @@
         <v>45911</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25404,7 +25404,7 @@
         <v>44979</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25477,7 +25477,7 @@
         <v>45819</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25550,7 +25550,7 @@
         <v>44784</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25628,7 +25628,7 @@
         <v>45887</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25701,7 +25701,7 @@
         <v>45373</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25779,7 +25779,7 @@
         <v>45373</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25857,7 +25857,7 @@
         <v>45531</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25930,7 +25930,7 @@
         <v>45084</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26003,7 +26003,7 @@
         <v>45010</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26076,7 +26076,7 @@
         <v>45581</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26149,7 +26149,7 @@
         <v>45763</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26222,7 +26222,7 @@
         <v>45763</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26295,7 +26295,7 @@
         <v>45938</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26368,7 +26368,7 @@
         <v>45812</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26441,7 +26441,7 @@
         <v>45631</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26514,7 +26514,7 @@
         <v>45355</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26587,7 +26587,7 @@
         <v>45355</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26665,7 +26665,7 @@
         <v>45529</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26738,7 +26738,7 @@
         <v>46140</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26816,7 +26816,7 @@
         <v>45631</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26889,7 +26889,7 @@
         <v>44943</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26962,7 +26962,7 @@
         <v>45589</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27035,7 +27035,7 @@
         <v>45010</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27108,7 +27108,7 @@
         <v>45581</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27181,7 +27181,7 @@
         <v>45867</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27254,7 +27254,7 @@
         <v>45726</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27327,7 +27327,7 @@
         <v>45271</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27400,7 +27400,7 @@
         <v>46147</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27473,7 +27473,7 @@
         <v>45085</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27546,7 +27546,7 @@
         <v>44543</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27619,7 +27619,7 @@
         <v>44865</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27692,7 +27692,7 @@
         <v>46141</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27765,7 +27765,7 @@
         <v>45048</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27838,7 +27838,7 @@
         <v>45533</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27911,7 +27911,7 @@
         <v>46155</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -27984,7 +27984,7 @@
         <v>45001</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28057,7 +28057,7 @@
         <v>45282</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28130,7 +28130,7 @@
         <v>45273</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28203,7 +28203,7 @@
         <v>45273</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28276,7 +28276,7 @@
         <v>45706</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28349,7 +28349,7 @@
         <v>45612</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28422,7 +28422,7 @@
         <v>45615</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28495,7 +28495,7 @@
         <v>45818</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28568,7 +28568,7 @@
         <v>45250</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28641,7 +28641,7 @@
         <v>45250</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28714,7 +28714,7 @@
         <v>45251</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28787,7 +28787,7 @@
         <v>45546</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -28860,7 +28860,7 @@
         <v>45180</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -28933,7 +28933,7 @@
         <v>46076</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29006,7 +29006,7 @@
         <v>45539</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29079,7 +29079,7 @@
         <v>45311</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29152,7 +29152,7 @@
         <v>45308</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29225,7 +29225,7 @@
         <v>45384</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29298,7 +29298,7 @@
         <v>45374</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29371,7 +29371,7 @@
         <v>45706</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29444,7 +29444,7 @@
         <v>45211</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29517,7 +29517,7 @@
         <v>45728</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29590,7 +29590,7 @@
         <v>45012</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29663,7 +29663,7 @@
         <v>45314</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -29736,7 +29736,7 @@
         <v>45476</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -29809,7 +29809,7 @@
         <v>45707</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -29882,7 +29882,7 @@
         <v>45303</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -29955,7 +29955,7 @@
         <v>45653</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30028,7 +30028,7 @@
         <v>45653</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30101,7 +30101,7 @@
         <v>45187</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30174,7 +30174,7 @@
         <v>45716</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30252,7 +30252,7 @@
         <v>44973</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30325,7 +30325,7 @@
         <v>44942</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30398,7 +30398,7 @@
         <v>45946</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30471,7 +30471,7 @@
         <v>45700</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30544,7 +30544,7 @@
         <v>45061</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30617,7 +30617,7 @@
         <v>45911</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30690,7 +30690,7 @@
         <v>44897</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -30763,7 +30763,7 @@
         <v>45286</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -30836,7 +30836,7 @@
         <v>45181</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -30909,7 +30909,7 @@
         <v>45887</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -30982,7 +30982,7 @@
         <v>44977</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31055,7 +31055,7 @@
         <v>45628</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31128,7 +31128,7 @@
         <v>45352</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31206,7 +31206,7 @@
         <v>45513</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31279,7 +31279,7 @@
         <v>45166</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31352,7 +31352,7 @@
         <v>45680</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31425,7 +31425,7 @@
         <v>46184</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31498,7 +31498,7 @@
         <v>45191</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31571,7 +31571,7 @@
         <v>46184</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31644,7 +31644,7 @@
         <v>44853</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -31717,7 +31717,7 @@
         <v>45251</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -31790,7 +31790,7 @@
         <v>45589</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -31863,7 +31863,7 @@
         <v>44855</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -31936,7 +31936,7 @@
         <v>44942</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32009,7 +32009,7 @@
         <v>45680</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32082,7 +32082,7 @@
         <v>45462</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32155,7 +32155,7 @@
         <v>45412</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32228,7 +32228,7 @@
         <v>45792</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32301,7 +32301,7 @@
         <v>45113</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32374,7 +32374,7 @@
         <v>45421</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32447,7 +32447,7 @@
         <v>45558</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32520,7 +32520,7 @@
         <v>45090</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32593,7 +32593,7 @@
         <v>45567</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -32666,7 +32666,7 @@
         <v>46198</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -32739,7 +32739,7 @@
         <v>46198</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -32812,7 +32812,7 @@
         <v>45268</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -32885,7 +32885,7 @@
         <v>46198</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -32958,7 +32958,7 @@
         <v>46198</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33031,7 +33031,7 @@
         <v>46190</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33109,7 +33109,7 @@
         <v>44930</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33182,7 +33182,7 @@
         <v>44476</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33255,7 +33255,7 @@
         <v>46202</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33328,7 +33328,7 @@
         <v>45698</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33401,7 +33401,7 @@
         <v>45177</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33474,7 +33474,7 @@
         <v>46204</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33547,7 +33547,7 @@
         <v>44986</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33625,7 +33625,7 @@
         <v>46204</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -33698,7 +33698,7 @@
         <v>46204</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -33771,7 +33771,7 @@
         <v>46204</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -33844,7 +33844,7 @@
         <v>46204</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -33917,7 +33917,7 @@
         <v>46204</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -33990,7 +33990,7 @@
         <v>46204</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34063,7 +34063,7 @@
         <v>45175</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34136,7 +34136,7 @@
         <v>45677</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34209,7 +34209,7 @@
         <v>46206</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34282,7 +34282,7 @@
         <v>45462</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34355,7 +34355,7 @@
         <v>45081</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34428,7 +34428,7 @@
         <v>46206</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34501,7 +34501,7 @@
         <v>45166</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34574,7 +34574,7 @@
         <v>45595</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -34647,7 +34647,7 @@
         <v>44942</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -34720,7 +34720,7 @@
         <v>45391</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -34793,7 +34793,7 @@
         <v>45373</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -34871,7 +34871,7 @@
         <v>45373</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -34949,7 +34949,7 @@
         <v>45155</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35022,7 +35022,7 @@
         <v>46257</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35095,7 +35095,7 @@
         <v>46258</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35168,7 +35168,7 @@
         <v>46258</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35241,7 +35241,7 @@
         <v>46216</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35319,7 +35319,7 @@
         <v>46216</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35397,7 +35397,7 @@
         <v>46216</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35475,7 +35475,7 @@
         <v>46216</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35553,7 +35553,7 @@
         <v>46216</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -35631,7 +35631,7 @@
         <v>46216</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -35709,7 +35709,7 @@
         <v>45564</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -35782,7 +35782,7 @@
         <v>45010</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -35855,7 +35855,7 @@
         <v>46261</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -35928,7 +35928,7 @@
         <v>45113</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36001,7 +36001,7 @@
         <v>45214</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36074,7 +36074,7 @@
         <v>45217</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36147,7 +36147,7 @@
         <v>45156</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36220,7 +36220,7 @@
         <v>44942</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36293,7 +36293,7 @@
         <v>45539</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36366,7 +36366,7 @@
         <v>45355</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36444,7 +36444,7 @@
         <v>44882</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36517,7 +36517,7 @@
         <v>45175</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36590,7 +36590,7 @@
         <v>45175</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -36663,7 +36663,7 @@
         <v>45076</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -36736,7 +36736,7 @@
         <v>45076</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -36809,7 +36809,7 @@
         <v>46267</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -36882,7 +36882,7 @@
         <v>46268</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -36955,7 +36955,7 @@
         <v>46226</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37028,7 +37028,7 @@
         <v>46226</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37101,7 +37101,7 @@
         <v>46226</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37174,7 +37174,7 @@
         <v>45653</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37247,7 +37247,7 @@
         <v>44526</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37320,7 +37320,7 @@
         <v>45612</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37393,7 +37393,7 @@
         <v>46227</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37466,7 +37466,7 @@
         <v>45625</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -37539,7 +37539,7 @@
         <v>46227</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -37612,7 +37612,7 @@
         <v>44816</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -37685,7 +37685,7 @@
         <v>45222</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -37758,7 +37758,7 @@
         <v>46234</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -37836,7 +37836,7 @@
         <v>45211</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -37909,7 +37909,7 @@
         <v>46279</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -37982,7 +37982,7 @@
         <v>45435</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38055,7 +38055,7 @@
         <v>45435</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38128,7 +38128,7 @@
         <v>45435</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38201,7 +38201,7 @@
         <v>44911</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38274,7 +38274,7 @@
         <v>46280</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38347,7 +38347,7 @@
         <v>45748</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38420,7 +38420,7 @@
         <v>45378</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38493,7 +38493,7 @@
         <v>45141</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -38566,7 +38566,7 @@
         <v>44992</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -38639,7 +38639,7 @@
         <v>44992</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -38712,7 +38712,7 @@
         <v>45202</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -38785,7 +38785,7 @@
         <v>45588</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -38858,7 +38858,7 @@
         <v>46240</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -38936,7 +38936,7 @@
         <v>45246</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39009,7 +39009,7 @@
         <v>46240</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39087,7 +39087,7 @@
         <v>46240</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39165,7 +39165,7 @@
         <v>44865</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39238,7 +39238,7 @@
         <v>44698</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39311,7 +39311,7 @@
         <v>46066</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39384,7 +39384,7 @@
         <v>45189</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39457,7 +39457,7 @@
         <v>45911</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39530,7 +39530,7 @@
         <v>45352</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -39608,7 +39608,7 @@
         <v>44687</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -39681,7 +39681,7 @@
         <v>45467</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -39754,7 +39754,7 @@
         <v>45211</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -39827,7 +39827,7 @@
         <v>46092</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -39900,7 +39900,7 @@
         <v>45187</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -39973,7 +39973,7 @@
         <v>45450</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40046,7 +40046,7 @@
         <v>45253</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40119,7 +40119,7 @@
         <v>46245</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40192,7 +40192,7 @@
         <v>46287</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40265,7 +40265,7 @@
         <v>46246</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40338,7 +40338,7 @@
         <v>46287</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40411,7 +40411,7 @@
         <v>46287</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40484,7 +40484,7 @@
         <v>46287</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -40557,7 +40557,7 @@
         <v>45051</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -40630,7 +40630,7 @@
         <v>45215</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -40703,7 +40703,7 @@
         <v>46287</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -40776,7 +40776,7 @@
         <v>46283</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -40849,7 +40849,7 @@
         <v>46245</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -40922,7 +40922,7 @@
         <v>46287</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -40995,7 +40995,7 @@
         <v>45078</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41068,7 +41068,7 @@
         <v>46247</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41141,7 +41141,7 @@
         <v>46154</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41214,7 +41214,7 @@
         <v>45916</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41287,7 +41287,7 @@
         <v>46290</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41360,7 +41360,7 @@
         <v>45574</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41433,7 +41433,7 @@
         <v>46248</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41506,7 +41506,7 @@
         <v>46168</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -41579,7 +41579,7 @@
         <v>46251</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -41657,7 +41657,7 @@
         <v>46248</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -41730,7 +41730,7 @@
         <v>44992</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -41803,7 +41803,7 @@
         <v>46293</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -41881,7 +41881,7 @@
         <v>46247</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -41954,7 +41954,7 @@
         <v>46030</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42027,7 +42027,7 @@
         <v>46290</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42100,7 +42100,7 @@
         <v>45244</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42173,7 +42173,7 @@
         <v>45687</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42246,7 +42246,7 @@
         <v>44858</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42319,7 +42319,7 @@
         <v>46262</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42392,7 +42392,7 @@
         <v>45539</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42465,7 +42465,7 @@
         <v>45609</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -42538,7 +42538,7 @@
         <v>46294</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -42611,7 +42611,7 @@
         <v>44531</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -42684,7 +42684,7 @@
         <v>45049</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -42757,7 +42757,7 @@
         <v>46295</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -42830,7 +42830,7 @@
         <v>45679</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -42903,7 +42903,7 @@
         <v>46294</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -42976,7 +42976,7 @@
         <v>44859</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43049,7 +43049,7 @@
         <v>44531</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43122,7 +43122,7 @@
         <v>46295</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43195,7 +43195,7 @@
         <v>46294</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43268,7 +43268,7 @@
         <v>46251</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43341,7 +43341,7 @@
         <v>46251</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43414,7 +43414,7 @@
         <v>45446</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43487,7 +43487,7 @@
         <v>45616</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -43560,7 +43560,7 @@
         <v>46155</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -43633,7 +43633,7 @@
         <v>44587</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -43706,7 +43706,7 @@
         <v>45770</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -43779,7 +43779,7 @@
         <v>44582</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -43852,7 +43852,7 @@
         <v>45759</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -43925,7 +43925,7 @@
         <v>45531</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -43998,7 +43998,7 @@
         <v>46254</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44071,7 +44071,7 @@
         <v>46254</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44144,7 +44144,7 @@
         <v>44897</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44217,7 +44217,7 @@
         <v>45583</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44290,7 +44290,7 @@
         <v>45594</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44363,7 +44363,7 @@
         <v>45469</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44441,7 +44441,7 @@
         <v>45401</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44514,7 +44514,7 @@
         <v>45092</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -44587,7 +44587,7 @@
         <v>45092</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -44660,7 +44660,7 @@
         <v>45103</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -44733,7 +44733,7 @@
         <v>44760</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -44806,7 +44806,7 @@
         <v>44526</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -44879,7 +44879,7 @@
         <v>45268</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -44952,7 +44952,7 @@
         <v>45440</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45025,7 +45025,7 @@
         <v>45244</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45098,7 +45098,7 @@
         <v>45051</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45171,7 +45171,7 @@
         <v>45176</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45244,7 +45244,7 @@
         <v>44921</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45317,7 +45317,7 @@
         <v>44928</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45390,7 +45390,7 @@
         <v>44568</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45463,7 +45463,7 @@
         <v>44634</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -45536,7 +45536,7 @@
         <v>44592</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -45609,7 +45609,7 @@
         <v>44777</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -45682,7 +45682,7 @@
         <v>44942</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -45755,7 +45755,7 @@
         <v>44942</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -45828,7 +45828,7 @@
         <v>45273</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -45901,7 +45901,7 @@
         <v>45497</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -45974,7 +45974,7 @@
         <v>45217</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46047,7 +46047,7 @@
         <v>44621</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46120,7 +46120,7 @@
         <v>44922</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46193,7 +46193,7 @@
         <v>45169</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46266,7 +46266,7 @@
         <v>44860</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46339,7 +46339,7 @@
         <v>45154</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46412,7 +46412,7 @@
         <v>44636</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -46485,7 +46485,7 @@
         <v>44529</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -46558,7 +46558,7 @@
         <v>44508</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -46631,7 +46631,7 @@
         <v>44858</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -46704,7 +46704,7 @@
         <v>45776</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -46777,7 +46777,7 @@
         <v>45663</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -46850,7 +46850,7 @@
         <v>45624</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -46923,7 +46923,7 @@
         <v>45781</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -46996,7 +46996,7 @@
         <v>45407</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47069,7 +47069,7 @@
         <v>45719</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47142,7 +47142,7 @@
         <v>44634</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47215,7 +47215,7 @@
         <v>44658</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47288,7 +47288,7 @@
         <v>44621</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -47361,7 +47361,7 @@
         <v>44474</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -47434,7 +47434,7 @@
         <v>44607</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -47507,7 +47507,7 @@
         <v>44733</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -47585,7 +47585,7 @@
         <v>45302</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -47658,7 +47658,7 @@
         <v>45476</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -47731,7 +47731,7 @@
         <v>45649</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -47804,7 +47804,7 @@
         <v>45728</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -47877,7 +47877,7 @@
         <v>45953</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -47950,7 +47950,7 @@
         <v>45967</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48023,7 +48023,7 @@
         <v>46010</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48096,7 +48096,7 @@
         <v>46010</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48169,7 +48169,7 @@
         <v>46029</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -48247,7 +48247,7 @@
         <v>46079</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -48320,7 +48320,7 @@
         <v>46094</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -48393,7 +48393,7 @@
         <v>46119</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -48466,7 +48466,7 @@
         <v>46182</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>

--- a/Översikt ÄLMHULT.xlsx
+++ b/Översikt ÄLMHULT.xlsx
@@ -601,7 +601,7 @@
         <v>46209</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>45786</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
         <v>46041</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
         <v>45945</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>44883</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>45215</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>45645</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>46211</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>44889</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>45012</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         <v>45183</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>45818</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1919,7 +1919,7 @@
         <v>46171</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         <v>44830</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>44883</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>45050</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>45908</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2454,7 +2454,7 @@
         <v>45560</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2563,7 +2563,7 @@
         <v>45888</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         <v>45932</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2777,7 +2777,7 @@
         <v>46129</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
         <v>45769</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         <v>45763</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3092,7 +3092,7 @@
         <v>45631</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
         <v>45218</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3302,7 +3302,7 @@
         <v>45856</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3411,7 +3411,7 @@
         <v>46204</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3516,7 +3516,7 @@
         <v>45386</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3621,7 +3621,7 @@
         <v>45719</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3726,7 +3726,7 @@
         <v>44882</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3831,7 +3831,7 @@
         <v>45280</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3936,7 +3936,7 @@
         <v>46290</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4041,7 +4041,7 @@
         <v>44869</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4146,7 +4146,7 @@
         <v>45786</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4251,7 +4251,7 @@
         <v>46043</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4356,7 +4356,7 @@
         <v>44609</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4429,7 +4429,7 @@
         <v>44525</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4502,7 +4502,7 @@
         <v>44785</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4575,7 +4575,7 @@
         <v>44785</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4648,7 +4648,7 @@
         <v>44785</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4721,7 +4721,7 @@
         <v>44473</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4794,7 +4794,7 @@
         <v>44477</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
         <v>44515</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4940,7 +4940,7 @@
         <v>44802</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5013,7 +5013,7 @@
         <v>44802</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
         <v>44785</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5159,7 +5159,7 @@
         <v>44749</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5232,7 +5232,7 @@
         <v>44474</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5305,7 +5305,7 @@
         <v>44798</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5378,7 +5378,7 @@
         <v>44523</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5451,7 +5451,7 @@
         <v>44503</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5524,7 +5524,7 @@
         <v>44503</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5597,7 +5597,7 @@
         <v>44785</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5670,7 +5670,7 @@
         <v>44665</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5748,7 +5748,7 @@
         <v>44846</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5821,7 +5821,7 @@
         <v>44847</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5894,7 +5894,7 @@
         <v>44498</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5967,7 +5967,7 @@
         <v>44690</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6040,7 +6040,7 @@
         <v>44812</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6113,7 +6113,7 @@
         <v>44504</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6186,7 +6186,7 @@
         <v>44602</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6259,7 +6259,7 @@
         <v>44512</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6332,7 +6332,7 @@
         <v>44621</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6405,7 +6405,7 @@
         <v>44609</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6478,7 +6478,7 @@
         <v>44487</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6551,7 +6551,7 @@
         <v>44721</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6624,7 +6624,7 @@
         <v>44587</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6702,7 +6702,7 @@
         <v>44802</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6775,7 +6775,7 @@
         <v>44509</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6848,7 +6848,7 @@
         <v>44739</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6921,7 +6921,7 @@
         <v>44551</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6994,7 +6994,7 @@
         <v>44733</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7067,7 +7067,7 @@
         <v>44621</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7140,7 +7140,7 @@
         <v>44854</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7213,7 +7213,7 @@
         <v>44854</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7286,7 +7286,7 @@
         <v>44680</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7359,7 +7359,7 @@
         <v>44524</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7432,7 +7432,7 @@
         <v>44690</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7505,7 +7505,7 @@
         <v>44690</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7578,7 +7578,7 @@
         <v>44477</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7651,7 +7651,7 @@
         <v>44865</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7724,7 +7724,7 @@
         <v>44496</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         <v>44721</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7870,7 +7870,7 @@
         <v>44525</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7943,7 +7943,7 @@
         <v>44685</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8016,7 +8016,7 @@
         <v>44474</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8089,7 +8089,7 @@
         <v>44596</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8162,7 +8162,7 @@
         <v>44643</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8235,7 +8235,7 @@
         <v>44510</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8308,7 +8308,7 @@
         <v>44522</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8381,7 +8381,7 @@
         <v>44636</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8454,7 +8454,7 @@
         <v>44657</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8527,7 +8527,7 @@
         <v>44491</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8600,7 +8600,7 @@
         <v>44831</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8673,7 +8673,7 @@
         <v>44831</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8746,7 +8746,7 @@
         <v>45433</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8819,7 +8819,7 @@
         <v>45209</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8892,7 +8892,7 @@
         <v>45244</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8965,7 +8965,7 @@
         <v>45348</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9038,7 +9038,7 @@
         <v>45098</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9131,7 +9131,7 @@
         <v>45062</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9204,7 +9204,7 @@
         <v>45457</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9277,7 +9277,7 @@
         <v>45734</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9350,7 +9350,7 @@
         <v>45735</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9423,7 +9423,7 @@
         <v>45735</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9496,7 +9496,7 @@
         <v>44496</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9569,7 +9569,7 @@
         <v>45610</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9642,7 +9642,7 @@
         <v>44826</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9715,7 +9715,7 @@
         <v>45469</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9788,7 +9788,7 @@
         <v>44610</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9861,7 +9861,7 @@
         <v>44962</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9934,7 +9934,7 @@
         <v>45457</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10007,7 +10007,7 @@
         <v>45457</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10080,7 +10080,7 @@
         <v>45543</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10153,7 +10153,7 @@
         <v>45527</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10226,7 +10226,7 @@
         <v>45638</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10299,7 +10299,7 @@
         <v>45578</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10372,7 +10372,7 @@
         <v>45254</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10445,7 +10445,7 @@
         <v>45133</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10518,7 +10518,7 @@
         <v>45575</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10591,7 +10591,7 @@
         <v>45554</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10664,7 +10664,7 @@
         <v>45049</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10737,7 +10737,7 @@
         <v>44473</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10810,7 +10810,7 @@
         <v>45359</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10883,7 +10883,7 @@
         <v>45133</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10956,7 +10956,7 @@
         <v>45737</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11029,7 +11029,7 @@
         <v>46005</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11102,7 +11102,7 @@
         <v>45175</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11175,7 +11175,7 @@
         <v>44496</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11248,7 +11248,7 @@
         <v>45469</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11326,7 +11326,7 @@
         <v>45720</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11399,7 +11399,7 @@
         <v>45812</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11472,7 +11472,7 @@
         <v>44998</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11550,7 +11550,7 @@
         <v>45884</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11623,7 +11623,7 @@
         <v>46016</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11696,7 +11696,7 @@
         <v>45637</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11769,7 +11769,7 @@
         <v>45566</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11842,7 +11842,7 @@
         <v>45222</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11915,7 +11915,7 @@
         <v>45222</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11988,7 +11988,7 @@
         <v>45888</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12061,7 +12061,7 @@
         <v>45309</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12134,7 +12134,7 @@
         <v>44876</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12207,7 +12207,7 @@
         <v>45897</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12280,7 +12280,7 @@
         <v>45898</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12353,7 +12353,7 @@
         <v>44686</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12426,7 +12426,7 @@
         <v>44994</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12499,7 +12499,7 @@
         <v>46035</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12572,7 +12572,7 @@
         <v>45051</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12645,7 +12645,7 @@
         <v>45103</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12718,7 +12718,7 @@
         <v>45638</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12791,7 +12791,7 @@
         <v>45638</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12864,7 +12864,7 @@
         <v>45748</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12937,7 +12937,7 @@
         <v>45187</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13010,7 +13010,7 @@
         <v>46037</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13083,7 +13083,7 @@
         <v>46038</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13156,7 +13156,7 @@
         <v>45315</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13229,7 +13229,7 @@
         <v>46045</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13302,7 +13302,7 @@
         <v>45915</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13380,7 +13380,7 @@
         <v>44817</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13453,7 +13453,7 @@
         <v>45917</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13531,7 +13531,7 @@
         <v>45799</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13604,7 +13604,7 @@
         <v>45917</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13682,7 +13682,7 @@
         <v>45917</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13760,7 +13760,7 @@
         <v>45916</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13833,7 +13833,7 @@
         <v>45405</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13906,7 +13906,7 @@
         <v>44511</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13979,7 +13979,7 @@
         <v>44511</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14052,7 +14052,7 @@
         <v>45702</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14125,7 +14125,7 @@
         <v>45589</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14198,7 +14198,7 @@
         <v>45460</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14271,7 +14271,7 @@
         <v>45663</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14344,7 +14344,7 @@
         <v>45240</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14422,7 +14422,7 @@
         <v>45804</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14495,7 +14495,7 @@
         <v>45350</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14568,7 +14568,7 @@
         <v>46052</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14641,7 +14641,7 @@
         <v>45693</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14714,7 +14714,7 @@
         <v>44853</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14787,7 +14787,7 @@
         <v>45303</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14860,7 +14860,7 @@
         <v>46052</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14933,7 +14933,7 @@
         <v>45290</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15006,7 +15006,7 @@
         <v>45180</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15079,7 +15079,7 @@
         <v>45586</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15152,7 +15152,7 @@
         <v>45929</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15225,7 +15225,7 @@
         <v>45443</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15298,7 +15298,7 @@
         <v>44935</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15371,7 +15371,7 @@
         <v>44979</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15444,7 +15444,7 @@
         <v>44859</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15517,7 +15517,7 @@
         <v>46063</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15590,7 +15590,7 @@
         <v>45930</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15663,7 +15663,7 @@
         <v>45930</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15736,7 +15736,7 @@
         <v>46061</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15809,7 +15809,7 @@
         <v>46065</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15882,7 +15882,7 @@
         <v>45771</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15955,7 +15955,7 @@
         <v>45015</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16028,7 +16028,7 @@
         <v>45944</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16101,7 +16101,7 @@
         <v>45945</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16174,7 +16174,7 @@
         <v>44958</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16247,7 +16247,7 @@
         <v>46076</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16320,7 +16320,7 @@
         <v>45947</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16393,7 +16393,7 @@
         <v>44861</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16466,7 +16466,7 @@
         <v>45916</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16544,7 +16544,7 @@
         <v>45827</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16617,7 +16617,7 @@
         <v>45062</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16690,7 +16690,7 @@
         <v>45414</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16763,7 +16763,7 @@
         <v>45952</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16836,7 +16836,7 @@
         <v>45681</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16909,7 +16909,7 @@
         <v>45460</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16982,7 +16982,7 @@
         <v>45959</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17055,7 +17055,7 @@
         <v>45612</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17128,7 +17128,7 @@
         <v>45090</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17201,7 +17201,7 @@
         <v>44994</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17274,7 +17274,7 @@
         <v>44994</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17347,7 +17347,7 @@
         <v>45042</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17420,7 +17420,7 @@
         <v>45680</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17493,7 +17493,7 @@
         <v>44897</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17566,7 +17566,7 @@
         <v>45373</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17644,7 +17644,7 @@
         <v>46093</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17717,7 +17717,7 @@
         <v>45078</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17790,7 +17790,7 @@
         <v>45966</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17863,7 +17863,7 @@
         <v>45681</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17936,7 +17936,7 @@
         <v>45966</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18009,7 +18009,7 @@
         <v>45967</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18082,7 +18082,7 @@
         <v>45068</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18155,7 +18155,7 @@
         <v>45966</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18228,7 +18228,7 @@
         <v>45715</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18301,7 +18301,7 @@
         <v>44921</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18374,7 +18374,7 @@
         <v>45969</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18447,7 +18447,7 @@
         <v>45969</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18520,7 +18520,7 @@
         <v>45145</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18593,7 +18593,7 @@
         <v>45352</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18671,7 +18671,7 @@
         <v>45228</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18744,7 +18744,7 @@
         <v>45608</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18817,7 +18817,7 @@
         <v>45258</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18890,7 +18890,7 @@
         <v>44914</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18963,7 +18963,7 @@
         <v>45538</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19036,7 +19036,7 @@
         <v>46105</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19114,7 +19114,7 @@
         <v>46105</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19192,7 +19192,7 @@
         <v>46105</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19270,7 +19270,7 @@
         <v>46105</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19348,7 +19348,7 @@
         <v>46106</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19426,7 +19426,7 @@
         <v>45548</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19499,7 +19499,7 @@
         <v>45818</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19572,7 +19572,7 @@
         <v>44743</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19645,7 +19645,7 @@
         <v>44503</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19718,7 +19718,7 @@
         <v>45695</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19791,7 +19791,7 @@
         <v>46105</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19869,7 +19869,7 @@
         <v>46105</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19947,7 +19947,7 @@
         <v>46105</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20025,7 +20025,7 @@
         <v>46107</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20098,7 +20098,7 @@
         <v>46108</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20171,7 +20171,7 @@
         <v>46108</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20244,7 +20244,7 @@
         <v>45559</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20317,7 +20317,7 @@
         <v>45547</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20390,7 +20390,7 @@
         <v>45317</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20463,7 +20463,7 @@
         <v>45986</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20541,7 +20541,7 @@
         <v>45078</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20614,7 +20614,7 @@
         <v>45078</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20687,7 +20687,7 @@
         <v>45254</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20760,7 +20760,7 @@
         <v>45992</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20838,7 +20838,7 @@
         <v>45716</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20911,7 +20911,7 @@
         <v>45992</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20989,7 +20989,7 @@
         <v>46125</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21062,7 +21062,7 @@
         <v>45992</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21140,7 +21140,7 @@
         <v>45992</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21218,7 +21218,7 @@
         <v>45441</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21291,7 +21291,7 @@
         <v>45716</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21364,7 +21364,7 @@
         <v>45716</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21442,7 +21442,7 @@
         <v>45335</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21515,7 +21515,7 @@
         <v>45372</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21588,7 +21588,7 @@
         <v>45251</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21661,7 +21661,7 @@
         <v>45334</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21734,7 +21734,7 @@
         <v>46128</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21807,7 +21807,7 @@
         <v>46000</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21885,7 +21885,7 @@
         <v>45440</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21958,7 +21958,7 @@
         <v>44545</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22031,7 +22031,7 @@
         <v>45140</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22104,7 +22104,7 @@
         <v>45111</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22177,7 +22177,7 @@
         <v>45348</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22250,7 +22250,7 @@
         <v>45233</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22323,7 +22323,7 @@
         <v>45233</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22396,7 +22396,7 @@
         <v>45835</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22469,7 +22469,7 @@
         <v>45834</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22542,7 +22542,7 @@
         <v>44523</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22615,7 +22615,7 @@
         <v>45211</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22688,7 +22688,7 @@
         <v>45215</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22761,7 +22761,7 @@
         <v>45839</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22834,7 +22834,7 @@
         <v>45629</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22907,7 +22907,7 @@
         <v>45170</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22980,7 +22980,7 @@
         <v>44641</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23053,7 +23053,7 @@
         <v>45835</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23126,7 +23126,7 @@
         <v>46000</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23204,7 +23204,7 @@
         <v>45841</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23277,7 +23277,7 @@
         <v>45252</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23350,7 +23350,7 @@
         <v>45842</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23423,7 +23423,7 @@
         <v>45842</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23496,7 +23496,7 @@
         <v>45006</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23574,7 +23574,7 @@
         <v>45842</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23647,7 +23647,7 @@
         <v>45089</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23720,7 +23720,7 @@
         <v>45529</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23793,7 +23793,7 @@
         <v>45167</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23866,7 +23866,7 @@
         <v>45608</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23939,7 +23939,7 @@
         <v>45817</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24012,7 +24012,7 @@
         <v>45722</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24085,7 +24085,7 @@
         <v>45328</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24158,7 +24158,7 @@
         <v>45845</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24231,7 +24231,7 @@
         <v>45930</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24304,7 +24304,7 @@
         <v>45846</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24377,7 +24377,7 @@
         <v>45630</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24450,7 +24450,7 @@
         <v>45734</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24523,7 +24523,7 @@
         <v>45211</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24596,7 +24596,7 @@
         <v>45726</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24669,7 +24669,7 @@
         <v>45215</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24742,7 +24742,7 @@
         <v>45733</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24815,7 +24815,7 @@
         <v>45376</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24888,7 +24888,7 @@
         <v>45134</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24961,7 +24961,7 @@
         <v>45726</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25034,7 +25034,7 @@
         <v>45854</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25107,7 +25107,7 @@
         <v>45537</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25180,7 +25180,7 @@
         <v>45531</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25258,7 +25258,7 @@
         <v>45883</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25331,7 +25331,7 @@
         <v>45911</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25404,7 +25404,7 @@
         <v>44979</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25477,7 +25477,7 @@
         <v>45819</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25550,7 +25550,7 @@
         <v>44784</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25628,7 +25628,7 @@
         <v>45887</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25701,7 +25701,7 @@
         <v>45373</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25779,7 +25779,7 @@
         <v>45373</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25857,7 +25857,7 @@
         <v>45531</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25930,7 +25930,7 @@
         <v>45084</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26003,7 +26003,7 @@
         <v>45010</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26076,7 +26076,7 @@
         <v>45581</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26149,7 +26149,7 @@
         <v>45763</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26222,7 +26222,7 @@
         <v>45763</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26295,7 +26295,7 @@
         <v>45938</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26368,7 +26368,7 @@
         <v>45812</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26441,7 +26441,7 @@
         <v>45631</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26514,7 +26514,7 @@
         <v>45355</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26587,7 +26587,7 @@
         <v>45355</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26665,7 +26665,7 @@
         <v>45529</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26738,7 +26738,7 @@
         <v>46140</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26816,7 +26816,7 @@
         <v>45631</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26889,7 +26889,7 @@
         <v>44943</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26962,7 +26962,7 @@
         <v>45589</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27035,7 +27035,7 @@
         <v>45010</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27108,7 +27108,7 @@
         <v>45581</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27181,7 +27181,7 @@
         <v>45867</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27254,7 +27254,7 @@
         <v>45726</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27327,7 +27327,7 @@
         <v>45271</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27400,7 +27400,7 @@
         <v>46147</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27473,7 +27473,7 @@
         <v>45085</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27546,7 +27546,7 @@
         <v>44543</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27619,7 +27619,7 @@
         <v>44865</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27692,7 +27692,7 @@
         <v>46141</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27765,7 +27765,7 @@
         <v>45048</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27838,7 +27838,7 @@
         <v>45533</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27911,7 +27911,7 @@
         <v>46155</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -27984,7 +27984,7 @@
         <v>45001</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28057,7 +28057,7 @@
         <v>45282</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28130,7 +28130,7 @@
         <v>45273</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28203,7 +28203,7 @@
         <v>45273</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28276,7 +28276,7 @@
         <v>45706</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28349,7 +28349,7 @@
         <v>45612</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28422,7 +28422,7 @@
         <v>45615</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28495,7 +28495,7 @@
         <v>45818</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28568,7 +28568,7 @@
         <v>45250</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28641,7 +28641,7 @@
         <v>45250</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28714,7 +28714,7 @@
         <v>45251</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28787,7 +28787,7 @@
         <v>45546</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -28860,7 +28860,7 @@
         <v>45180</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -28933,7 +28933,7 @@
         <v>46076</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29006,7 +29006,7 @@
         <v>45539</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29079,7 +29079,7 @@
         <v>45311</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29152,7 +29152,7 @@
         <v>45308</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29225,7 +29225,7 @@
         <v>45384</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29298,7 +29298,7 @@
         <v>45374</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29371,7 +29371,7 @@
         <v>45706</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29444,7 +29444,7 @@
         <v>45211</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29517,7 +29517,7 @@
         <v>45728</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29590,7 +29590,7 @@
         <v>45012</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29663,7 +29663,7 @@
         <v>45314</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -29736,7 +29736,7 @@
         <v>45476</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -29809,7 +29809,7 @@
         <v>45707</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -29882,7 +29882,7 @@
         <v>45303</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -29955,7 +29955,7 @@
         <v>45653</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30028,7 +30028,7 @@
         <v>45653</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30101,7 +30101,7 @@
         <v>45187</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30174,7 +30174,7 @@
         <v>45716</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30252,7 +30252,7 @@
         <v>44973</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30325,7 +30325,7 @@
         <v>44942</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30398,7 +30398,7 @@
         <v>45946</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30471,7 +30471,7 @@
         <v>45700</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30544,7 +30544,7 @@
         <v>45061</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30617,7 +30617,7 @@
         <v>45911</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30690,7 +30690,7 @@
         <v>44897</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -30763,7 +30763,7 @@
         <v>45286</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -30836,7 +30836,7 @@
         <v>45181</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -30909,7 +30909,7 @@
         <v>45887</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -30982,7 +30982,7 @@
         <v>44977</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31055,7 +31055,7 @@
         <v>45628</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31128,7 +31128,7 @@
         <v>45352</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31206,7 +31206,7 @@
         <v>45513</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31279,7 +31279,7 @@
         <v>45166</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31352,7 +31352,7 @@
         <v>45680</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31425,7 +31425,7 @@
         <v>46184</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31498,7 +31498,7 @@
         <v>45191</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31571,7 +31571,7 @@
         <v>46184</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31644,7 +31644,7 @@
         <v>44853</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -31717,7 +31717,7 @@
         <v>45251</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -31790,7 +31790,7 @@
         <v>45589</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -31863,7 +31863,7 @@
         <v>44855</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -31936,7 +31936,7 @@
         <v>44942</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32009,7 +32009,7 @@
         <v>45680</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32082,7 +32082,7 @@
         <v>45462</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32155,7 +32155,7 @@
         <v>45412</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32228,7 +32228,7 @@
         <v>45792</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32301,7 +32301,7 @@
         <v>45113</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32374,7 +32374,7 @@
         <v>45421</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32447,7 +32447,7 @@
         <v>45558</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32520,7 +32520,7 @@
         <v>45090</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32593,7 +32593,7 @@
         <v>45567</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -32666,7 +32666,7 @@
         <v>46198</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -32739,7 +32739,7 @@
         <v>46198</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -32812,7 +32812,7 @@
         <v>45268</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -32885,7 +32885,7 @@
         <v>46198</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -32958,7 +32958,7 @@
         <v>46198</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33031,7 +33031,7 @@
         <v>46190</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33109,7 +33109,7 @@
         <v>44930</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33182,7 +33182,7 @@
         <v>44476</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33255,7 +33255,7 @@
         <v>46202</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33328,7 +33328,7 @@
         <v>45698</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33401,7 +33401,7 @@
         <v>45177</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33474,7 +33474,7 @@
         <v>46204</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33547,7 +33547,7 @@
         <v>44986</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33625,7 +33625,7 @@
         <v>46204</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -33698,7 +33698,7 @@
         <v>46204</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -33771,7 +33771,7 @@
         <v>46204</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -33844,7 +33844,7 @@
         <v>46204</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -33917,7 +33917,7 @@
         <v>46204</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -33990,7 +33990,7 @@
         <v>46204</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34063,7 +34063,7 @@
         <v>45175</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34136,7 +34136,7 @@
         <v>45677</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34209,7 +34209,7 @@
         <v>46206</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34282,7 +34282,7 @@
         <v>45462</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34355,7 +34355,7 @@
         <v>45081</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34428,7 +34428,7 @@
         <v>46206</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34501,7 +34501,7 @@
         <v>45166</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34574,7 +34574,7 @@
         <v>45595</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -34647,7 +34647,7 @@
         <v>44942</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -34720,7 +34720,7 @@
         <v>45391</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -34793,7 +34793,7 @@
         <v>45373</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -34871,7 +34871,7 @@
         <v>45373</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -34949,7 +34949,7 @@
         <v>45155</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35022,7 +35022,7 @@
         <v>46257</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35095,7 +35095,7 @@
         <v>46258</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35168,7 +35168,7 @@
         <v>46258</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35241,7 +35241,7 @@
         <v>46216</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35319,7 +35319,7 @@
         <v>46216</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35397,7 +35397,7 @@
         <v>46216</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35475,7 +35475,7 @@
         <v>46216</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35553,7 +35553,7 @@
         <v>46216</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -35631,7 +35631,7 @@
         <v>46216</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -35709,7 +35709,7 @@
         <v>45564</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -35782,7 +35782,7 @@
         <v>45010</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -35855,7 +35855,7 @@
         <v>46261</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -35928,7 +35928,7 @@
         <v>45113</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36001,7 +36001,7 @@
         <v>45214</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36074,7 +36074,7 @@
         <v>45217</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36147,7 +36147,7 @@
         <v>45156</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36220,7 +36220,7 @@
         <v>44942</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36293,7 +36293,7 @@
         <v>45539</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36366,7 +36366,7 @@
         <v>45355</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36444,7 +36444,7 @@
         <v>44882</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36517,7 +36517,7 @@
         <v>45175</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36590,7 +36590,7 @@
         <v>45175</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -36663,7 +36663,7 @@
         <v>45076</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -36736,7 +36736,7 @@
         <v>45076</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -36809,7 +36809,7 @@
         <v>46267</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -36882,7 +36882,7 @@
         <v>46268</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -36955,7 +36955,7 @@
         <v>46226</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37028,7 +37028,7 @@
         <v>46226</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37101,7 +37101,7 @@
         <v>46226</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37174,7 +37174,7 @@
         <v>45653</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37247,7 +37247,7 @@
         <v>44526</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37320,7 +37320,7 @@
         <v>45612</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37393,7 +37393,7 @@
         <v>46227</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37466,7 +37466,7 @@
         <v>45625</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -37539,7 +37539,7 @@
         <v>46227</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -37612,7 +37612,7 @@
         <v>44816</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -37685,7 +37685,7 @@
         <v>45222</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -37758,7 +37758,7 @@
         <v>46234</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -37836,7 +37836,7 @@
         <v>45211</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -37909,7 +37909,7 @@
         <v>46279</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -37982,7 +37982,7 @@
         <v>45435</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38055,7 +38055,7 @@
         <v>45435</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38128,7 +38128,7 @@
         <v>45435</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38201,7 +38201,7 @@
         <v>44911</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38274,7 +38274,7 @@
         <v>46280</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38347,7 +38347,7 @@
         <v>45748</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38420,7 +38420,7 @@
         <v>45378</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38493,7 +38493,7 @@
         <v>45141</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -38566,7 +38566,7 @@
         <v>44992</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -38639,7 +38639,7 @@
         <v>44992</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -38712,7 +38712,7 @@
         <v>45202</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -38785,7 +38785,7 @@
         <v>45588</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -38858,7 +38858,7 @@
         <v>46240</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -38936,7 +38936,7 @@
         <v>45246</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39009,7 +39009,7 @@
         <v>46240</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39087,7 +39087,7 @@
         <v>46240</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39165,7 +39165,7 @@
         <v>44865</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39238,7 +39238,7 @@
         <v>44698</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39311,7 +39311,7 @@
         <v>46066</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39384,7 +39384,7 @@
         <v>45189</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39457,7 +39457,7 @@
         <v>45911</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39530,7 +39530,7 @@
         <v>45352</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -39608,7 +39608,7 @@
         <v>44687</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -39681,7 +39681,7 @@
         <v>45467</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -39754,7 +39754,7 @@
         <v>45211</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -39827,7 +39827,7 @@
         <v>46092</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -39900,7 +39900,7 @@
         <v>45187</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -39973,7 +39973,7 @@
         <v>45450</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40046,7 +40046,7 @@
         <v>45253</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40119,7 +40119,7 @@
         <v>46245</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40192,7 +40192,7 @@
         <v>46287</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40265,7 +40265,7 @@
         <v>46246</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40338,7 +40338,7 @@
         <v>46287</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40411,7 +40411,7 @@
         <v>46287</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40484,7 +40484,7 @@
         <v>46287</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -40557,7 +40557,7 @@
         <v>45051</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -40630,7 +40630,7 @@
         <v>45215</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -40703,7 +40703,7 @@
         <v>46287</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -40776,7 +40776,7 @@
         <v>46283</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -40849,7 +40849,7 @@
         <v>46245</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -40922,7 +40922,7 @@
         <v>46287</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -40995,7 +40995,7 @@
         <v>45078</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41068,7 +41068,7 @@
         <v>46247</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41141,7 +41141,7 @@
         <v>46154</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41214,7 +41214,7 @@
         <v>45916</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41287,7 +41287,7 @@
         <v>46290</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41360,7 +41360,7 @@
         <v>45574</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41433,7 +41433,7 @@
         <v>46248</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41506,7 +41506,7 @@
         <v>46168</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -41579,7 +41579,7 @@
         <v>46251</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -41657,7 +41657,7 @@
         <v>46248</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -41730,7 +41730,7 @@
         <v>44992</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -41803,7 +41803,7 @@
         <v>46293</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -41881,7 +41881,7 @@
         <v>46247</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -41954,7 +41954,7 @@
         <v>46030</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42027,7 +42027,7 @@
         <v>46290</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42100,7 +42100,7 @@
         <v>45244</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42173,7 +42173,7 @@
         <v>45687</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42246,7 +42246,7 @@
         <v>44858</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42319,7 +42319,7 @@
         <v>46262</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42392,7 +42392,7 @@
         <v>45539</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42465,7 +42465,7 @@
         <v>45609</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -42538,7 +42538,7 @@
         <v>46294</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -42611,7 +42611,7 @@
         <v>44531</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -42684,7 +42684,7 @@
         <v>45049</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -42757,7 +42757,7 @@
         <v>46295</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -42830,7 +42830,7 @@
         <v>45679</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -42903,7 +42903,7 @@
         <v>46294</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -42976,7 +42976,7 @@
         <v>44859</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43049,7 +43049,7 @@
         <v>44531</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43122,7 +43122,7 @@
         <v>46295</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43195,7 +43195,7 @@
         <v>46294</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43268,7 +43268,7 @@
         <v>46251</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43341,7 +43341,7 @@
         <v>46251</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43414,7 +43414,7 @@
         <v>45446</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43487,7 +43487,7 @@
         <v>45616</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -43560,7 +43560,7 @@
         <v>46155</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -43633,7 +43633,7 @@
         <v>44587</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -43706,7 +43706,7 @@
         <v>45770</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -43779,7 +43779,7 @@
         <v>44582</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -43852,7 +43852,7 @@
         <v>45759</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -43925,7 +43925,7 @@
         <v>45531</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -43998,7 +43998,7 @@
         <v>46254</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44071,7 +44071,7 @@
         <v>46254</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44144,7 +44144,7 @@
         <v>44897</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44217,7 +44217,7 @@
         <v>45583</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44290,7 +44290,7 @@
         <v>45594</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44363,7 +44363,7 @@
         <v>45469</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44441,7 +44441,7 @@
         <v>45401</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44514,7 +44514,7 @@
         <v>45092</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -44587,7 +44587,7 @@
         <v>45092</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -44660,7 +44660,7 @@
         <v>45103</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -44733,7 +44733,7 @@
         <v>44760</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -44806,7 +44806,7 @@
         <v>44526</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -44879,7 +44879,7 @@
         <v>45268</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -44952,7 +44952,7 @@
         <v>45440</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45025,7 +45025,7 @@
         <v>45244</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45098,7 +45098,7 @@
         <v>45051</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45171,7 +45171,7 @@
         <v>45176</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45244,7 +45244,7 @@
         <v>44921</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45317,7 +45317,7 @@
         <v>44928</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45390,7 +45390,7 @@
         <v>44568</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45463,7 +45463,7 @@
         <v>44634</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -45536,7 +45536,7 @@
         <v>44592</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -45609,7 +45609,7 @@
         <v>44777</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -45682,7 +45682,7 @@
         <v>44942</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -45755,7 +45755,7 @@
         <v>44942</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -45828,7 +45828,7 @@
         <v>45273</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -45901,7 +45901,7 @@
         <v>45497</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -45974,7 +45974,7 @@
         <v>45217</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46047,7 +46047,7 @@
         <v>44621</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46120,7 +46120,7 @@
         <v>44922</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46193,7 +46193,7 @@
         <v>45169</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46266,7 +46266,7 @@
         <v>44860</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46339,7 +46339,7 @@
         <v>45154</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46412,7 +46412,7 @@
         <v>44636</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -46485,7 +46485,7 @@
         <v>44529</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -46558,7 +46558,7 @@
         <v>44508</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -46631,7 +46631,7 @@
         <v>44858</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -46704,7 +46704,7 @@
         <v>45776</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -46777,7 +46777,7 @@
         <v>45663</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -46850,7 +46850,7 @@
         <v>45624</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -46923,7 +46923,7 @@
         <v>45781</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -46996,7 +46996,7 @@
         <v>45407</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47069,7 +47069,7 @@
         <v>45719</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47142,7 +47142,7 @@
         <v>44634</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47215,7 +47215,7 @@
         <v>44658</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47288,7 +47288,7 @@
         <v>44621</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -47361,7 +47361,7 @@
         <v>44474</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -47434,7 +47434,7 @@
         <v>44607</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -47507,7 +47507,7 @@
         <v>44733</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -47585,7 +47585,7 @@
         <v>45302</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -47658,7 +47658,7 @@
         <v>45476</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -47731,7 +47731,7 @@
         <v>45649</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -47804,7 +47804,7 @@
         <v>45728</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -47877,7 +47877,7 @@
         <v>45953</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -47950,7 +47950,7 @@
         <v>45967</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48023,7 +48023,7 @@
         <v>46010</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48096,7 +48096,7 @@
         <v>46010</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48169,7 +48169,7 @@
         <v>46029</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -48247,7 +48247,7 @@
         <v>46079</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -48320,7 +48320,7 @@
         <v>46094</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -48393,7 +48393,7 @@
         <v>46119</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -48466,7 +48466,7 @@
         <v>46182</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>

--- a/Översikt ÄLMHULT.xlsx
+++ b/Översikt ÄLMHULT.xlsx
@@ -601,7 +601,7 @@
         <v>46209</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>45786</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
         <v>46041</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
         <v>45945</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>44883</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>45215</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>45645</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>46211</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>44883</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         <v>45183</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>44830</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>45012</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
         <v>45818</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2021,7 +2021,7 @@
         <v>44889</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>46171</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>45050</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>45908</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2454,7 +2454,7 @@
         <v>45386</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2559,7 +2559,7 @@
         <v>45280</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
         <v>45560</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2773,7 +2773,7 @@
         <v>45631</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2878,7 +2878,7 @@
         <v>45218</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2983,7 +2983,7 @@
         <v>45932</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3092,7 +3092,7 @@
         <v>44882</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
         <v>45719</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3302,7 +3302,7 @@
         <v>45763</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3407,7 +3407,7 @@
         <v>45856</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3516,7 +3516,7 @@
         <v>45769</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3621,7 +3621,7 @@
         <v>46204</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3726,7 +3726,7 @@
         <v>46290</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3831,7 +3831,7 @@
         <v>45888</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3936,7 +3936,7 @@
         <v>44869</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4041,7 +4041,7 @@
         <v>45786</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4146,7 +4146,7 @@
         <v>46043</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4251,7 +4251,7 @@
         <v>44609</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4324,7 +4324,7 @@
         <v>44525</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4397,7 +4397,7 @@
         <v>44785</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4470,7 +4470,7 @@
         <v>44785</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4543,7 +4543,7 @@
         <v>44785</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4616,7 +4616,7 @@
         <v>44515</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4689,7 +4689,7 @@
         <v>44785</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4762,7 +4762,7 @@
         <v>44802</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4835,7 +4835,7 @@
         <v>44802</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4908,7 +4908,7 @@
         <v>44749</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4981,7 +4981,7 @@
         <v>44798</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5054,7 +5054,7 @@
         <v>44523</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5127,7 +5127,7 @@
         <v>44503</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5200,7 +5200,7 @@
         <v>44503</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5273,7 +5273,7 @@
         <v>44785</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5346,7 +5346,7 @@
         <v>44665</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5424,7 +5424,7 @@
         <v>44846</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5497,7 +5497,7 @@
         <v>44847</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5570,7 +5570,7 @@
         <v>44498</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5643,7 +5643,7 @@
         <v>44690</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5716,7 +5716,7 @@
         <v>44812</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5789,7 +5789,7 @@
         <v>44504</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5862,7 +5862,7 @@
         <v>44602</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5935,7 +5935,7 @@
         <v>44690</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6008,7 +6008,7 @@
         <v>44690</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         <v>44509</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6154,7 +6154,7 @@
         <v>44643</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6227,7 +6227,7 @@
         <v>44596</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6300,7 +6300,7 @@
         <v>44865</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6373,7 +6373,7 @@
         <v>44739</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6446,7 +6446,7 @@
         <v>44510</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6519,7 +6519,7 @@
         <v>44522</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6592,7 +6592,7 @@
         <v>44551</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6665,7 +6665,7 @@
         <v>44512</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6738,7 +6738,7 @@
         <v>44733</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6811,7 +6811,7 @@
         <v>44621</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6884,7 +6884,7 @@
         <v>44496</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6957,7 +6957,7 @@
         <v>44609</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7030,7 +7030,7 @@
         <v>44721</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7103,7 +7103,7 @@
         <v>44525</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7176,7 +7176,7 @@
         <v>44685</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7249,7 +7249,7 @@
         <v>44621</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7322,7 +7322,7 @@
         <v>44854</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7395,7 +7395,7 @@
         <v>44487</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7468,7 +7468,7 @@
         <v>44721</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7541,7 +7541,7 @@
         <v>44636</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7614,7 +7614,7 @@
         <v>44854</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7687,7 +7687,7 @@
         <v>44680</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7760,7 +7760,7 @@
         <v>44587</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7838,7 +7838,7 @@
         <v>44524</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7911,7 +7911,7 @@
         <v>44802</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7984,7 +7984,7 @@
         <v>44529</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8057,7 +8057,7 @@
         <v>44657</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8130,7 +8130,7 @@
         <v>44831</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8203,7 +8203,7 @@
         <v>44831</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8276,7 +8276,7 @@
         <v>45061</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8349,7 +8349,7 @@
         <v>45638</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8422,7 +8422,7 @@
         <v>45090</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8495,7 +8495,7 @@
         <v>45133</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8568,7 +8568,7 @@
         <v>44882</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8641,7 +8641,7 @@
         <v>45467</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8714,7 +8714,7 @@
         <v>44491</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         <v>45638</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8860,7 +8860,7 @@
         <v>44897</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8933,7 +8933,7 @@
         <v>45090</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9006,7 +9006,7 @@
         <v>44816</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9079,7 +9079,7 @@
         <v>45612</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9152,7 +9152,7 @@
         <v>45440</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9225,7 +9225,7 @@
         <v>45051</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9298,7 +9298,7 @@
         <v>45078</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9371,7 +9371,7 @@
         <v>45078</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9444,7 +9444,7 @@
         <v>45215</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9517,7 +9517,7 @@
         <v>44858</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9590,7 +9590,7 @@
         <v>44942</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9663,7 +9663,7 @@
         <v>45222</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9736,7 +9736,7 @@
         <v>45222</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9809,7 +9809,7 @@
         <v>45374</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9882,7 +9882,7 @@
         <v>45268</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9955,7 +9955,7 @@
         <v>45716</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10028,7 +10028,7 @@
         <v>45497</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10101,7 +10101,7 @@
         <v>45433</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10174,7 +10174,7 @@
         <v>44897</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10247,7 +10247,7 @@
         <v>45737</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10320,7 +10320,7 @@
         <v>45700</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10393,7 +10393,7 @@
         <v>45653</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10466,7 +10466,7 @@
         <v>45254</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10539,7 +10539,7 @@
         <v>44942</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10612,7 +10612,7 @@
         <v>45103</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10685,7 +10685,7 @@
         <v>45303</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10758,7 +10758,7 @@
         <v>45251</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10831,7 +10831,7 @@
         <v>45251</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10904,7 +10904,7 @@
         <v>45539</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10977,7 +10977,7 @@
         <v>45211</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11050,7 +11050,7 @@
         <v>45010</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11123,7 +11123,7 @@
         <v>45049</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11196,7 +11196,7 @@
         <v>45217</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11269,7 +11269,7 @@
         <v>44508</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11342,7 +11342,7 @@
         <v>45707</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11415,7 +11415,7 @@
         <v>45595</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11488,7 +11488,7 @@
         <v>45457</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11561,7 +11561,7 @@
         <v>44853</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11634,7 +11634,7 @@
         <v>45566</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11707,7 +11707,7 @@
         <v>45384</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11780,7 +11780,7 @@
         <v>45271</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11853,7 +11853,7 @@
         <v>45547</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11926,7 +11926,7 @@
         <v>45317</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11999,7 +11999,7 @@
         <v>45529</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12072,7 +12072,7 @@
         <v>44986</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12150,7 +12150,7 @@
         <v>45211</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12223,7 +12223,7 @@
         <v>45089</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12296,7 +12296,7 @@
         <v>45251</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12369,7 +12369,7 @@
         <v>45244</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12442,7 +12442,7 @@
         <v>45001</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12515,7 +12515,7 @@
         <v>45348</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12588,7 +12588,7 @@
         <v>45228</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12661,7 +12661,7 @@
         <v>45252</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12734,7 +12734,7 @@
         <v>44922</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12807,7 +12807,7 @@
         <v>45401</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12880,7 +12880,7 @@
         <v>45352</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12958,7 +12958,7 @@
         <v>45680</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13031,7 +13031,7 @@
         <v>44865</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13104,7 +13104,7 @@
         <v>44855</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13177,7 +13177,7 @@
         <v>45309</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13250,7 +13250,7 @@
         <v>44897</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13323,7 +13323,7 @@
         <v>45215</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13396,7 +13396,7 @@
         <v>44935</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13469,7 +13469,7 @@
         <v>45303</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13542,7 +13542,7 @@
         <v>44992</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13615,7 +13615,7 @@
         <v>45286</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13688,7 +13688,7 @@
         <v>45533</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13761,7 +13761,7 @@
         <v>44962</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13834,7 +13834,7 @@
         <v>44973</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13907,7 +13907,7 @@
         <v>44998</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13985,7 +13985,7 @@
         <v>45211</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14058,7 +14058,7 @@
         <v>45457</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14131,7 +14131,7 @@
         <v>45457</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14204,7 +14204,7 @@
         <v>45140</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14277,7 +14277,7 @@
         <v>45589</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14350,7 +14350,7 @@
         <v>45884</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14423,7 +14423,7 @@
         <v>45103</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14496,7 +14496,7 @@
         <v>44777</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14569,7 +14569,7 @@
         <v>45352</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14647,7 +14647,7 @@
         <v>45888</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14720,7 +14720,7 @@
         <v>44582</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14793,7 +14793,7 @@
         <v>45653</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14866,7 +14866,7 @@
         <v>45887</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14939,7 +14939,7 @@
         <v>44942</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15012,7 +15012,7 @@
         <v>45181</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15085,7 +15085,7 @@
         <v>45637</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15158,7 +15158,7 @@
         <v>45706</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15231,7 +15231,7 @@
         <v>45092</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15304,7 +15304,7 @@
         <v>45006</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15382,7 +15382,7 @@
         <v>45092</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15455,7 +15455,7 @@
         <v>45443</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15528,7 +15528,7 @@
         <v>45734</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15601,7 +15601,7 @@
         <v>45113</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15674,7 +15674,7 @@
         <v>45166</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15747,7 +15747,7 @@
         <v>44545</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15820,7 +15820,7 @@
         <v>45376</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15893,7 +15893,7 @@
         <v>44942</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15966,7 +15966,7 @@
         <v>45015</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16039,7 +16039,7 @@
         <v>45169</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16112,7 +16112,7 @@
         <v>44543</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16185,7 +16185,7 @@
         <v>44943</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16258,7 +16258,7 @@
         <v>45155</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16331,7 +16331,7 @@
         <v>44921</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16404,7 +16404,7 @@
         <v>45450</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16477,7 +16477,7 @@
         <v>45378</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16550,7 +16550,7 @@
         <v>44817</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16623,7 +16623,7 @@
         <v>45898</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16696,7 +16696,7 @@
         <v>45897</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16769,7 +16769,7 @@
         <v>45759</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16842,7 +16842,7 @@
         <v>45314</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16915,7 +16915,7 @@
         <v>44930</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16988,7 +16988,7 @@
         <v>45589</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17061,7 +17061,7 @@
         <v>45373</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17139,7 +17139,7 @@
         <v>45373</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17217,7 +17217,7 @@
         <v>45435</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17290,7 +17290,7 @@
         <v>45435</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17363,7 +17363,7 @@
         <v>45748</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17436,7 +17436,7 @@
         <v>45435</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17509,7 +17509,7 @@
         <v>44853</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17582,7 +17582,7 @@
         <v>44523</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17655,7 +17655,7 @@
         <v>44994</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17728,7 +17728,7 @@
         <v>44994</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17801,7 +17801,7 @@
         <v>44531</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17874,7 +17874,7 @@
         <v>45373</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17952,7 +17952,7 @@
         <v>45567</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18025,7 +18025,7 @@
         <v>45586</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18098,7 +18098,7 @@
         <v>44911</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18171,7 +18171,7 @@
         <v>45538</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18244,7 +18244,7 @@
         <v>45315</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18317,7 +18317,7 @@
         <v>44928</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18390,7 +18390,7 @@
         <v>45209</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18463,7 +18463,7 @@
         <v>45615</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18536,7 +18536,7 @@
         <v>44958</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18609,7 +18609,7 @@
         <v>45098</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18702,7 +18702,7 @@
         <v>45680</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18775,7 +18775,7 @@
         <v>45663</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18848,7 +18848,7 @@
         <v>45175</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18921,7 +18921,7 @@
         <v>44503</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18994,7 +18994,7 @@
         <v>45776</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19067,7 +19067,7 @@
         <v>44859</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19140,7 +19140,7 @@
         <v>44914</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19213,7 +19213,7 @@
         <v>45781</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19286,7 +19286,7 @@
         <v>45574</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19359,7 +19359,7 @@
         <v>45559</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19432,7 +19432,7 @@
         <v>45624</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19505,7 +19505,7 @@
         <v>45608</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19578,7 +19578,7 @@
         <v>45916</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19651,7 +19651,7 @@
         <v>45915</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19729,7 +19729,7 @@
         <v>45156</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19802,7 +19802,7 @@
         <v>45558</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19875,7 +19875,7 @@
         <v>45539</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19948,7 +19948,7 @@
         <v>45638</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20021,7 +20021,7 @@
         <v>45407</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20094,7 +20094,7 @@
         <v>45133</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20167,7 +20167,7 @@
         <v>45917</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20245,7 +20245,7 @@
         <v>45917</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20323,7 +20323,7 @@
         <v>45527</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20396,7 +20396,7 @@
         <v>45719</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20469,7 +20469,7 @@
         <v>45355</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20542,7 +20542,7 @@
         <v>45355</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20620,7 +20620,7 @@
         <v>44979</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20693,7 +20693,7 @@
         <v>45917</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20771,7 +20771,7 @@
         <v>45681</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20844,7 +20844,7 @@
         <v>45189</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20917,7 +20917,7 @@
         <v>45010</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20990,7 +20990,7 @@
         <v>45539</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21063,7 +21063,7 @@
         <v>45355</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21141,7 +21141,7 @@
         <v>45687</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21214,7 +21214,7 @@
         <v>45543</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21287,7 +21287,7 @@
         <v>45513</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21360,7 +21360,7 @@
         <v>45929</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21433,7 +21433,7 @@
         <v>45720</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21506,7 +21506,7 @@
         <v>45462</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21579,7 +21579,7 @@
         <v>45554</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21652,7 +21652,7 @@
         <v>45564</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21725,7 +21725,7 @@
         <v>45930</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21798,7 +21798,7 @@
         <v>45254</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21871,7 +21871,7 @@
         <v>45049</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21944,7 +21944,7 @@
         <v>44994</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22017,7 +22017,7 @@
         <v>45930</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22090,7 +22090,7 @@
         <v>45706</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22163,7 +22163,7 @@
         <v>45589</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22236,7 +22236,7 @@
         <v>45799</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22309,7 +22309,7 @@
         <v>45282</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22382,7 +22382,7 @@
         <v>44686</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22455,7 +22455,7 @@
         <v>45460</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22528,7 +22528,7 @@
         <v>45350</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22601,7 +22601,7 @@
         <v>45405</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22674,7 +22674,7 @@
         <v>45702</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22747,7 +22747,7 @@
         <v>45663</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22820,7 +22820,7 @@
         <v>45616</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22893,7 +22893,7 @@
         <v>44636</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22966,7 +22966,7 @@
         <v>44511</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23039,7 +23039,7 @@
         <v>44511</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23112,7 +23112,7 @@
         <v>45446</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23185,7 +23185,7 @@
         <v>45804</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23258,7 +23258,7 @@
         <v>45191</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23331,7 +23331,7 @@
         <v>45716</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23409,7 +23409,7 @@
         <v>44531</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23482,7 +23482,7 @@
         <v>44587</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23555,7 +23555,7 @@
         <v>45062</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23628,7 +23628,7 @@
         <v>45677</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23701,7 +23701,7 @@
         <v>45170</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23774,7 +23774,7 @@
         <v>45944</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23847,7 +23847,7 @@
         <v>45222</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23920,7 +23920,7 @@
         <v>44592</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23993,7 +23993,7 @@
         <v>45594</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24066,7 +24066,7 @@
         <v>45215</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24139,7 +24139,7 @@
         <v>45588</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24212,7 +24212,7 @@
         <v>45945</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24285,7 +24285,7 @@
         <v>45462</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24358,7 +24358,7 @@
         <v>45258</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24431,7 +24431,7 @@
         <v>45653</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24504,7 +24504,7 @@
         <v>45548</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24577,7 +24577,7 @@
         <v>44859</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24650,7 +24650,7 @@
         <v>45818</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24723,7 +24723,7 @@
         <v>45695</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24796,7 +24796,7 @@
         <v>44634</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24869,7 +24869,7 @@
         <v>44861</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24942,7 +24942,7 @@
         <v>45625</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25015,7 +25015,7 @@
         <v>45716</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25088,7 +25088,7 @@
         <v>44698</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25161,7 +25161,7 @@
         <v>45771</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25234,7 +25234,7 @@
         <v>45578</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25307,7 +25307,7 @@
         <v>45308</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25380,7 +25380,7 @@
         <v>45947</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25453,7 +25453,7 @@
         <v>45372</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25526,7 +25526,7 @@
         <v>45240</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25604,7 +25604,7 @@
         <v>45629</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25677,7 +25677,7 @@
         <v>45166</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25750,7 +25750,7 @@
         <v>45916</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25828,7 +25828,7 @@
         <v>45335</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25901,7 +25901,7 @@
         <v>45441</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -25974,7 +25974,7 @@
         <v>45334</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26047,7 +26047,7 @@
         <v>45460</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26120,7 +26120,7 @@
         <v>45693</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26193,7 +26193,7 @@
         <v>45698</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26266,7 +26266,7 @@
         <v>45952</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26339,7 +26339,7 @@
         <v>45959</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26412,7 +26412,7 @@
         <v>45202</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26485,7 +26485,7 @@
         <v>45180</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26558,7 +26558,7 @@
         <v>45145</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26631,7 +26631,7 @@
         <v>45834</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26704,7 +26704,7 @@
         <v>45211</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26777,7 +26777,7 @@
         <v>45214</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26850,7 +26850,7 @@
         <v>45835</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -26923,7 +26923,7 @@
         <v>45175</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -26996,7 +26996,7 @@
         <v>45175</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27069,7 +27069,7 @@
         <v>45680</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27142,7 +27142,7 @@
         <v>44641</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27215,7 +27215,7 @@
         <v>45187</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27288,7 +27288,7 @@
         <v>45966</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27361,7 +27361,7 @@
         <v>45839</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27434,7 +27434,7 @@
         <v>45469</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27512,7 +27512,7 @@
         <v>45966</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27585,7 +27585,7 @@
         <v>45078</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27658,7 +27658,7 @@
         <v>45715</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27731,7 +27731,7 @@
         <v>45966</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27804,7 +27804,7 @@
         <v>45681</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -27877,7 +27877,7 @@
         <v>45842</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -27950,7 +27950,7 @@
         <v>45967</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28023,7 +28023,7 @@
         <v>45233</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28096,7 +28096,7 @@
         <v>45233</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28169,7 +28169,7 @@
         <v>45631</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28242,7 +28242,7 @@
         <v>45842</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28315,7 +28315,7 @@
         <v>45051</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28388,7 +28388,7 @@
         <v>45154</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28461,7 +28461,7 @@
         <v>45842</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28534,7 +28534,7 @@
         <v>45841</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28607,7 +28607,7 @@
         <v>45529</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28680,7 +28680,7 @@
         <v>45969</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -28753,7 +28753,7 @@
         <v>45969</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -28826,7 +28826,7 @@
         <v>45846</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -28899,7 +28899,7 @@
         <v>45845</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -28972,7 +28972,7 @@
         <v>44760</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29045,7 +29045,7 @@
         <v>45610</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29118,7 +29118,7 @@
         <v>44526</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29191,7 +29191,7 @@
         <v>45612</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29264,7 +29264,7 @@
         <v>45770</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29337,7 +29337,7 @@
         <v>45076</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29410,7 +29410,7 @@
         <v>45076</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29483,7 +29483,7 @@
         <v>45726</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29556,7 +29556,7 @@
         <v>45726</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -29629,7 +29629,7 @@
         <v>45854</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -29702,7 +29702,7 @@
         <v>45763</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -29775,7 +29775,7 @@
         <v>45763</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -29848,7 +29848,7 @@
         <v>45581</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -29921,7 +29921,7 @@
         <v>45246</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -29994,7 +29994,7 @@
         <v>45819</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30067,7 +30067,7 @@
         <v>44979</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30140,7 +30140,7 @@
         <v>45812</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30213,7 +30213,7 @@
         <v>45679</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30286,7 +30286,7 @@
         <v>45631</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30359,7 +30359,7 @@
         <v>45531</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30432,7 +30432,7 @@
         <v>44826</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30505,7 +30505,7 @@
         <v>45352</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30583,7 +30583,7 @@
         <v>45062</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -30656,7 +30656,7 @@
         <v>45726</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -30729,7 +30729,7 @@
         <v>44496</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -30802,7 +30802,7 @@
         <v>45867</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -30875,7 +30875,7 @@
         <v>45581</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -30948,7 +30948,7 @@
         <v>44568</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31021,7 +31021,7 @@
         <v>45250</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31094,7 +31094,7 @@
         <v>45250</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31167,7 +31167,7 @@
         <v>45253</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31240,7 +31240,7 @@
         <v>45748</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31313,7 +31313,7 @@
         <v>45421</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31386,7 +31386,7 @@
         <v>45716</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31464,7 +31464,7 @@
         <v>45211</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31537,7 +31537,7 @@
         <v>45176</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -31610,7 +31610,7 @@
         <v>44784</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -31688,7 +31688,7 @@
         <v>45348</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -31761,7 +31761,7 @@
         <v>45476</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -31834,7 +31834,7 @@
         <v>45244</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -31907,7 +31907,7 @@
         <v>45084</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -31980,7 +31980,7 @@
         <v>44496</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32053,7 +32053,7 @@
         <v>45735</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32126,7 +32126,7 @@
         <v>45735</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32199,7 +32199,7 @@
         <v>45051</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32272,7 +32272,7 @@
         <v>45273</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32345,7 +32345,7 @@
         <v>45273</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32418,7 +32418,7 @@
         <v>45268</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32491,7 +32491,7 @@
         <v>46105</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -32569,7 +32569,7 @@
         <v>46105</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -32647,7 +32647,7 @@
         <v>46105</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -32725,7 +32725,7 @@
         <v>44865</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -32798,7 +32798,7 @@
         <v>46105</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -32876,7 +32876,7 @@
         <v>46105</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -32954,7 +32954,7 @@
         <v>45469</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33027,7 +33027,7 @@
         <v>45986</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33105,7 +33105,7 @@
         <v>46105</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33183,7 +33183,7 @@
         <v>46105</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33261,7 +33261,7 @@
         <v>46107</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33334,7 +33334,7 @@
         <v>45175</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33407,7 +33407,7 @@
         <v>44876</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33480,7 +33480,7 @@
         <v>46106</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33558,7 +33558,7 @@
         <v>45440</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -33631,7 +33631,7 @@
         <v>46108</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -33704,7 +33704,7 @@
         <v>45078</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -33777,7 +33777,7 @@
         <v>45113</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -33850,7 +33850,7 @@
         <v>46108</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -33923,7 +33923,7 @@
         <v>45992</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34001,7 +34001,7 @@
         <v>45992</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34079,7 +34079,7 @@
         <v>45992</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34157,7 +34157,7 @@
         <v>45992</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34235,7 +34235,7 @@
         <v>45180</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34308,7 +34308,7 @@
         <v>44921</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34381,7 +34381,7 @@
         <v>45734</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34454,7 +34454,7 @@
         <v>45583</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34527,7 +34527,7 @@
         <v>45608</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -34600,7 +34600,7 @@
         <v>45546</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -34673,7 +34673,7 @@
         <v>44621</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -34746,7 +34746,7 @@
         <v>46125</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -34819,7 +34819,7 @@
         <v>46000</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -34897,7 +34897,7 @@
         <v>46128</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -34970,7 +34970,7 @@
         <v>44858</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35043,7 +35043,7 @@
         <v>45187</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35116,7 +35116,7 @@
         <v>45412</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35189,7 +35189,7 @@
         <v>45414</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35262,7 +35262,7 @@
         <v>44992</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35335,7 +35335,7 @@
         <v>44610</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35408,7 +35408,7 @@
         <v>46005</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35481,7 +35481,7 @@
         <v>44992</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -35554,7 +35554,7 @@
         <v>45575</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -35627,7 +35627,7 @@
         <v>45167</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -35700,7 +35700,7 @@
         <v>44942</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -35773,7 +35773,7 @@
         <v>45085</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -35846,7 +35846,7 @@
         <v>45938</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -35919,7 +35919,7 @@
         <v>44942</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -35992,7 +35992,7 @@
         <v>45722</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36065,7 +36065,7 @@
         <v>44860</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36138,7 +36138,7 @@
         <v>45187</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36211,7 +36211,7 @@
         <v>45290</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36284,7 +36284,7 @@
         <v>45609</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36357,7 +36357,7 @@
         <v>45217</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36430,7 +36430,7 @@
         <v>45244</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36503,7 +36503,7 @@
         <v>45835</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -36576,7 +36576,7 @@
         <v>45111</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -36649,7 +36649,7 @@
         <v>45531</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -36727,7 +36727,7 @@
         <v>45812</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -36800,7 +36800,7 @@
         <v>44526</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -36873,7 +36873,7 @@
         <v>45141</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -36946,7 +36946,7 @@
         <v>45359</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37019,7 +37019,7 @@
         <v>46016</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37092,7 +37092,7 @@
         <v>45911</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37165,7 +37165,7 @@
         <v>45887</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37238,7 +37238,7 @@
         <v>45883</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37311,7 +37311,7 @@
         <v>45012</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37384,7 +37384,7 @@
         <v>45817</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -37457,7 +37457,7 @@
         <v>45733</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -37530,7 +37530,7 @@
         <v>44687</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -37603,7 +37603,7 @@
         <v>45081</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -37676,7 +37676,7 @@
         <v>45537</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -37749,7 +37749,7 @@
         <v>45531</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -37822,7 +37822,7 @@
         <v>45068</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -37895,7 +37895,7 @@
         <v>46000</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -37973,7 +37973,7 @@
         <v>45328</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38046,7 +38046,7 @@
         <v>45010</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38119,7 +38119,7 @@
         <v>46035</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38192,7 +38192,7 @@
         <v>45048</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38265,7 +38265,7 @@
         <v>46038</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38338,7 +38338,7 @@
         <v>46037</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38411,7 +38411,7 @@
         <v>45177</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -38484,7 +38484,7 @@
         <v>45042</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -38557,7 +38557,7 @@
         <v>45273</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -38630,7 +38630,7 @@
         <v>45930</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -38703,7 +38703,7 @@
         <v>45630</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -38776,7 +38776,7 @@
         <v>45391</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -38849,7 +38849,7 @@
         <v>45134</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -38922,7 +38922,7 @@
         <v>44743</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -38995,7 +38995,7 @@
         <v>45469</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39073,7 +39073,7 @@
         <v>46045</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39146,7 +39146,7 @@
         <v>44977</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39219,7 +39219,7 @@
         <v>45373</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39297,7 +39297,7 @@
         <v>45373</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39375,7 +39375,7 @@
         <v>45628</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39448,7 +39448,7 @@
         <v>45311</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -39521,7 +39521,7 @@
         <v>46052</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -39594,7 +39594,7 @@
         <v>46052</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -39667,7 +39667,7 @@
         <v>46140</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -39745,7 +39745,7 @@
         <v>46061</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -39818,7 +39818,7 @@
         <v>46063</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -39891,7 +39891,7 @@
         <v>46065</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -39964,7 +39964,7 @@
         <v>46147</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40037,7 +40037,7 @@
         <v>46141</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40110,7 +40110,7 @@
         <v>46076</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40183,7 +40183,7 @@
         <v>45827</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40256,7 +40256,7 @@
         <v>46155</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40329,7 +40329,7 @@
         <v>46076</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40402,7 +40402,7 @@
         <v>46093</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -40475,7 +40475,7 @@
         <v>45818</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -40548,7 +40548,7 @@
         <v>45728</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -40621,7 +40621,7 @@
         <v>45946</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -40694,7 +40694,7 @@
         <v>45911</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -40767,7 +40767,7 @@
         <v>46184</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -40840,7 +40840,7 @@
         <v>46184</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -40913,7 +40913,7 @@
         <v>45792</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -40986,7 +40986,7 @@
         <v>46190</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41064,7 +41064,7 @@
         <v>46198</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41137,7 +41137,7 @@
         <v>46198</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41210,7 +41210,7 @@
         <v>46198</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41283,7 +41283,7 @@
         <v>46198</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41356,7 +41356,7 @@
         <v>46202</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41429,7 +41429,7 @@
         <v>46204</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -41502,7 +41502,7 @@
         <v>46204</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -41575,7 +41575,7 @@
         <v>46204</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -41648,7 +41648,7 @@
         <v>46206</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -41721,7 +41721,7 @@
         <v>46204</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -41794,7 +41794,7 @@
         <v>46204</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -41867,7 +41867,7 @@
         <v>46204</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -41940,7 +41940,7 @@
         <v>46204</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42013,7 +42013,7 @@
         <v>46206</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42086,7 +42086,7 @@
         <v>46216</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42164,7 +42164,7 @@
         <v>46216</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42242,7 +42242,7 @@
         <v>46216</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42320,7 +42320,7 @@
         <v>46216</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42398,7 +42398,7 @@
         <v>46216</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -42476,7 +42476,7 @@
         <v>46216</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -42554,7 +42554,7 @@
         <v>46268</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -42627,7 +42627,7 @@
         <v>46267</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -42700,7 +42700,7 @@
         <v>46227</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -42773,7 +42773,7 @@
         <v>46226</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -42846,7 +42846,7 @@
         <v>46227</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -42919,7 +42919,7 @@
         <v>46226</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -42992,7 +42992,7 @@
         <v>46226</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43065,7 +43065,7 @@
         <v>46280</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43138,7 +43138,7 @@
         <v>46279</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43211,7 +43211,7 @@
         <v>46234</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43289,7 +43289,7 @@
         <v>46240</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43367,7 +43367,7 @@
         <v>46240</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43445,7 +43445,7 @@
         <v>46240</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -43523,7 +43523,7 @@
         <v>46287</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -43596,7 +43596,7 @@
         <v>46092</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -43669,7 +43669,7 @@
         <v>46287</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -43742,7 +43742,7 @@
         <v>45911</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -43815,7 +43815,7 @@
         <v>46066</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -43888,7 +43888,7 @@
         <v>46245</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -43961,7 +43961,7 @@
         <v>46283</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44034,7 +44034,7 @@
         <v>46287</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44107,7 +44107,7 @@
         <v>46245</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44180,7 +44180,7 @@
         <v>46247</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44253,7 +44253,7 @@
         <v>46168</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44326,7 +44326,7 @@
         <v>46247</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44399,7 +44399,7 @@
         <v>46154</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44472,7 +44472,7 @@
         <v>46246</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -44545,7 +44545,7 @@
         <v>46287</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -44618,7 +44618,7 @@
         <v>46287</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -44691,7 +44691,7 @@
         <v>46290</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -44764,7 +44764,7 @@
         <v>46030</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -44837,7 +44837,7 @@
         <v>46290</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -44910,7 +44910,7 @@
         <v>46287</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -44983,7 +44983,7 @@
         <v>45916</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45056,7 +45056,7 @@
         <v>46248</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45129,7 +45129,7 @@
         <v>46294</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45202,7 +45202,7 @@
         <v>46294</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45275,7 +45275,7 @@
         <v>46294</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45348,7 +45348,7 @@
         <v>46293</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45426,7 +45426,7 @@
         <v>46251</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -45504,7 +45504,7 @@
         <v>46248</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -45577,7 +45577,7 @@
         <v>46251</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -45650,7 +45650,7 @@
         <v>46295</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -45723,7 +45723,7 @@
         <v>46295</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -45796,7 +45796,7 @@
         <v>46251</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -45869,7 +45869,7 @@
         <v>46300</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -45942,7 +45942,7 @@
         <v>46257</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46015,7 +46015,7 @@
         <v>45612</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46088,7 +46088,7 @@
         <v>45612</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46161,7 +46161,7 @@
         <v>46254</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46234,7 +46234,7 @@
         <v>46254</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46307,7 +46307,7 @@
         <v>46155</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46380,7 +46380,7 @@
         <v>46258</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -46453,7 +46453,7 @@
         <v>46302</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -46526,7 +46526,7 @@
         <v>46258</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -46599,7 +46599,7 @@
         <v>46303</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -46672,7 +46672,7 @@
         <v>46261</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -46745,7 +46745,7 @@
         <v>46262</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -46818,7 +46818,7 @@
         <v>46303</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -46891,7 +46891,7 @@
         <v>44634</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -46964,7 +46964,7 @@
         <v>44658</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47037,7 +47037,7 @@
         <v>44621</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47110,7 +47110,7 @@
         <v>44607</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47183,7 +47183,7 @@
         <v>44733</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47261,7 +47261,7 @@
         <v>45302</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -47334,7 +47334,7 @@
         <v>45476</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -47407,7 +47407,7 @@
         <v>45649</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -47480,7 +47480,7 @@
         <v>45728</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -47553,7 +47553,7 @@
         <v>45953</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -47626,7 +47626,7 @@
         <v>45967</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -47699,7 +47699,7 @@
         <v>46010</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -47772,7 +47772,7 @@
         <v>46010</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -47845,7 +47845,7 @@
         <v>46029</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -47923,7 +47923,7 @@
         <v>46079</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -47996,7 +47996,7 @@
         <v>46094</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48069,7 +48069,7 @@
         <v>46119</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48142,7 +48142,7 @@
         <v>46182</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>

--- a/Översikt ÄLMHULT.xlsx
+++ b/Översikt ÄLMHULT.xlsx
@@ -601,7 +601,7 @@
         <v>46209</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>45786</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
         <v>46041</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
         <v>45945</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>44883</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>45215</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>45645</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>46211</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>44883</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         <v>45183</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>44830</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>45012</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
         <v>45818</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2021,7 +2021,7 @@
         <v>44889</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>46171</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>45050</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>45908</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2454,7 +2454,7 @@
         <v>45386</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2559,7 +2559,7 @@
         <v>45280</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
         <v>45560</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2773,7 +2773,7 @@
         <v>45631</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2878,7 +2878,7 @@
         <v>45218</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2983,7 +2983,7 @@
         <v>45932</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3092,7 +3092,7 @@
         <v>44882</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
         <v>45719</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3302,7 +3302,7 @@
         <v>45763</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3407,7 +3407,7 @@
         <v>45856</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3516,7 +3516,7 @@
         <v>45769</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3621,7 +3621,7 @@
         <v>46204</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3726,7 +3726,7 @@
         <v>46290</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3831,7 +3831,7 @@
         <v>45888</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3936,7 +3936,7 @@
         <v>44869</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4041,7 +4041,7 @@
         <v>45786</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4146,7 +4146,7 @@
         <v>46043</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4251,7 +4251,7 @@
         <v>44609</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4324,7 +4324,7 @@
         <v>44525</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4397,7 +4397,7 @@
         <v>44785</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4470,7 +4470,7 @@
         <v>44785</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4543,7 +4543,7 @@
         <v>44785</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4616,7 +4616,7 @@
         <v>44515</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4689,7 +4689,7 @@
         <v>44785</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4762,7 +4762,7 @@
         <v>44802</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4835,7 +4835,7 @@
         <v>44802</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4908,7 +4908,7 @@
         <v>44749</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4981,7 +4981,7 @@
         <v>44798</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5054,7 +5054,7 @@
         <v>44523</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5127,7 +5127,7 @@
         <v>44503</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5200,7 +5200,7 @@
         <v>44503</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5273,7 +5273,7 @@
         <v>44785</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5346,7 +5346,7 @@
         <v>44665</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5424,7 +5424,7 @@
         <v>44846</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5497,7 +5497,7 @@
         <v>44847</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5570,7 +5570,7 @@
         <v>44498</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5643,7 +5643,7 @@
         <v>44690</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5716,7 +5716,7 @@
         <v>44812</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5789,7 +5789,7 @@
         <v>44504</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5862,7 +5862,7 @@
         <v>44602</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5935,7 +5935,7 @@
         <v>44690</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6008,7 +6008,7 @@
         <v>44690</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         <v>44509</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6154,7 +6154,7 @@
         <v>44643</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6227,7 +6227,7 @@
         <v>44596</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6300,7 +6300,7 @@
         <v>44865</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6373,7 +6373,7 @@
         <v>44739</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6446,7 +6446,7 @@
         <v>44510</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6519,7 +6519,7 @@
         <v>44522</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6592,7 +6592,7 @@
         <v>44551</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6665,7 +6665,7 @@
         <v>44512</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6738,7 +6738,7 @@
         <v>44733</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6811,7 +6811,7 @@
         <v>44621</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6884,7 +6884,7 @@
         <v>44496</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6957,7 +6957,7 @@
         <v>44609</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7030,7 +7030,7 @@
         <v>44721</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7103,7 +7103,7 @@
         <v>44525</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7176,7 +7176,7 @@
         <v>44685</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7249,7 +7249,7 @@
         <v>44621</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7322,7 +7322,7 @@
         <v>44854</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7395,7 +7395,7 @@
         <v>44487</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7468,7 +7468,7 @@
         <v>44721</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7541,7 +7541,7 @@
         <v>44636</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7614,7 +7614,7 @@
         <v>44854</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7687,7 +7687,7 @@
         <v>44680</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7760,7 +7760,7 @@
         <v>44587</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7838,7 +7838,7 @@
         <v>44524</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7911,7 +7911,7 @@
         <v>44802</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7984,7 +7984,7 @@
         <v>44529</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8057,7 +8057,7 @@
         <v>44657</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8130,7 +8130,7 @@
         <v>44831</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8203,7 +8203,7 @@
         <v>44831</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8276,7 +8276,7 @@
         <v>45061</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8349,7 +8349,7 @@
         <v>45638</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8422,7 +8422,7 @@
         <v>45090</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8495,7 +8495,7 @@
         <v>45133</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8568,7 +8568,7 @@
         <v>44882</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8641,7 +8641,7 @@
         <v>45467</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8714,7 +8714,7 @@
         <v>44491</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         <v>45638</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8860,7 +8860,7 @@
         <v>44897</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8933,7 +8933,7 @@
         <v>45090</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9006,7 +9006,7 @@
         <v>44816</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9079,7 +9079,7 @@
         <v>45612</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9152,7 +9152,7 @@
         <v>45440</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9225,7 +9225,7 @@
         <v>45051</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9298,7 +9298,7 @@
         <v>45078</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9371,7 +9371,7 @@
         <v>45078</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9444,7 +9444,7 @@
         <v>45215</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9517,7 +9517,7 @@
         <v>44858</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9590,7 +9590,7 @@
         <v>44942</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9663,7 +9663,7 @@
         <v>45222</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9736,7 +9736,7 @@
         <v>45222</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9809,7 +9809,7 @@
         <v>45374</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9882,7 +9882,7 @@
         <v>45268</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9955,7 +9955,7 @@
         <v>45716</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10028,7 +10028,7 @@
         <v>45497</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10101,7 +10101,7 @@
         <v>45433</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10174,7 +10174,7 @@
         <v>44897</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10247,7 +10247,7 @@
         <v>45737</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10320,7 +10320,7 @@
         <v>45700</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10393,7 +10393,7 @@
         <v>45653</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10466,7 +10466,7 @@
         <v>45254</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10539,7 +10539,7 @@
         <v>44942</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10612,7 +10612,7 @@
         <v>45103</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10685,7 +10685,7 @@
         <v>45303</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10758,7 +10758,7 @@
         <v>45251</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10831,7 +10831,7 @@
         <v>45251</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10904,7 +10904,7 @@
         <v>45539</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10977,7 +10977,7 @@
         <v>45211</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11050,7 +11050,7 @@
         <v>45010</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11123,7 +11123,7 @@
         <v>45049</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11196,7 +11196,7 @@
         <v>45217</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11269,7 +11269,7 @@
         <v>44508</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11342,7 +11342,7 @@
         <v>45707</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11415,7 +11415,7 @@
         <v>45595</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11488,7 +11488,7 @@
         <v>45457</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11561,7 +11561,7 @@
         <v>44853</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11634,7 +11634,7 @@
         <v>45566</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11707,7 +11707,7 @@
         <v>45384</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11780,7 +11780,7 @@
         <v>45271</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11853,7 +11853,7 @@
         <v>45547</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11926,7 +11926,7 @@
         <v>45317</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11999,7 +11999,7 @@
         <v>45529</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12072,7 +12072,7 @@
         <v>44986</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12150,7 +12150,7 @@
         <v>45211</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12223,7 +12223,7 @@
         <v>45089</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12296,7 +12296,7 @@
         <v>45251</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12369,7 +12369,7 @@
         <v>45244</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12442,7 +12442,7 @@
         <v>45001</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12515,7 +12515,7 @@
         <v>45348</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12588,7 +12588,7 @@
         <v>45228</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12661,7 +12661,7 @@
         <v>45252</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12734,7 +12734,7 @@
         <v>44922</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12807,7 +12807,7 @@
         <v>45401</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12880,7 +12880,7 @@
         <v>45352</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12958,7 +12958,7 @@
         <v>45680</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13031,7 +13031,7 @@
         <v>44865</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13104,7 +13104,7 @@
         <v>44855</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13177,7 +13177,7 @@
         <v>45309</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13250,7 +13250,7 @@
         <v>44897</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13323,7 +13323,7 @@
         <v>45215</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13396,7 +13396,7 @@
         <v>44935</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13469,7 +13469,7 @@
         <v>45303</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13542,7 +13542,7 @@
         <v>44992</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13615,7 +13615,7 @@
         <v>45286</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13688,7 +13688,7 @@
         <v>45533</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13761,7 +13761,7 @@
         <v>44962</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13834,7 +13834,7 @@
         <v>44973</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13907,7 +13907,7 @@
         <v>44998</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13985,7 +13985,7 @@
         <v>45211</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14058,7 +14058,7 @@
         <v>45457</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14131,7 +14131,7 @@
         <v>45457</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14204,7 +14204,7 @@
         <v>45140</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14277,7 +14277,7 @@
         <v>45589</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14350,7 +14350,7 @@
         <v>45884</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14423,7 +14423,7 @@
         <v>45103</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14496,7 +14496,7 @@
         <v>44777</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14569,7 +14569,7 @@
         <v>45352</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14647,7 +14647,7 @@
         <v>45888</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14720,7 +14720,7 @@
         <v>44582</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14793,7 +14793,7 @@
         <v>45653</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14866,7 +14866,7 @@
         <v>45887</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14939,7 +14939,7 @@
         <v>44942</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15012,7 +15012,7 @@
         <v>45181</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15085,7 +15085,7 @@
         <v>45637</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15158,7 +15158,7 @@
         <v>45706</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15231,7 +15231,7 @@
         <v>45092</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15304,7 +15304,7 @@
         <v>45006</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15382,7 +15382,7 @@
         <v>45092</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15455,7 +15455,7 @@
         <v>45443</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15528,7 +15528,7 @@
         <v>45734</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15601,7 +15601,7 @@
         <v>45113</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15674,7 +15674,7 @@
         <v>45166</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15747,7 +15747,7 @@
         <v>44545</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15820,7 +15820,7 @@
         <v>45376</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15893,7 +15893,7 @@
         <v>44942</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15966,7 +15966,7 @@
         <v>45015</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16039,7 +16039,7 @@
         <v>45169</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16112,7 +16112,7 @@
         <v>44543</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16185,7 +16185,7 @@
         <v>44943</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16258,7 +16258,7 @@
         <v>45155</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16331,7 +16331,7 @@
         <v>44921</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16404,7 +16404,7 @@
         <v>45450</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16477,7 +16477,7 @@
         <v>45378</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16550,7 +16550,7 @@
         <v>44817</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16623,7 +16623,7 @@
         <v>45898</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16696,7 +16696,7 @@
         <v>45897</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16769,7 +16769,7 @@
         <v>45759</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16842,7 +16842,7 @@
         <v>45314</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16915,7 +16915,7 @@
         <v>44930</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16988,7 +16988,7 @@
         <v>45589</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17061,7 +17061,7 @@
         <v>45373</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17139,7 +17139,7 @@
         <v>45373</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17217,7 +17217,7 @@
         <v>45435</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17290,7 +17290,7 @@
         <v>45435</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17363,7 +17363,7 @@
         <v>45748</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17436,7 +17436,7 @@
         <v>45435</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17509,7 +17509,7 @@
         <v>44853</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17582,7 +17582,7 @@
         <v>44523</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17655,7 +17655,7 @@
         <v>44994</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17728,7 +17728,7 @@
         <v>44994</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17801,7 +17801,7 @@
         <v>44531</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17874,7 +17874,7 @@
         <v>45373</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17952,7 +17952,7 @@
         <v>45567</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18025,7 +18025,7 @@
         <v>45586</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18098,7 +18098,7 @@
         <v>44911</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18171,7 +18171,7 @@
         <v>45538</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18244,7 +18244,7 @@
         <v>45315</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18317,7 +18317,7 @@
         <v>44928</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18390,7 +18390,7 @@
         <v>45209</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18463,7 +18463,7 @@
         <v>45615</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18536,7 +18536,7 @@
         <v>44958</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18609,7 +18609,7 @@
         <v>45098</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18702,7 +18702,7 @@
         <v>45680</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18775,7 +18775,7 @@
         <v>45663</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18848,7 +18848,7 @@
         <v>45175</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18921,7 +18921,7 @@
         <v>44503</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18994,7 +18994,7 @@
         <v>45776</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19067,7 +19067,7 @@
         <v>44859</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19140,7 +19140,7 @@
         <v>44914</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19213,7 +19213,7 @@
         <v>45781</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19286,7 +19286,7 @@
         <v>45574</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19359,7 +19359,7 @@
         <v>45559</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19432,7 +19432,7 @@
         <v>45624</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19505,7 +19505,7 @@
         <v>45608</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19578,7 +19578,7 @@
         <v>45916</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19651,7 +19651,7 @@
         <v>45915</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19729,7 +19729,7 @@
         <v>45156</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19802,7 +19802,7 @@
         <v>45558</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19875,7 +19875,7 @@
         <v>45539</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19948,7 +19948,7 @@
         <v>45638</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20021,7 +20021,7 @@
         <v>45407</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20094,7 +20094,7 @@
         <v>45133</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20167,7 +20167,7 @@
         <v>45917</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20245,7 +20245,7 @@
         <v>45917</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20323,7 +20323,7 @@
         <v>45527</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20396,7 +20396,7 @@
         <v>45719</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20469,7 +20469,7 @@
         <v>45355</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20542,7 +20542,7 @@
         <v>45355</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20620,7 +20620,7 @@
         <v>44979</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20693,7 +20693,7 @@
         <v>45917</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20771,7 +20771,7 @@
         <v>45681</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20844,7 +20844,7 @@
         <v>45189</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20917,7 +20917,7 @@
         <v>45010</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20990,7 +20990,7 @@
         <v>45539</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21063,7 +21063,7 @@
         <v>45355</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21141,7 +21141,7 @@
         <v>45687</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21214,7 +21214,7 @@
         <v>45543</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21287,7 +21287,7 @@
         <v>45513</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21360,7 +21360,7 @@
         <v>45929</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21433,7 +21433,7 @@
         <v>45720</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21506,7 +21506,7 @@
         <v>45462</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21579,7 +21579,7 @@
         <v>45554</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21652,7 +21652,7 @@
         <v>45564</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21725,7 +21725,7 @@
         <v>45930</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21798,7 +21798,7 @@
         <v>45254</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21871,7 +21871,7 @@
         <v>45049</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21944,7 +21944,7 @@
         <v>44994</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22017,7 +22017,7 @@
         <v>45930</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22090,7 +22090,7 @@
         <v>45706</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22163,7 +22163,7 @@
         <v>45589</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22236,7 +22236,7 @@
         <v>45799</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22309,7 +22309,7 @@
         <v>45282</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22382,7 +22382,7 @@
         <v>44686</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22455,7 +22455,7 @@
         <v>45460</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22528,7 +22528,7 @@
         <v>45350</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22601,7 +22601,7 @@
         <v>45405</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22674,7 +22674,7 @@
         <v>45702</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22747,7 +22747,7 @@
         <v>45663</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22820,7 +22820,7 @@
         <v>45616</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22893,7 +22893,7 @@
         <v>44636</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22966,7 +22966,7 @@
         <v>44511</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23039,7 +23039,7 @@
         <v>44511</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23112,7 +23112,7 @@
         <v>45446</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23185,7 +23185,7 @@
         <v>45804</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23258,7 +23258,7 @@
         <v>45191</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23331,7 +23331,7 @@
         <v>45716</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23409,7 +23409,7 @@
         <v>44531</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23482,7 +23482,7 @@
         <v>44587</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23555,7 +23555,7 @@
         <v>45062</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23628,7 +23628,7 @@
         <v>45677</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23701,7 +23701,7 @@
         <v>45170</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23774,7 +23774,7 @@
         <v>45944</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23847,7 +23847,7 @@
         <v>45222</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23920,7 +23920,7 @@
         <v>44592</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23993,7 +23993,7 @@
         <v>45594</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24066,7 +24066,7 @@
         <v>45215</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24139,7 +24139,7 @@
         <v>45588</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24212,7 +24212,7 @@
         <v>45945</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24285,7 +24285,7 @@
         <v>45462</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24358,7 +24358,7 @@
         <v>45258</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24431,7 +24431,7 @@
         <v>45653</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24504,7 +24504,7 @@
         <v>45548</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24577,7 +24577,7 @@
         <v>44859</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24650,7 +24650,7 @@
         <v>45818</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24723,7 +24723,7 @@
         <v>45695</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24796,7 +24796,7 @@
         <v>44634</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24869,7 +24869,7 @@
         <v>44861</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24942,7 +24942,7 @@
         <v>45625</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25015,7 +25015,7 @@
         <v>45716</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25088,7 +25088,7 @@
         <v>44698</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25161,7 +25161,7 @@
         <v>45771</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25234,7 +25234,7 @@
         <v>45578</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25307,7 +25307,7 @@
         <v>45308</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25380,7 +25380,7 @@
         <v>45947</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25453,7 +25453,7 @@
         <v>45372</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25526,7 +25526,7 @@
         <v>45240</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25604,7 +25604,7 @@
         <v>45629</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25677,7 +25677,7 @@
         <v>45166</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25750,7 +25750,7 @@
         <v>45916</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25828,7 +25828,7 @@
         <v>45335</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25901,7 +25901,7 @@
         <v>45441</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -25974,7 +25974,7 @@
         <v>45334</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26047,7 +26047,7 @@
         <v>45460</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26120,7 +26120,7 @@
         <v>45693</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26193,7 +26193,7 @@
         <v>45698</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26266,7 +26266,7 @@
         <v>45952</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26339,7 +26339,7 @@
         <v>45959</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26412,7 +26412,7 @@
         <v>45202</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26485,7 +26485,7 @@
         <v>45180</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26558,7 +26558,7 @@
         <v>45145</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26631,7 +26631,7 @@
         <v>45834</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26704,7 +26704,7 @@
         <v>45211</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26777,7 +26777,7 @@
         <v>45214</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26850,7 +26850,7 @@
         <v>45835</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -26923,7 +26923,7 @@
         <v>45175</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -26996,7 +26996,7 @@
         <v>45175</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27069,7 +27069,7 @@
         <v>45680</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27142,7 +27142,7 @@
         <v>44641</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27215,7 +27215,7 @@
         <v>45187</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27288,7 +27288,7 @@
         <v>45966</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27361,7 +27361,7 @@
         <v>45839</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27434,7 +27434,7 @@
         <v>45469</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27512,7 +27512,7 @@
         <v>45966</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27585,7 +27585,7 @@
         <v>45078</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27658,7 +27658,7 @@
         <v>45715</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27731,7 +27731,7 @@
         <v>45966</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27804,7 +27804,7 @@
         <v>45681</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -27877,7 +27877,7 @@
         <v>45842</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -27950,7 +27950,7 @@
         <v>45967</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28023,7 +28023,7 @@
         <v>45233</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28096,7 +28096,7 @@
         <v>45233</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28169,7 +28169,7 @@
         <v>45631</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28242,7 +28242,7 @@
         <v>45842</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28315,7 +28315,7 @@
         <v>45051</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28388,7 +28388,7 @@
         <v>45154</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28461,7 +28461,7 @@
         <v>45842</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28534,7 +28534,7 @@
         <v>45841</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28607,7 +28607,7 @@
         <v>45529</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28680,7 +28680,7 @@
         <v>45969</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -28753,7 +28753,7 @@
         <v>45969</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -28826,7 +28826,7 @@
         <v>45846</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -28899,7 +28899,7 @@
         <v>45845</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -28972,7 +28972,7 @@
         <v>44760</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29045,7 +29045,7 @@
         <v>45610</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29118,7 +29118,7 @@
         <v>44526</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29191,7 +29191,7 @@
         <v>45612</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29264,7 +29264,7 @@
         <v>45770</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29337,7 +29337,7 @@
         <v>45076</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29410,7 +29410,7 @@
         <v>45076</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29483,7 +29483,7 @@
         <v>45726</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29556,7 +29556,7 @@
         <v>45726</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -29629,7 +29629,7 @@
         <v>45854</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -29702,7 +29702,7 @@
         <v>45763</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -29775,7 +29775,7 @@
         <v>45763</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -29848,7 +29848,7 @@
         <v>45581</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -29921,7 +29921,7 @@
         <v>45246</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -29994,7 +29994,7 @@
         <v>45819</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30067,7 +30067,7 @@
         <v>44979</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30140,7 +30140,7 @@
         <v>45812</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30213,7 +30213,7 @@
         <v>45679</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30286,7 +30286,7 @@
         <v>45631</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30359,7 +30359,7 @@
         <v>45531</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30432,7 +30432,7 @@
         <v>44826</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30505,7 +30505,7 @@
         <v>45352</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30583,7 +30583,7 @@
         <v>45062</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -30656,7 +30656,7 @@
         <v>45726</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -30729,7 +30729,7 @@
         <v>44496</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -30802,7 +30802,7 @@
         <v>45867</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -30875,7 +30875,7 @@
         <v>45581</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -30948,7 +30948,7 @@
         <v>44568</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31021,7 +31021,7 @@
         <v>45250</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31094,7 +31094,7 @@
         <v>45250</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31167,7 +31167,7 @@
         <v>45253</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31240,7 +31240,7 @@
         <v>45748</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31313,7 +31313,7 @@
         <v>45421</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31386,7 +31386,7 @@
         <v>45716</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31464,7 +31464,7 @@
         <v>45211</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31537,7 +31537,7 @@
         <v>45176</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -31610,7 +31610,7 @@
         <v>44784</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -31688,7 +31688,7 @@
         <v>45348</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -31761,7 +31761,7 @@
         <v>45476</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -31834,7 +31834,7 @@
         <v>45244</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -31907,7 +31907,7 @@
         <v>45084</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -31980,7 +31980,7 @@
         <v>44496</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32053,7 +32053,7 @@
         <v>45735</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32126,7 +32126,7 @@
         <v>45735</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32199,7 +32199,7 @@
         <v>45051</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32272,7 +32272,7 @@
         <v>45273</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32345,7 +32345,7 @@
         <v>45273</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32418,7 +32418,7 @@
         <v>45268</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32491,7 +32491,7 @@
         <v>46105</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -32569,7 +32569,7 @@
         <v>46105</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -32647,7 +32647,7 @@
         <v>46105</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -32725,7 +32725,7 @@
         <v>44865</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -32798,7 +32798,7 @@
         <v>46105</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -32876,7 +32876,7 @@
         <v>46105</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -32954,7 +32954,7 @@
         <v>45469</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33027,7 +33027,7 @@
         <v>45986</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33105,7 +33105,7 @@
         <v>46105</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33183,7 +33183,7 @@
         <v>46105</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33261,7 +33261,7 @@
         <v>46107</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33334,7 +33334,7 @@
         <v>45175</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33407,7 +33407,7 @@
         <v>44876</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33480,7 +33480,7 @@
         <v>46106</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33558,7 +33558,7 @@
         <v>45440</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -33631,7 +33631,7 @@
         <v>46108</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -33704,7 +33704,7 @@
         <v>45078</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -33777,7 +33777,7 @@
         <v>45113</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -33850,7 +33850,7 @@
         <v>46108</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -33923,7 +33923,7 @@
         <v>45992</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34001,7 +34001,7 @@
         <v>45992</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34079,7 +34079,7 @@
         <v>45992</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34157,7 +34157,7 @@
         <v>45992</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34235,7 +34235,7 @@
         <v>45180</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34308,7 +34308,7 @@
         <v>44921</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34381,7 +34381,7 @@
         <v>45734</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34454,7 +34454,7 @@
         <v>45583</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34527,7 +34527,7 @@
         <v>45608</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -34600,7 +34600,7 @@
         <v>45546</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -34673,7 +34673,7 @@
         <v>44621</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -34746,7 +34746,7 @@
         <v>46125</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -34819,7 +34819,7 @@
         <v>46000</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -34897,7 +34897,7 @@
         <v>46128</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -34970,7 +34970,7 @@
         <v>44858</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35043,7 +35043,7 @@
         <v>45187</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35116,7 +35116,7 @@
         <v>45412</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35189,7 +35189,7 @@
         <v>45414</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35262,7 +35262,7 @@
         <v>44992</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35335,7 +35335,7 @@
         <v>44610</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35408,7 +35408,7 @@
         <v>46005</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35481,7 +35481,7 @@
         <v>44992</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -35554,7 +35554,7 @@
         <v>45575</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -35627,7 +35627,7 @@
         <v>45167</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -35700,7 +35700,7 @@
         <v>44942</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -35773,7 +35773,7 @@
         <v>45085</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -35846,7 +35846,7 @@
         <v>45938</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -35919,7 +35919,7 @@
         <v>44942</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -35992,7 +35992,7 @@
         <v>45722</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36065,7 +36065,7 @@
         <v>44860</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36138,7 +36138,7 @@
         <v>45187</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36211,7 +36211,7 @@
         <v>45290</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36284,7 +36284,7 @@
         <v>45609</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36357,7 +36357,7 @@
         <v>45217</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36430,7 +36430,7 @@
         <v>45244</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36503,7 +36503,7 @@
         <v>45835</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -36576,7 +36576,7 @@
         <v>45111</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -36649,7 +36649,7 @@
         <v>45531</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -36727,7 +36727,7 @@
         <v>45812</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -36800,7 +36800,7 @@
         <v>44526</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -36873,7 +36873,7 @@
         <v>45141</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -36946,7 +36946,7 @@
         <v>45359</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37019,7 +37019,7 @@
         <v>46016</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37092,7 +37092,7 @@
         <v>45911</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37165,7 +37165,7 @@
         <v>45887</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37238,7 +37238,7 @@
         <v>45883</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37311,7 +37311,7 @@
         <v>45012</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37384,7 +37384,7 @@
         <v>45817</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -37457,7 +37457,7 @@
         <v>45733</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -37530,7 +37530,7 @@
         <v>44687</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -37603,7 +37603,7 @@
         <v>45081</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -37676,7 +37676,7 @@
         <v>45537</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -37749,7 +37749,7 @@
         <v>45531</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -37822,7 +37822,7 @@
         <v>45068</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -37895,7 +37895,7 @@
         <v>46000</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -37973,7 +37973,7 @@
         <v>45328</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38046,7 +38046,7 @@
         <v>45010</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38119,7 +38119,7 @@
         <v>46035</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38192,7 +38192,7 @@
         <v>45048</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38265,7 +38265,7 @@
         <v>46038</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38338,7 +38338,7 @@
         <v>46037</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38411,7 +38411,7 @@
         <v>45177</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -38484,7 +38484,7 @@
         <v>45042</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -38557,7 +38557,7 @@
         <v>45273</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -38630,7 +38630,7 @@
         <v>45930</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -38703,7 +38703,7 @@
         <v>45630</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -38776,7 +38776,7 @@
         <v>45391</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -38849,7 +38849,7 @@
         <v>45134</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -38922,7 +38922,7 @@
         <v>44743</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -38995,7 +38995,7 @@
         <v>45469</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39073,7 +39073,7 @@
         <v>46045</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39146,7 +39146,7 @@
         <v>44977</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39219,7 +39219,7 @@
         <v>45373</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39297,7 +39297,7 @@
         <v>45373</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39375,7 +39375,7 @@
         <v>45628</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39448,7 +39448,7 @@
         <v>45311</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -39521,7 +39521,7 @@
         <v>46052</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -39594,7 +39594,7 @@
         <v>46052</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -39667,7 +39667,7 @@
         <v>46140</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -39745,7 +39745,7 @@
         <v>46061</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -39818,7 +39818,7 @@
         <v>46063</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -39891,7 +39891,7 @@
         <v>46065</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -39964,7 +39964,7 @@
         <v>46147</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40037,7 +40037,7 @@
         <v>46141</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40110,7 +40110,7 @@
         <v>46076</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40183,7 +40183,7 @@
         <v>45827</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40256,7 +40256,7 @@
         <v>46155</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40329,7 +40329,7 @@
         <v>46076</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40402,7 +40402,7 @@
         <v>46093</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -40475,7 +40475,7 @@
         <v>45818</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -40548,7 +40548,7 @@
         <v>45728</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -40621,7 +40621,7 @@
         <v>45946</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -40694,7 +40694,7 @@
         <v>45911</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -40767,7 +40767,7 @@
         <v>46184</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -40840,7 +40840,7 @@
         <v>46184</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -40913,7 +40913,7 @@
         <v>45792</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -40986,7 +40986,7 @@
         <v>46190</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41064,7 +41064,7 @@
         <v>46198</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41137,7 +41137,7 @@
         <v>46198</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41210,7 +41210,7 @@
         <v>46198</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41283,7 +41283,7 @@
         <v>46198</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41356,7 +41356,7 @@
         <v>46202</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41429,7 +41429,7 @@
         <v>46204</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -41502,7 +41502,7 @@
         <v>46204</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -41575,7 +41575,7 @@
         <v>46204</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -41648,7 +41648,7 @@
         <v>46206</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -41721,7 +41721,7 @@
         <v>46204</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -41794,7 +41794,7 @@
         <v>46204</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -41867,7 +41867,7 @@
         <v>46204</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -41940,7 +41940,7 @@
         <v>46204</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42013,7 +42013,7 @@
         <v>46206</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42086,7 +42086,7 @@
         <v>46216</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42164,7 +42164,7 @@
         <v>46216</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42242,7 +42242,7 @@
         <v>46216</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42320,7 +42320,7 @@
         <v>46216</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42398,7 +42398,7 @@
         <v>46216</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -42476,7 +42476,7 @@
         <v>46216</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -42554,7 +42554,7 @@
         <v>46268</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -42627,7 +42627,7 @@
         <v>46267</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -42700,7 +42700,7 @@
         <v>46227</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -42773,7 +42773,7 @@
         <v>46226</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -42846,7 +42846,7 @@
         <v>46227</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -42919,7 +42919,7 @@
         <v>46226</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -42992,7 +42992,7 @@
         <v>46226</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43065,7 +43065,7 @@
         <v>46280</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43138,7 +43138,7 @@
         <v>46279</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43211,7 +43211,7 @@
         <v>46234</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43289,7 +43289,7 @@
         <v>46240</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43367,7 +43367,7 @@
         <v>46240</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43445,7 +43445,7 @@
         <v>46240</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -43523,7 +43523,7 @@
         <v>46287</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -43596,7 +43596,7 @@
         <v>46092</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -43669,7 +43669,7 @@
         <v>46287</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -43742,7 +43742,7 @@
         <v>45911</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -43815,7 +43815,7 @@
         <v>46066</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -43888,7 +43888,7 @@
         <v>46245</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -43961,7 +43961,7 @@
         <v>46283</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44034,7 +44034,7 @@
         <v>46287</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44107,7 +44107,7 @@
         <v>46245</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44180,7 +44180,7 @@
         <v>46247</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44253,7 +44253,7 @@
         <v>46168</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44326,7 +44326,7 @@
         <v>46247</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44399,7 +44399,7 @@
         <v>46154</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44472,7 +44472,7 @@
         <v>46246</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -44545,7 +44545,7 @@
         <v>46287</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -44618,7 +44618,7 @@
         <v>46287</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -44691,7 +44691,7 @@
         <v>46290</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -44764,7 +44764,7 @@
         <v>46030</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -44837,7 +44837,7 @@
         <v>46290</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -44910,7 +44910,7 @@
         <v>46287</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -44983,7 +44983,7 @@
         <v>45916</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45056,7 +45056,7 @@
         <v>46248</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45129,7 +45129,7 @@
         <v>46294</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45202,7 +45202,7 @@
         <v>46294</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45275,7 +45275,7 @@
         <v>46294</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45348,7 +45348,7 @@
         <v>46293</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45426,7 +45426,7 @@
         <v>46251</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -45504,7 +45504,7 @@
         <v>46248</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -45577,7 +45577,7 @@
         <v>46251</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -45650,7 +45650,7 @@
         <v>46295</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -45723,7 +45723,7 @@
         <v>46295</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -45796,7 +45796,7 @@
         <v>46251</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -45869,7 +45869,7 @@
         <v>46300</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -45942,7 +45942,7 @@
         <v>46257</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46015,7 +46015,7 @@
         <v>45612</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46088,7 +46088,7 @@
         <v>45612</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46161,7 +46161,7 @@
         <v>46254</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46234,7 +46234,7 @@
         <v>46254</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46307,7 +46307,7 @@
         <v>46155</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46380,7 +46380,7 @@
         <v>46258</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -46453,7 +46453,7 @@
         <v>46302</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -46526,7 +46526,7 @@
         <v>46258</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -46599,7 +46599,7 @@
         <v>46303</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -46672,7 +46672,7 @@
         <v>46261</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -46745,7 +46745,7 @@
         <v>46262</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -46818,7 +46818,7 @@
         <v>46303</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -46891,7 +46891,7 @@
         <v>44634</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -46964,7 +46964,7 @@
         <v>44658</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47037,7 +47037,7 @@
         <v>44621</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47110,7 +47110,7 @@
         <v>44607</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47183,7 +47183,7 @@
         <v>44733</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47261,7 +47261,7 @@
         <v>45302</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -47334,7 +47334,7 @@
         <v>45476</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -47407,7 +47407,7 @@
         <v>45649</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -47480,7 +47480,7 @@
         <v>45728</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -47553,7 +47553,7 @@
         <v>45953</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -47626,7 +47626,7 @@
         <v>45967</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -47699,7 +47699,7 @@
         <v>46010</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -47772,7 +47772,7 @@
         <v>46010</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -47845,7 +47845,7 @@
         <v>46029</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -47923,7 +47923,7 @@
         <v>46079</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -47996,7 +47996,7 @@
         <v>46094</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48069,7 +48069,7 @@
         <v>46119</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48142,7 +48142,7 @@
         <v>46182</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>

--- a/Översikt ÄLMHULT.xlsx
+++ b/Översikt ÄLMHULT.xlsx
@@ -601,7 +601,7 @@
         <v>46209</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>45786</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
         <v>46041</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
         <v>45945</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>44883</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>45215</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>45645</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>46043</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
         <v>46211</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>44889</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>45012</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>45183</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>44830</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2021,7 +2021,7 @@
         <v>44883</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2127,7 +2127,7 @@
         <v>46171</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         <v>45818</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
         <v>45050</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2455,7 +2455,7 @@
         <v>45908</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
         <v>45560</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
         <v>45932</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2779,7 +2779,7 @@
         <v>45631</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
         <v>45218</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2989,7 +2989,7 @@
         <v>45386</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3094,7 +3094,7 @@
         <v>45719</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3199,7 +3199,7 @@
         <v>46204</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3304,7 +3304,7 @@
         <v>44882</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3409,7 +3409,7 @@
         <v>45769</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
         <v>45280</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3619,7 +3619,7 @@
         <v>45888</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3724,7 +3724,7 @@
         <v>46290</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
         <v>45763</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3934,7 +3934,7 @@
         <v>45856</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         <v>44869</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4148,7 +4148,7 @@
         <v>45786</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4253,7 +4253,7 @@
         <v>44609</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4326,7 +4326,7 @@
         <v>44525</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4399,7 +4399,7 @@
         <v>44785</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4472,7 +4472,7 @@
         <v>44785</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4545,7 +4545,7 @@
         <v>44785</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4618,7 +4618,7 @@
         <v>44515</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4691,7 +4691,7 @@
         <v>44802</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4764,7 +4764,7 @@
         <v>44785</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4837,7 +4837,7 @@
         <v>44749</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4910,7 +4910,7 @@
         <v>44802</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4983,7 +4983,7 @@
         <v>44798</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5056,7 +5056,7 @@
         <v>44523</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5129,7 +5129,7 @@
         <v>44503</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5202,7 +5202,7 @@
         <v>44503</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5275,7 +5275,7 @@
         <v>44785</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5348,7 +5348,7 @@
         <v>44665</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5426,7 +5426,7 @@
         <v>44846</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5499,7 +5499,7 @@
         <v>44498</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5572,7 +5572,7 @@
         <v>44847</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5645,7 +5645,7 @@
         <v>44690</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5718,7 +5718,7 @@
         <v>44812</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5791,7 +5791,7 @@
         <v>44504</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5864,7 +5864,7 @@
         <v>44602</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5937,7 +5937,7 @@
         <v>44512</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6010,7 +6010,7 @@
         <v>44621</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6083,7 +6083,7 @@
         <v>44609</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6156,7 +6156,7 @@
         <v>44487</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6229,7 +6229,7 @@
         <v>44721</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6302,7 +6302,7 @@
         <v>44587</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6380,7 +6380,7 @@
         <v>44802</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6453,7 +6453,7 @@
         <v>44509</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6526,7 +6526,7 @@
         <v>44739</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6599,7 +6599,7 @@
         <v>44733</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6672,7 +6672,7 @@
         <v>44551</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6745,7 +6745,7 @@
         <v>44621</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6818,7 +6818,7 @@
         <v>44854</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6891,7 +6891,7 @@
         <v>44854</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6964,7 +6964,7 @@
         <v>44680</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7037,7 +7037,7 @@
         <v>44524</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7110,7 +7110,7 @@
         <v>44690</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7183,7 +7183,7 @@
         <v>44690</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7256,7 +7256,7 @@
         <v>44865</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7329,7 +7329,7 @@
         <v>44496</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7402,7 +7402,7 @@
         <v>44721</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         <v>44525</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7548,7 +7548,7 @@
         <v>44685</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7621,7 +7621,7 @@
         <v>44643</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7694,7 +7694,7 @@
         <v>44596</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7767,7 +7767,7 @@
         <v>44510</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7840,7 +7840,7 @@
         <v>44522</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7913,7 +7913,7 @@
         <v>44636</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7986,7 +7986,7 @@
         <v>44657</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8059,7 +8059,7 @@
         <v>44491</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8132,7 +8132,7 @@
         <v>44831</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8205,7 +8205,7 @@
         <v>44831</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8278,7 +8278,7 @@
         <v>45433</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8351,7 +8351,7 @@
         <v>45209</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8424,7 +8424,7 @@
         <v>45244</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8497,7 +8497,7 @@
         <v>45098</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8590,7 +8590,7 @@
         <v>45062</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8663,7 +8663,7 @@
         <v>45734</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8736,7 +8736,7 @@
         <v>45735</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8809,7 +8809,7 @@
         <v>45735</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8882,7 +8882,7 @@
         <v>45348</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8955,7 +8955,7 @@
         <v>45457</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9028,7 +9028,7 @@
         <v>44496</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9101,7 +9101,7 @@
         <v>45610</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9174,7 +9174,7 @@
         <v>44610</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9247,7 +9247,7 @@
         <v>45469</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9320,7 +9320,7 @@
         <v>44826</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9393,7 +9393,7 @@
         <v>44962</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9466,7 +9466,7 @@
         <v>45543</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9539,7 +9539,7 @@
         <v>45254</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9612,7 +9612,7 @@
         <v>45578</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9685,7 +9685,7 @@
         <v>45554</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9758,7 +9758,7 @@
         <v>45133</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9831,7 +9831,7 @@
         <v>45575</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9904,7 +9904,7 @@
         <v>45359</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9977,7 +9977,7 @@
         <v>45457</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10050,7 +10050,7 @@
         <v>45457</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10123,7 +10123,7 @@
         <v>45133</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10196,7 +10196,7 @@
         <v>45175</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10269,7 +10269,7 @@
         <v>45737</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10342,7 +10342,7 @@
         <v>44496</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10415,7 +10415,7 @@
         <v>45469</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10493,7 +10493,7 @@
         <v>45720</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10566,7 +10566,7 @@
         <v>45566</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10639,7 +10639,7 @@
         <v>45222</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10712,7 +10712,7 @@
         <v>45222</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10785,7 +10785,7 @@
         <v>45049</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10858,7 +10858,7 @@
         <v>45309</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10931,7 +10931,7 @@
         <v>44876</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11004,7 +11004,7 @@
         <v>44686</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11077,7 +11077,7 @@
         <v>44994</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11150,7 +11150,7 @@
         <v>45638</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11223,7 +11223,7 @@
         <v>45638</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11296,7 +11296,7 @@
         <v>45051</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11369,7 +11369,7 @@
         <v>45103</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11442,7 +11442,7 @@
         <v>45187</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11515,7 +11515,7 @@
         <v>44817</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11588,7 +11588,7 @@
         <v>45315</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11661,7 +11661,7 @@
         <v>45240</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11739,7 +11739,7 @@
         <v>45350</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11812,7 +11812,7 @@
         <v>45693</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11885,7 +11885,7 @@
         <v>44853</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11958,7 +11958,7 @@
         <v>45303</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12031,7 +12031,7 @@
         <v>45290</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12104,7 +12104,7 @@
         <v>45443</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12177,7 +12177,7 @@
         <v>44935</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12250,7 +12250,7 @@
         <v>45586</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12323,7 +12323,7 @@
         <v>44979</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12396,7 +12396,7 @@
         <v>45180</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12469,7 +12469,7 @@
         <v>44859</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12542,7 +12542,7 @@
         <v>45015</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12615,7 +12615,7 @@
         <v>45771</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12688,7 +12688,7 @@
         <v>44958</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12761,7 +12761,7 @@
         <v>44861</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12834,7 +12834,7 @@
         <v>45062</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12907,7 +12907,7 @@
         <v>45414</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12980,7 +12980,7 @@
         <v>45460</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13053,7 +13053,7 @@
         <v>45090</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13126,7 +13126,7 @@
         <v>44994</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13199,7 +13199,7 @@
         <v>45681</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13272,7 +13272,7 @@
         <v>44994</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13345,7 +13345,7 @@
         <v>45042</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13418,7 +13418,7 @@
         <v>45680</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13491,7 +13491,7 @@
         <v>44897</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13564,7 +13564,7 @@
         <v>45373</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13642,7 +13642,7 @@
         <v>45715</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13715,7 +13715,7 @@
         <v>44921</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13788,7 +13788,7 @@
         <v>45078</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13861,7 +13861,7 @@
         <v>45145</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13934,7 +13934,7 @@
         <v>45352</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14012,7 +14012,7 @@
         <v>45681</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14085,7 +14085,7 @@
         <v>45068</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14158,7 +14158,7 @@
         <v>45228</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14231,7 +14231,7 @@
         <v>45608</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14304,7 +14304,7 @@
         <v>45258</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14377,7 +14377,7 @@
         <v>44914</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14450,7 +14450,7 @@
         <v>45538</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14523,7 +14523,7 @@
         <v>44743</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14596,7 +14596,7 @@
         <v>44503</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14669,7 +14669,7 @@
         <v>45559</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14742,7 +14742,7 @@
         <v>45167</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14815,7 +14815,7 @@
         <v>45817</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14888,7 +14888,7 @@
         <v>45722</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14961,7 +14961,7 @@
         <v>45547</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15034,7 +15034,7 @@
         <v>45328</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15107,7 +15107,7 @@
         <v>45930</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15180,7 +15180,7 @@
         <v>45630</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15253,7 +15253,7 @@
         <v>45317</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15326,7 +15326,7 @@
         <v>45078</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15399,7 +15399,7 @@
         <v>45078</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15472,7 +15472,7 @@
         <v>45254</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15545,7 +15545,7 @@
         <v>45733</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15618,7 +15618,7 @@
         <v>45286</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15691,7 +15691,7 @@
         <v>44998</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15769,7 +15769,7 @@
         <v>45716</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15842,7 +15842,7 @@
         <v>45537</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15915,7 +15915,7 @@
         <v>45884</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15988,7 +15988,7 @@
         <v>45181</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16061,7 +16061,7 @@
         <v>45716</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16134,7 +16134,7 @@
         <v>45531</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16212,7 +16212,7 @@
         <v>45716</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16290,7 +16290,7 @@
         <v>45887</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16363,7 +16363,7 @@
         <v>45883</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16436,7 +16436,7 @@
         <v>45637</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16509,7 +16509,7 @@
         <v>45911</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16582,7 +16582,7 @@
         <v>45372</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16655,7 +16655,7 @@
         <v>45888</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16728,7 +16728,7 @@
         <v>45251</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16801,7 +16801,7 @@
         <v>45440</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16874,7 +16874,7 @@
         <v>44545</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16947,7 +16947,7 @@
         <v>45887</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17020,7 +17020,7 @@
         <v>45897</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17093,7 +17093,7 @@
         <v>45140</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17166,7 +17166,7 @@
         <v>45531</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17239,7 +17239,7 @@
         <v>45898</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17312,7 +17312,7 @@
         <v>45938</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17385,7 +17385,7 @@
         <v>46140</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17463,7 +17463,7 @@
         <v>45111</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17536,7 +17536,7 @@
         <v>45348</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17609,7 +17609,7 @@
         <v>45233</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17682,7 +17682,7 @@
         <v>45233</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17755,7 +17755,7 @@
         <v>45748</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17828,7 +17828,7 @@
         <v>44523</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17901,7 +17901,7 @@
         <v>45211</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17974,7 +17974,7 @@
         <v>45215</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18047,7 +18047,7 @@
         <v>45629</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18120,7 +18120,7 @@
         <v>45170</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18193,7 +18193,7 @@
         <v>45915</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18271,7 +18271,7 @@
         <v>45917</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18349,7 +18349,7 @@
         <v>45917</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18427,7 +18427,7 @@
         <v>45917</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18505,7 +18505,7 @@
         <v>45252</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18578,7 +18578,7 @@
         <v>45916</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18651,7 +18651,7 @@
         <v>45006</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18729,7 +18729,7 @@
         <v>45089</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18802,7 +18802,7 @@
         <v>45608</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18875,7 +18875,7 @@
         <v>46147</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18948,7 +18948,7 @@
         <v>45734</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19021,7 +19021,7 @@
         <v>45211</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19094,7 +19094,7 @@
         <v>45215</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19167,7 +19167,7 @@
         <v>45376</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19240,7 +19240,7 @@
         <v>45134</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19313,7 +19313,7 @@
         <v>45929</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19386,7 +19386,7 @@
         <v>45930</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19459,7 +19459,7 @@
         <v>45930</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19532,7 +19532,7 @@
         <v>46141</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19605,7 +19605,7 @@
         <v>44784</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19683,7 +19683,7 @@
         <v>45373</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19761,7 +19761,7 @@
         <v>45373</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19839,7 +19839,7 @@
         <v>45084</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19912,7 +19912,7 @@
         <v>45010</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19985,7 +19985,7 @@
         <v>45944</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20058,7 +20058,7 @@
         <v>45945</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20131,7 +20131,7 @@
         <v>46155</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20204,7 +20204,7 @@
         <v>45947</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20277,7 +20277,7 @@
         <v>45631</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20350,7 +20350,7 @@
         <v>45355</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20423,7 +20423,7 @@
         <v>45355</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20501,7 +20501,7 @@
         <v>45916</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20579,7 +20579,7 @@
         <v>45529</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20652,7 +20652,7 @@
         <v>45952</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20725,7 +20725,7 @@
         <v>45959</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20798,7 +20798,7 @@
         <v>44943</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20871,7 +20871,7 @@
         <v>45589</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20944,7 +20944,7 @@
         <v>45010</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21017,7 +21017,7 @@
         <v>45818</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21090,7 +21090,7 @@
         <v>45271</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21163,7 +21163,7 @@
         <v>45966</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21236,7 +21236,7 @@
         <v>45966</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21309,7 +21309,7 @@
         <v>45967</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21382,7 +21382,7 @@
         <v>46076</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21455,7 +21455,7 @@
         <v>45966</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21528,7 +21528,7 @@
         <v>45969</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21601,7 +21601,7 @@
         <v>45969</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21674,7 +21674,7 @@
         <v>45085</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21747,7 +21747,7 @@
         <v>44543</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21820,7 +21820,7 @@
         <v>44865</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21893,7 +21893,7 @@
         <v>45048</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21966,7 +21966,7 @@
         <v>45533</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22039,7 +22039,7 @@
         <v>45001</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22112,7 +22112,7 @@
         <v>45282</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22185,7 +22185,7 @@
         <v>45728</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22258,7 +22258,7 @@
         <v>45273</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22331,7 +22331,7 @@
         <v>45273</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22404,7 +22404,7 @@
         <v>45986</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22482,7 +22482,7 @@
         <v>45706</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22555,7 +22555,7 @@
         <v>45612</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22628,7 +22628,7 @@
         <v>45615</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22701,7 +22701,7 @@
         <v>45250</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22774,7 +22774,7 @@
         <v>45250</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22847,7 +22847,7 @@
         <v>45251</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22920,7 +22920,7 @@
         <v>45546</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22993,7 +22993,7 @@
         <v>45992</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23071,7 +23071,7 @@
         <v>45180</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23144,7 +23144,7 @@
         <v>45992</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23222,7 +23222,7 @@
         <v>45992</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23300,7 +23300,7 @@
         <v>45992</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23378,7 +23378,7 @@
         <v>45539</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23451,7 +23451,7 @@
         <v>45311</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23524,7 +23524,7 @@
         <v>45308</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23597,7 +23597,7 @@
         <v>45384</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23670,7 +23670,7 @@
         <v>45374</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23743,7 +23743,7 @@
         <v>45706</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23816,7 +23816,7 @@
         <v>46000</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23894,7 +23894,7 @@
         <v>45211</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23967,7 +23967,7 @@
         <v>45012</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24040,7 +24040,7 @@
         <v>45314</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24113,7 +24113,7 @@
         <v>45707</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24186,7 +24186,7 @@
         <v>45303</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24259,7 +24259,7 @@
         <v>45653</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24332,7 +24332,7 @@
         <v>45653</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24405,7 +24405,7 @@
         <v>46005</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24478,7 +24478,7 @@
         <v>45187</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24551,7 +24551,7 @@
         <v>45716</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24629,7 +24629,7 @@
         <v>45946</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24702,7 +24702,7 @@
         <v>44973</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24775,7 +24775,7 @@
         <v>44942</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24848,7 +24848,7 @@
         <v>45812</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24921,7 +24921,7 @@
         <v>45700</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24994,7 +24994,7 @@
         <v>45061</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25067,7 +25067,7 @@
         <v>44897</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25140,7 +25140,7 @@
         <v>45911</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25213,7 +25213,7 @@
         <v>46016</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25286,7 +25286,7 @@
         <v>44977</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25359,7 +25359,7 @@
         <v>45628</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25432,7 +25432,7 @@
         <v>45352</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25510,7 +25510,7 @@
         <v>45513</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25583,7 +25583,7 @@
         <v>45166</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25656,7 +25656,7 @@
         <v>45680</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25729,7 +25729,7 @@
         <v>45191</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25802,7 +25802,7 @@
         <v>44853</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25875,7 +25875,7 @@
         <v>45251</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25948,7 +25948,7 @@
         <v>46035</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26021,7 +26021,7 @@
         <v>46037</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26094,7 +26094,7 @@
         <v>45589</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26167,7 +26167,7 @@
         <v>46038</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26240,7 +26240,7 @@
         <v>44855</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26313,7 +26313,7 @@
         <v>44942</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26386,7 +26386,7 @@
         <v>45680</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26459,7 +26459,7 @@
         <v>46045</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26532,7 +26532,7 @@
         <v>45462</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26605,7 +26605,7 @@
         <v>45412</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26678,7 +26678,7 @@
         <v>45113</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26751,7 +26751,7 @@
         <v>45421</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26824,7 +26824,7 @@
         <v>45558</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26897,7 +26897,7 @@
         <v>46052</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -26970,7 +26970,7 @@
         <v>45090</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27043,7 +27043,7 @@
         <v>45567</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27116,7 +27116,7 @@
         <v>46052</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27189,7 +27189,7 @@
         <v>45268</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27262,7 +27262,7 @@
         <v>46184</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27335,7 +27335,7 @@
         <v>46184</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27408,7 +27408,7 @@
         <v>46063</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27481,7 +27481,7 @@
         <v>44930</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27554,7 +27554,7 @@
         <v>46061</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27627,7 +27627,7 @@
         <v>46065</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27700,7 +27700,7 @@
         <v>45698</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27773,7 +27773,7 @@
         <v>45177</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27846,7 +27846,7 @@
         <v>44986</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -27924,7 +27924,7 @@
         <v>46076</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -27997,7 +27997,7 @@
         <v>45175</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28070,7 +28070,7 @@
         <v>45827</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28143,7 +28143,7 @@
         <v>45677</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28216,7 +28216,7 @@
         <v>45462</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28289,7 +28289,7 @@
         <v>45081</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28362,7 +28362,7 @@
         <v>45166</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28435,7 +28435,7 @@
         <v>45595</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28508,7 +28508,7 @@
         <v>44942</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28581,7 +28581,7 @@
         <v>45391</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28654,7 +28654,7 @@
         <v>45373</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28732,7 +28732,7 @@
         <v>45373</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -28810,7 +28810,7 @@
         <v>45155</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -28883,7 +28883,7 @@
         <v>46093</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -28956,7 +28956,7 @@
         <v>45792</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29029,7 +29029,7 @@
         <v>45564</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29102,7 +29102,7 @@
         <v>45010</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29175,7 +29175,7 @@
         <v>46105</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29253,7 +29253,7 @@
         <v>46105</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29331,7 +29331,7 @@
         <v>46105</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29409,7 +29409,7 @@
         <v>46105</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29487,7 +29487,7 @@
         <v>46106</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29565,7 +29565,7 @@
         <v>46105</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29643,7 +29643,7 @@
         <v>46105</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -29721,7 +29721,7 @@
         <v>46105</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -29799,7 +29799,7 @@
         <v>45113</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -29872,7 +29872,7 @@
         <v>46198</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -29945,7 +29945,7 @@
         <v>46107</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30018,7 +30018,7 @@
         <v>46198</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30091,7 +30091,7 @@
         <v>45214</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30164,7 +30164,7 @@
         <v>45217</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30237,7 +30237,7 @@
         <v>46108</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30310,7 +30310,7 @@
         <v>45156</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30383,7 +30383,7 @@
         <v>46108</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30456,7 +30456,7 @@
         <v>46198</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30529,7 +30529,7 @@
         <v>46198</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30602,7 +30602,7 @@
         <v>44942</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30675,7 +30675,7 @@
         <v>46190</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -30753,7 +30753,7 @@
         <v>45539</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -30826,7 +30826,7 @@
         <v>45355</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -30904,7 +30904,7 @@
         <v>44882</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -30977,7 +30977,7 @@
         <v>45175</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31050,7 +31050,7 @@
         <v>45175</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31123,7 +31123,7 @@
         <v>45076</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31196,7 +31196,7 @@
         <v>45076</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31269,7 +31269,7 @@
         <v>46125</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31342,7 +31342,7 @@
         <v>46202</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31415,7 +31415,7 @@
         <v>45653</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31488,7 +31488,7 @@
         <v>44526</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31561,7 +31561,7 @@
         <v>46128</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31634,7 +31634,7 @@
         <v>45612</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -31707,7 +31707,7 @@
         <v>46204</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -31780,7 +31780,7 @@
         <v>45625</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -31853,7 +31853,7 @@
         <v>44816</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -31926,7 +31926,7 @@
         <v>46204</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -31999,7 +31999,7 @@
         <v>46204</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32072,7 +32072,7 @@
         <v>46204</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32145,7 +32145,7 @@
         <v>45222</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32218,7 +32218,7 @@
         <v>45211</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32291,7 +32291,7 @@
         <v>45435</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32364,7 +32364,7 @@
         <v>45435</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32437,7 +32437,7 @@
         <v>45435</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32510,7 +32510,7 @@
         <v>44911</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32583,7 +32583,7 @@
         <v>46204</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -32656,7 +32656,7 @@
         <v>46204</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -32729,7 +32729,7 @@
         <v>46204</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -32802,7 +32802,7 @@
         <v>45748</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -32875,7 +32875,7 @@
         <v>45378</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -32948,7 +32948,7 @@
         <v>45141</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33021,7 +33021,7 @@
         <v>45835</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33094,7 +33094,7 @@
         <v>46000</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33172,7 +33172,7 @@
         <v>46206</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33245,7 +33245,7 @@
         <v>44992</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33318,7 +33318,7 @@
         <v>44992</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33391,7 +33391,7 @@
         <v>45202</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33464,7 +33464,7 @@
         <v>46206</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33537,7 +33537,7 @@
         <v>45588</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33610,7 +33610,7 @@
         <v>45246</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -33683,7 +33683,7 @@
         <v>44865</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -33756,7 +33756,7 @@
         <v>44698</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -33829,7 +33829,7 @@
         <v>45189</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -33902,7 +33902,7 @@
         <v>46216</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -33980,7 +33980,7 @@
         <v>46216</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34058,7 +34058,7 @@
         <v>46216</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34136,7 +34136,7 @@
         <v>46216</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34214,7 +34214,7 @@
         <v>46216</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34292,7 +34292,7 @@
         <v>46216</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34370,7 +34370,7 @@
         <v>45352</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34448,7 +34448,7 @@
         <v>44687</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34521,7 +34521,7 @@
         <v>45467</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34594,7 +34594,7 @@
         <v>45211</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -34667,7 +34667,7 @@
         <v>45187</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -34740,7 +34740,7 @@
         <v>45450</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -34813,7 +34813,7 @@
         <v>45253</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -34886,7 +34886,7 @@
         <v>46226</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -34959,7 +34959,7 @@
         <v>46226</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35032,7 +35032,7 @@
         <v>46226</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35105,7 +35105,7 @@
         <v>45051</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35178,7 +35178,7 @@
         <v>45215</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35251,7 +35251,7 @@
         <v>45078</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35324,7 +35324,7 @@
         <v>46227</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35397,7 +35397,7 @@
         <v>46227</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35470,7 +35470,7 @@
         <v>45574</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35543,7 +35543,7 @@
         <v>44992</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -35616,7 +35616,7 @@
         <v>45244</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -35689,7 +35689,7 @@
         <v>45687</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -35762,7 +35762,7 @@
         <v>46234</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -35840,7 +35840,7 @@
         <v>44858</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -35913,7 +35913,7 @@
         <v>45539</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -35986,7 +35986,7 @@
         <v>45609</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36059,7 +36059,7 @@
         <v>44531</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36132,7 +36132,7 @@
         <v>46279</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36205,7 +36205,7 @@
         <v>45049</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36278,7 +36278,7 @@
         <v>45679</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36351,7 +36351,7 @@
         <v>46280</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36424,7 +36424,7 @@
         <v>44859</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36497,7 +36497,7 @@
         <v>44531</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36570,7 +36570,7 @@
         <v>45446</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -36643,7 +36643,7 @@
         <v>45616</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -36716,7 +36716,7 @@
         <v>46240</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -36794,7 +36794,7 @@
         <v>46240</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -36872,7 +36872,7 @@
         <v>46240</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -36950,7 +36950,7 @@
         <v>44587</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37023,7 +37023,7 @@
         <v>45770</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37096,7 +37096,7 @@
         <v>44582</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37169,7 +37169,7 @@
         <v>45759</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37242,7 +37242,7 @@
         <v>45531</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37315,7 +37315,7 @@
         <v>46066</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37388,7 +37388,7 @@
         <v>44897</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37461,7 +37461,7 @@
         <v>45911</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -37534,7 +37534,7 @@
         <v>45583</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -37607,7 +37607,7 @@
         <v>45594</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -37680,7 +37680,7 @@
         <v>45469</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -37758,7 +37758,7 @@
         <v>45401</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -37831,7 +37831,7 @@
         <v>46092</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -37904,7 +37904,7 @@
         <v>45092</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -37977,7 +37977,7 @@
         <v>45092</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38050,7 +38050,7 @@
         <v>45103</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38123,7 +38123,7 @@
         <v>46245</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38196,7 +38196,7 @@
         <v>46287</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38269,7 +38269,7 @@
         <v>46246</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38342,7 +38342,7 @@
         <v>46287</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38415,7 +38415,7 @@
         <v>44760</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38488,7 +38488,7 @@
         <v>44526</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -38561,7 +38561,7 @@
         <v>46287</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -38634,7 +38634,7 @@
         <v>46287</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -38707,7 +38707,7 @@
         <v>45268</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -38780,7 +38780,7 @@
         <v>46287</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -38853,7 +38853,7 @@
         <v>45440</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -38926,7 +38926,7 @@
         <v>46283</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -38999,7 +38999,7 @@
         <v>45244</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39072,7 +39072,7 @@
         <v>46245</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39145,7 +39145,7 @@
         <v>46287</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39218,7 +39218,7 @@
         <v>45051</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39291,7 +39291,7 @@
         <v>46247</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39364,7 +39364,7 @@
         <v>45176</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39437,7 +39437,7 @@
         <v>46154</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39510,7 +39510,7 @@
         <v>45916</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -39583,7 +39583,7 @@
         <v>46290</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -39656,7 +39656,7 @@
         <v>44921</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -39729,7 +39729,7 @@
         <v>44928</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -39802,7 +39802,7 @@
         <v>44568</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -39875,7 +39875,7 @@
         <v>46248</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -39948,7 +39948,7 @@
         <v>46168</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40021,7 +40021,7 @@
         <v>44634</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40094,7 +40094,7 @@
         <v>46251</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40172,7 +40172,7 @@
         <v>46248</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40245,7 +40245,7 @@
         <v>46293</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40323,7 +40323,7 @@
         <v>46247</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40396,7 +40396,7 @@
         <v>44592</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40469,7 +40469,7 @@
         <v>46030</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -40542,7 +40542,7 @@
         <v>44777</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -40615,7 +40615,7 @@
         <v>44942</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -40688,7 +40688,7 @@
         <v>44942</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -40761,7 +40761,7 @@
         <v>45273</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -40834,7 +40834,7 @@
         <v>46290</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -40907,7 +40907,7 @@
         <v>45497</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -40980,7 +40980,7 @@
         <v>45217</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41053,7 +41053,7 @@
         <v>44621</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41126,7 +41126,7 @@
         <v>44922</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41199,7 +41199,7 @@
         <v>46294</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41272,7 +41272,7 @@
         <v>45169</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41345,7 +41345,7 @@
         <v>46295</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41418,7 +41418,7 @@
         <v>46294</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41491,7 +41491,7 @@
         <v>46295</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -41564,7 +41564,7 @@
         <v>46294</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -41637,7 +41637,7 @@
         <v>44860</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -41710,7 +41710,7 @@
         <v>46251</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -41783,7 +41783,7 @@
         <v>45154</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -41856,7 +41856,7 @@
         <v>46251</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -41929,7 +41929,7 @@
         <v>44636</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42002,7 +42002,7 @@
         <v>44529</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42075,7 +42075,7 @@
         <v>46155</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42148,7 +42148,7 @@
         <v>46254</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42221,7 +42221,7 @@
         <v>46254</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42294,7 +42294,7 @@
         <v>44508</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42367,7 +42367,7 @@
         <v>46258</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42440,7 +42440,7 @@
         <v>44858</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -42513,7 +42513,7 @@
         <v>45776</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -42586,7 +42586,7 @@
         <v>46257</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -42659,7 +42659,7 @@
         <v>46300</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -42732,7 +42732,7 @@
         <v>45663</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -42805,7 +42805,7 @@
         <v>46258</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -42878,7 +42878,7 @@
         <v>45624</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -42951,7 +42951,7 @@
         <v>45781</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43024,7 +43024,7 @@
         <v>45407</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43097,7 +43097,7 @@
         <v>45612</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43170,7 +43170,7 @@
         <v>45612</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43243,7 +43243,7 @@
         <v>45719</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43316,7 +43316,7 @@
         <v>45527</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43389,7 +43389,7 @@
         <v>45638</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43462,7 +43462,7 @@
         <v>46303</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -43535,7 +43535,7 @@
         <v>46302</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -43608,7 +43608,7 @@
         <v>46303</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -43681,7 +43681,7 @@
         <v>46262</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -43754,7 +43754,7 @@
         <v>46307</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -43827,7 +43827,7 @@
         <v>45799</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -43900,7 +43900,7 @@
         <v>46307</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -43973,7 +43973,7 @@
         <v>46307</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44046,7 +44046,7 @@
         <v>46307</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44119,7 +44119,7 @@
         <v>45405</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44192,7 +44192,7 @@
         <v>44511</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44265,7 +44265,7 @@
         <v>44511</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44338,7 +44338,7 @@
         <v>46261</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44411,7 +44411,7 @@
         <v>45702</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44484,7 +44484,7 @@
         <v>45589</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -44557,7 +44557,7 @@
         <v>45460</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -44630,7 +44630,7 @@
         <v>45663</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -44703,7 +44703,7 @@
         <v>45804</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -44776,7 +44776,7 @@
         <v>46268</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -44849,7 +44849,7 @@
         <v>45548</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -44922,7 +44922,7 @@
         <v>45818</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -44995,7 +44995,7 @@
         <v>45695</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45068,7 +45068,7 @@
         <v>46267</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45141,7 +45141,7 @@
         <v>45441</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45214,7 +45214,7 @@
         <v>45335</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45287,7 +45287,7 @@
         <v>45334</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45360,7 +45360,7 @@
         <v>45835</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45433,7 +45433,7 @@
         <v>45834</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -45506,7 +45506,7 @@
         <v>45839</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -45579,7 +45579,7 @@
         <v>44641</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -45652,7 +45652,7 @@
         <v>45841</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -45725,7 +45725,7 @@
         <v>45842</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -45798,7 +45798,7 @@
         <v>45842</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -45871,7 +45871,7 @@
         <v>45842</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -45944,7 +45944,7 @@
         <v>45529</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46017,7 +46017,7 @@
         <v>45845</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46090,7 +46090,7 @@
         <v>45846</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46163,7 +46163,7 @@
         <v>45726</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46236,7 +46236,7 @@
         <v>45726</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46309,7 +46309,7 @@
         <v>45854</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46382,7 +46382,7 @@
         <v>44979</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -46455,7 +46455,7 @@
         <v>45819</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -46528,7 +46528,7 @@
         <v>45581</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -46601,7 +46601,7 @@
         <v>45763</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -46674,7 +46674,7 @@
         <v>45763</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -46747,7 +46747,7 @@
         <v>45812</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -46820,7 +46820,7 @@
         <v>45631</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -46893,7 +46893,7 @@
         <v>45581</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -46966,7 +46966,7 @@
         <v>45867</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47039,7 +47039,7 @@
         <v>45726</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47112,7 +47112,7 @@
         <v>45476</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47185,7 +47185,7 @@
         <v>44634</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47258,7 +47258,7 @@
         <v>44658</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -47331,7 +47331,7 @@
         <v>44621</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -47404,7 +47404,7 @@
         <v>44607</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -47477,7 +47477,7 @@
         <v>44733</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -47555,7 +47555,7 @@
         <v>45302</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -47628,7 +47628,7 @@
         <v>45476</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -47701,7 +47701,7 @@
         <v>45649</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -47774,7 +47774,7 @@
         <v>45728</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -47847,7 +47847,7 @@
         <v>45953</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -47920,7 +47920,7 @@
         <v>45967</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -47993,7 +47993,7 @@
         <v>46010</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48066,7 +48066,7 @@
         <v>46010</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48139,7 +48139,7 @@
         <v>46029</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -48217,7 +48217,7 @@
         <v>46079</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -48290,7 +48290,7 @@
         <v>46094</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -48363,7 +48363,7 @@
         <v>46119</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -48436,7 +48436,7 @@
         <v>46182</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>

--- a/Översikt ÄLMHULT.xlsx
+++ b/Översikt ÄLMHULT.xlsx
@@ -601,7 +601,7 @@
         <v>46209</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>45786</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
         <v>46041</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
         <v>45945</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>44883</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>45215</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>45645</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>46043</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
         <v>46211</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>44889</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>45012</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>45183</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>44830</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2021,7 +2021,7 @@
         <v>44883</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2127,7 +2127,7 @@
         <v>46171</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         <v>45818</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
         <v>45050</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2455,7 +2455,7 @@
         <v>45908</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
         <v>45560</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
         <v>45932</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2779,7 +2779,7 @@
         <v>45631</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
         <v>45218</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2989,7 +2989,7 @@
         <v>45386</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3094,7 +3094,7 @@
         <v>45719</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3199,7 +3199,7 @@
         <v>46204</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3304,7 +3304,7 @@
         <v>44882</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3409,7 +3409,7 @@
         <v>45769</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
         <v>45280</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3619,7 +3619,7 @@
         <v>45888</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3724,7 +3724,7 @@
         <v>46290</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
         <v>45763</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3934,7 +3934,7 @@
         <v>45856</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         <v>44869</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4148,7 +4148,7 @@
         <v>45786</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4253,7 +4253,7 @@
         <v>44609</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4326,7 +4326,7 @@
         <v>44525</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4399,7 +4399,7 @@
         <v>44785</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4472,7 +4472,7 @@
         <v>44785</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4545,7 +4545,7 @@
         <v>44785</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4618,7 +4618,7 @@
         <v>44515</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4691,7 +4691,7 @@
         <v>44802</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4764,7 +4764,7 @@
         <v>44785</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4837,7 +4837,7 @@
         <v>44749</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4910,7 +4910,7 @@
         <v>44802</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4983,7 +4983,7 @@
         <v>44798</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5056,7 +5056,7 @@
         <v>44523</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5129,7 +5129,7 @@
         <v>44503</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5202,7 +5202,7 @@
         <v>44503</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5275,7 +5275,7 @@
         <v>44785</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5348,7 +5348,7 @@
         <v>44665</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5426,7 +5426,7 @@
         <v>44846</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5499,7 +5499,7 @@
         <v>44498</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5572,7 +5572,7 @@
         <v>44847</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5645,7 +5645,7 @@
         <v>44690</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5718,7 +5718,7 @@
         <v>44812</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5791,7 +5791,7 @@
         <v>44504</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5864,7 +5864,7 @@
         <v>44602</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5937,7 +5937,7 @@
         <v>44512</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6010,7 +6010,7 @@
         <v>44621</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6083,7 +6083,7 @@
         <v>44609</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6156,7 +6156,7 @@
         <v>44487</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6229,7 +6229,7 @@
         <v>44721</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6302,7 +6302,7 @@
         <v>44587</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6380,7 +6380,7 @@
         <v>44802</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6453,7 +6453,7 @@
         <v>44509</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6526,7 +6526,7 @@
         <v>44739</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6599,7 +6599,7 @@
         <v>44733</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6672,7 +6672,7 @@
         <v>44551</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6745,7 +6745,7 @@
         <v>44621</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6818,7 +6818,7 @@
         <v>44854</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6891,7 +6891,7 @@
         <v>44854</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6964,7 +6964,7 @@
         <v>44680</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7037,7 +7037,7 @@
         <v>44524</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7110,7 +7110,7 @@
         <v>44690</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7183,7 +7183,7 @@
         <v>44690</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7256,7 +7256,7 @@
         <v>44865</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7329,7 +7329,7 @@
         <v>44496</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7402,7 +7402,7 @@
         <v>44721</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         <v>44525</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7548,7 +7548,7 @@
         <v>44685</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7621,7 +7621,7 @@
         <v>44643</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7694,7 +7694,7 @@
         <v>44596</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7767,7 +7767,7 @@
         <v>44510</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7840,7 +7840,7 @@
         <v>44522</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7913,7 +7913,7 @@
         <v>44636</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7986,7 +7986,7 @@
         <v>44657</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8059,7 +8059,7 @@
         <v>44491</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8132,7 +8132,7 @@
         <v>44831</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8205,7 +8205,7 @@
         <v>44831</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8278,7 +8278,7 @@
         <v>45433</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8351,7 +8351,7 @@
         <v>45209</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8424,7 +8424,7 @@
         <v>45244</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8497,7 +8497,7 @@
         <v>45098</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8590,7 +8590,7 @@
         <v>45062</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8663,7 +8663,7 @@
         <v>45734</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8736,7 +8736,7 @@
         <v>45735</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8809,7 +8809,7 @@
         <v>45735</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8882,7 +8882,7 @@
         <v>45348</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8955,7 +8955,7 @@
         <v>45457</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9028,7 +9028,7 @@
         <v>44496</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9101,7 +9101,7 @@
         <v>45610</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9174,7 +9174,7 @@
         <v>44610</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9247,7 +9247,7 @@
         <v>45469</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9320,7 +9320,7 @@
         <v>44826</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9393,7 +9393,7 @@
         <v>44962</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9466,7 +9466,7 @@
         <v>45543</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9539,7 +9539,7 @@
         <v>45254</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9612,7 +9612,7 @@
         <v>45578</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9685,7 +9685,7 @@
         <v>45554</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9758,7 +9758,7 @@
         <v>45133</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9831,7 +9831,7 @@
         <v>45575</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9904,7 +9904,7 @@
         <v>45359</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9977,7 +9977,7 @@
         <v>45457</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10050,7 +10050,7 @@
         <v>45457</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10123,7 +10123,7 @@
         <v>45133</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10196,7 +10196,7 @@
         <v>45175</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10269,7 +10269,7 @@
         <v>45737</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10342,7 +10342,7 @@
         <v>44496</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10415,7 +10415,7 @@
         <v>45469</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10493,7 +10493,7 @@
         <v>45720</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10566,7 +10566,7 @@
         <v>45566</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10639,7 +10639,7 @@
         <v>45222</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10712,7 +10712,7 @@
         <v>45222</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10785,7 +10785,7 @@
         <v>45049</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10858,7 +10858,7 @@
         <v>45309</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10931,7 +10931,7 @@
         <v>44876</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11004,7 +11004,7 @@
         <v>44686</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11077,7 +11077,7 @@
         <v>44994</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11150,7 +11150,7 @@
         <v>45638</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11223,7 +11223,7 @@
         <v>45638</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11296,7 +11296,7 @@
         <v>45051</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11369,7 +11369,7 @@
         <v>45103</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11442,7 +11442,7 @@
         <v>45187</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11515,7 +11515,7 @@
         <v>44817</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11588,7 +11588,7 @@
         <v>45315</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11661,7 +11661,7 @@
         <v>45240</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11739,7 +11739,7 @@
         <v>45350</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11812,7 +11812,7 @@
         <v>45693</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11885,7 +11885,7 @@
         <v>44853</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11958,7 +11958,7 @@
         <v>45303</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12031,7 +12031,7 @@
         <v>45290</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12104,7 +12104,7 @@
         <v>45443</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12177,7 +12177,7 @@
         <v>44935</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12250,7 +12250,7 @@
         <v>45586</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12323,7 +12323,7 @@
         <v>44979</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12396,7 +12396,7 @@
         <v>45180</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12469,7 +12469,7 @@
         <v>44859</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12542,7 +12542,7 @@
         <v>45015</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12615,7 +12615,7 @@
         <v>45771</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12688,7 +12688,7 @@
         <v>44958</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12761,7 +12761,7 @@
         <v>44861</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12834,7 +12834,7 @@
         <v>45062</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12907,7 +12907,7 @@
         <v>45414</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12980,7 +12980,7 @@
         <v>45460</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13053,7 +13053,7 @@
         <v>45090</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13126,7 +13126,7 @@
         <v>44994</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13199,7 +13199,7 @@
         <v>45681</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13272,7 +13272,7 @@
         <v>44994</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13345,7 +13345,7 @@
         <v>45042</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13418,7 +13418,7 @@
         <v>45680</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13491,7 +13491,7 @@
         <v>44897</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13564,7 +13564,7 @@
         <v>45373</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13642,7 +13642,7 @@
         <v>45715</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13715,7 +13715,7 @@
         <v>44921</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13788,7 +13788,7 @@
         <v>45078</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13861,7 +13861,7 @@
         <v>45145</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13934,7 +13934,7 @@
         <v>45352</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14012,7 +14012,7 @@
         <v>45681</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14085,7 +14085,7 @@
         <v>45068</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14158,7 +14158,7 @@
         <v>45228</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14231,7 +14231,7 @@
         <v>45608</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14304,7 +14304,7 @@
         <v>45258</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14377,7 +14377,7 @@
         <v>44914</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14450,7 +14450,7 @@
         <v>45538</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14523,7 +14523,7 @@
         <v>44743</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14596,7 +14596,7 @@
         <v>44503</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14669,7 +14669,7 @@
         <v>45559</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14742,7 +14742,7 @@
         <v>45167</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14815,7 +14815,7 @@
         <v>45817</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14888,7 +14888,7 @@
         <v>45722</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14961,7 +14961,7 @@
         <v>45547</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15034,7 +15034,7 @@
         <v>45328</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15107,7 +15107,7 @@
         <v>45930</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15180,7 +15180,7 @@
         <v>45630</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15253,7 +15253,7 @@
         <v>45317</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15326,7 +15326,7 @@
         <v>45078</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15399,7 +15399,7 @@
         <v>45078</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15472,7 +15472,7 @@
         <v>45254</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15545,7 +15545,7 @@
         <v>45733</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15618,7 +15618,7 @@
         <v>45286</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15691,7 +15691,7 @@
         <v>44998</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15769,7 +15769,7 @@
         <v>45716</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15842,7 +15842,7 @@
         <v>45537</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15915,7 +15915,7 @@
         <v>45884</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15988,7 +15988,7 @@
         <v>45181</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16061,7 +16061,7 @@
         <v>45716</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16134,7 +16134,7 @@
         <v>45531</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16212,7 +16212,7 @@
         <v>45716</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16290,7 +16290,7 @@
         <v>45887</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16363,7 +16363,7 @@
         <v>45883</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16436,7 +16436,7 @@
         <v>45637</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16509,7 +16509,7 @@
         <v>45911</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16582,7 +16582,7 @@
         <v>45372</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16655,7 +16655,7 @@
         <v>45888</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16728,7 +16728,7 @@
         <v>45251</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16801,7 +16801,7 @@
         <v>45440</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16874,7 +16874,7 @@
         <v>44545</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16947,7 +16947,7 @@
         <v>45887</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17020,7 +17020,7 @@
         <v>45897</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17093,7 +17093,7 @@
         <v>45140</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17166,7 +17166,7 @@
         <v>45531</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17239,7 +17239,7 @@
         <v>45898</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17312,7 +17312,7 @@
         <v>45938</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17385,7 +17385,7 @@
         <v>46140</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17463,7 +17463,7 @@
         <v>45111</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17536,7 +17536,7 @@
         <v>45348</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17609,7 +17609,7 @@
         <v>45233</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17682,7 +17682,7 @@
         <v>45233</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17755,7 +17755,7 @@
         <v>45748</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17828,7 +17828,7 @@
         <v>44523</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17901,7 +17901,7 @@
         <v>45211</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17974,7 +17974,7 @@
         <v>45215</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18047,7 +18047,7 @@
         <v>45629</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18120,7 +18120,7 @@
         <v>45170</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18193,7 +18193,7 @@
         <v>45915</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18271,7 +18271,7 @@
         <v>45917</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18349,7 +18349,7 @@
         <v>45917</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18427,7 +18427,7 @@
         <v>45917</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18505,7 +18505,7 @@
         <v>45252</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18578,7 +18578,7 @@
         <v>45916</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18651,7 +18651,7 @@
         <v>45006</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18729,7 +18729,7 @@
         <v>45089</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18802,7 +18802,7 @@
         <v>45608</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18875,7 +18875,7 @@
         <v>46147</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18948,7 +18948,7 @@
         <v>45734</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19021,7 +19021,7 @@
         <v>45211</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19094,7 +19094,7 @@
         <v>45215</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19167,7 +19167,7 @@
         <v>45376</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19240,7 +19240,7 @@
         <v>45134</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19313,7 +19313,7 @@
         <v>45929</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19386,7 +19386,7 @@
         <v>45930</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19459,7 +19459,7 @@
         <v>45930</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19532,7 +19532,7 @@
         <v>46141</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19605,7 +19605,7 @@
         <v>44784</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19683,7 +19683,7 @@
         <v>45373</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19761,7 +19761,7 @@
         <v>45373</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19839,7 +19839,7 @@
         <v>45084</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19912,7 +19912,7 @@
         <v>45010</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19985,7 +19985,7 @@
         <v>45944</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20058,7 +20058,7 @@
         <v>45945</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20131,7 +20131,7 @@
         <v>46155</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20204,7 +20204,7 @@
         <v>45947</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20277,7 +20277,7 @@
         <v>45631</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20350,7 +20350,7 @@
         <v>45355</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20423,7 +20423,7 @@
         <v>45355</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20501,7 +20501,7 @@
         <v>45916</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20579,7 +20579,7 @@
         <v>45529</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20652,7 +20652,7 @@
         <v>45952</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20725,7 +20725,7 @@
         <v>45959</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20798,7 +20798,7 @@
         <v>44943</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20871,7 +20871,7 @@
         <v>45589</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20944,7 +20944,7 @@
         <v>45010</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21017,7 +21017,7 @@
         <v>45818</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21090,7 +21090,7 @@
         <v>45271</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21163,7 +21163,7 @@
         <v>45966</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21236,7 +21236,7 @@
         <v>45966</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21309,7 +21309,7 @@
         <v>45967</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21382,7 +21382,7 @@
         <v>46076</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21455,7 +21455,7 @@
         <v>45966</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21528,7 +21528,7 @@
         <v>45969</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21601,7 +21601,7 @@
         <v>45969</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21674,7 +21674,7 @@
         <v>45085</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21747,7 +21747,7 @@
         <v>44543</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21820,7 +21820,7 @@
         <v>44865</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21893,7 +21893,7 @@
         <v>45048</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21966,7 +21966,7 @@
         <v>45533</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22039,7 +22039,7 @@
         <v>45001</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22112,7 +22112,7 @@
         <v>45282</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22185,7 +22185,7 @@
         <v>45728</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22258,7 +22258,7 @@
         <v>45273</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22331,7 +22331,7 @@
         <v>45273</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22404,7 +22404,7 @@
         <v>45986</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22482,7 +22482,7 @@
         <v>45706</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22555,7 +22555,7 @@
         <v>45612</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22628,7 +22628,7 @@
         <v>45615</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22701,7 +22701,7 @@
         <v>45250</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22774,7 +22774,7 @@
         <v>45250</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22847,7 +22847,7 @@
         <v>45251</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22920,7 +22920,7 @@
         <v>45546</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22993,7 +22993,7 @@
         <v>45992</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23071,7 +23071,7 @@
         <v>45180</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23144,7 +23144,7 @@
         <v>45992</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23222,7 +23222,7 @@
         <v>45992</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23300,7 +23300,7 @@
         <v>45992</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23378,7 +23378,7 @@
         <v>45539</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23451,7 +23451,7 @@
         <v>45311</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23524,7 +23524,7 @@
         <v>45308</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23597,7 +23597,7 @@
         <v>45384</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23670,7 +23670,7 @@
         <v>45374</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23743,7 +23743,7 @@
         <v>45706</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23816,7 +23816,7 @@
         <v>46000</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23894,7 +23894,7 @@
         <v>45211</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23967,7 +23967,7 @@
         <v>45012</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24040,7 +24040,7 @@
         <v>45314</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24113,7 +24113,7 @@
         <v>45707</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24186,7 +24186,7 @@
         <v>45303</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24259,7 +24259,7 @@
         <v>45653</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24332,7 +24332,7 @@
         <v>45653</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24405,7 +24405,7 @@
         <v>46005</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24478,7 +24478,7 @@
         <v>45187</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24551,7 +24551,7 @@
         <v>45716</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24629,7 +24629,7 @@
         <v>45946</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24702,7 +24702,7 @@
         <v>44973</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24775,7 +24775,7 @@
         <v>44942</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24848,7 +24848,7 @@
         <v>45812</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24921,7 +24921,7 @@
         <v>45700</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24994,7 +24994,7 @@
         <v>45061</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25067,7 +25067,7 @@
         <v>44897</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25140,7 +25140,7 @@
         <v>45911</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25213,7 +25213,7 @@
         <v>46016</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25286,7 +25286,7 @@
         <v>44977</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25359,7 +25359,7 @@
         <v>45628</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25432,7 +25432,7 @@
         <v>45352</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25510,7 +25510,7 @@
         <v>45513</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25583,7 +25583,7 @@
         <v>45166</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25656,7 +25656,7 @@
         <v>45680</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25729,7 +25729,7 @@
         <v>45191</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25802,7 +25802,7 @@
         <v>44853</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25875,7 +25875,7 @@
         <v>45251</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25948,7 +25948,7 @@
         <v>46035</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26021,7 +26021,7 @@
         <v>46037</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26094,7 +26094,7 @@
         <v>45589</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26167,7 +26167,7 @@
         <v>46038</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26240,7 +26240,7 @@
         <v>44855</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26313,7 +26313,7 @@
         <v>44942</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26386,7 +26386,7 @@
         <v>45680</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26459,7 +26459,7 @@
         <v>46045</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26532,7 +26532,7 @@
         <v>45462</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26605,7 +26605,7 @@
         <v>45412</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26678,7 +26678,7 @@
         <v>45113</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26751,7 +26751,7 @@
         <v>45421</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26824,7 +26824,7 @@
         <v>45558</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26897,7 +26897,7 @@
         <v>46052</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -26970,7 +26970,7 @@
         <v>45090</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27043,7 +27043,7 @@
         <v>45567</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27116,7 +27116,7 @@
         <v>46052</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27189,7 +27189,7 @@
         <v>45268</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27262,7 +27262,7 @@
         <v>46184</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27335,7 +27335,7 @@
         <v>46184</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27408,7 +27408,7 @@
         <v>46063</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27481,7 +27481,7 @@
         <v>44930</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27554,7 +27554,7 @@
         <v>46061</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27627,7 +27627,7 @@
         <v>46065</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27700,7 +27700,7 @@
         <v>45698</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27773,7 +27773,7 @@
         <v>45177</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27846,7 +27846,7 @@
         <v>44986</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -27924,7 +27924,7 @@
         <v>46076</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -27997,7 +27997,7 @@
         <v>45175</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28070,7 +28070,7 @@
         <v>45827</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28143,7 +28143,7 @@
         <v>45677</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28216,7 +28216,7 @@
         <v>45462</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28289,7 +28289,7 @@
         <v>45081</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28362,7 +28362,7 @@
         <v>45166</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28435,7 +28435,7 @@
         <v>45595</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28508,7 +28508,7 @@
         <v>44942</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28581,7 +28581,7 @@
         <v>45391</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28654,7 +28654,7 @@
         <v>45373</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28732,7 +28732,7 @@
         <v>45373</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -28810,7 +28810,7 @@
         <v>45155</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -28883,7 +28883,7 @@
         <v>46093</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -28956,7 +28956,7 @@
         <v>45792</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29029,7 +29029,7 @@
         <v>45564</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29102,7 +29102,7 @@
         <v>45010</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29175,7 +29175,7 @@
         <v>46105</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29253,7 +29253,7 @@
         <v>46105</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29331,7 +29331,7 @@
         <v>46105</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29409,7 +29409,7 @@
         <v>46105</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29487,7 +29487,7 @@
         <v>46106</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29565,7 +29565,7 @@
         <v>46105</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29643,7 +29643,7 @@
         <v>46105</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -29721,7 +29721,7 @@
         <v>46105</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -29799,7 +29799,7 @@
         <v>45113</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -29872,7 +29872,7 @@
         <v>46198</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -29945,7 +29945,7 @@
         <v>46107</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30018,7 +30018,7 @@
         <v>46198</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30091,7 +30091,7 @@
         <v>45214</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30164,7 +30164,7 @@
         <v>45217</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30237,7 +30237,7 @@
         <v>46108</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30310,7 +30310,7 @@
         <v>45156</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30383,7 +30383,7 @@
         <v>46108</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30456,7 +30456,7 @@
         <v>46198</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30529,7 +30529,7 @@
         <v>46198</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30602,7 +30602,7 @@
         <v>44942</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30675,7 +30675,7 @@
         <v>46190</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -30753,7 +30753,7 @@
         <v>45539</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -30826,7 +30826,7 @@
         <v>45355</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -30904,7 +30904,7 @@
         <v>44882</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -30977,7 +30977,7 @@
         <v>45175</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31050,7 +31050,7 @@
         <v>45175</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31123,7 +31123,7 @@
         <v>45076</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31196,7 +31196,7 @@
         <v>45076</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31269,7 +31269,7 @@
         <v>46125</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31342,7 +31342,7 @@
         <v>46202</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31415,7 +31415,7 @@
         <v>45653</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31488,7 +31488,7 @@
         <v>44526</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31561,7 +31561,7 @@
         <v>46128</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31634,7 +31634,7 @@
         <v>45612</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -31707,7 +31707,7 @@
         <v>46204</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -31780,7 +31780,7 @@
         <v>45625</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -31853,7 +31853,7 @@
         <v>44816</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -31926,7 +31926,7 @@
         <v>46204</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -31999,7 +31999,7 @@
         <v>46204</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32072,7 +32072,7 @@
         <v>46204</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32145,7 +32145,7 @@
         <v>45222</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32218,7 +32218,7 @@
         <v>45211</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32291,7 +32291,7 @@
         <v>45435</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32364,7 +32364,7 @@
         <v>45435</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32437,7 +32437,7 @@
         <v>45435</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32510,7 +32510,7 @@
         <v>44911</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32583,7 +32583,7 @@
         <v>46204</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -32656,7 +32656,7 @@
         <v>46204</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -32729,7 +32729,7 @@
         <v>46204</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -32802,7 +32802,7 @@
         <v>45748</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -32875,7 +32875,7 @@
         <v>45378</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -32948,7 +32948,7 @@
         <v>45141</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33021,7 +33021,7 @@
         <v>45835</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33094,7 +33094,7 @@
         <v>46000</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33172,7 +33172,7 @@
         <v>46206</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33245,7 +33245,7 @@
         <v>44992</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33318,7 +33318,7 @@
         <v>44992</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33391,7 +33391,7 @@
         <v>45202</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33464,7 +33464,7 @@
         <v>46206</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33537,7 +33537,7 @@
         <v>45588</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33610,7 +33610,7 @@
         <v>45246</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -33683,7 +33683,7 @@
         <v>44865</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -33756,7 +33756,7 @@
         <v>44698</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -33829,7 +33829,7 @@
         <v>45189</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -33902,7 +33902,7 @@
         <v>46216</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -33980,7 +33980,7 @@
         <v>46216</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34058,7 +34058,7 @@
         <v>46216</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34136,7 +34136,7 @@
         <v>46216</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34214,7 +34214,7 @@
         <v>46216</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34292,7 +34292,7 @@
         <v>46216</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34370,7 +34370,7 @@
         <v>45352</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34448,7 +34448,7 @@
         <v>44687</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34521,7 +34521,7 @@
         <v>45467</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34594,7 +34594,7 @@
         <v>45211</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -34667,7 +34667,7 @@
         <v>45187</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -34740,7 +34740,7 @@
         <v>45450</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -34813,7 +34813,7 @@
         <v>45253</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -34886,7 +34886,7 @@
         <v>46226</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -34959,7 +34959,7 @@
         <v>46226</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35032,7 +35032,7 @@
         <v>46226</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35105,7 +35105,7 @@
         <v>45051</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35178,7 +35178,7 @@
         <v>45215</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35251,7 +35251,7 @@
         <v>45078</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35324,7 +35324,7 @@
         <v>46227</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35397,7 +35397,7 @@
         <v>46227</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35470,7 +35470,7 @@
         <v>45574</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35543,7 +35543,7 @@
         <v>44992</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -35616,7 +35616,7 @@
         <v>45244</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -35689,7 +35689,7 @@
         <v>45687</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -35762,7 +35762,7 @@
         <v>46234</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -35840,7 +35840,7 @@
         <v>44858</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -35913,7 +35913,7 @@
         <v>45539</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -35986,7 +35986,7 @@
         <v>45609</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36059,7 +36059,7 @@
         <v>44531</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36132,7 +36132,7 @@
         <v>46279</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36205,7 +36205,7 @@
         <v>45049</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36278,7 +36278,7 @@
         <v>45679</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36351,7 +36351,7 @@
         <v>46280</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36424,7 +36424,7 @@
         <v>44859</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36497,7 +36497,7 @@
         <v>44531</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36570,7 +36570,7 @@
         <v>45446</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -36643,7 +36643,7 @@
         <v>45616</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -36716,7 +36716,7 @@
         <v>46240</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -36794,7 +36794,7 @@
         <v>46240</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -36872,7 +36872,7 @@
         <v>46240</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -36950,7 +36950,7 @@
         <v>44587</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37023,7 +37023,7 @@
         <v>45770</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37096,7 +37096,7 @@
         <v>44582</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37169,7 +37169,7 @@
         <v>45759</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37242,7 +37242,7 @@
         <v>45531</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37315,7 +37315,7 @@
         <v>46066</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37388,7 +37388,7 @@
         <v>44897</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37461,7 +37461,7 @@
         <v>45911</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -37534,7 +37534,7 @@
         <v>45583</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -37607,7 +37607,7 @@
         <v>45594</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -37680,7 +37680,7 @@
         <v>45469</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -37758,7 +37758,7 @@
         <v>45401</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -37831,7 +37831,7 @@
         <v>46092</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -37904,7 +37904,7 @@
         <v>45092</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -37977,7 +37977,7 @@
         <v>45092</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38050,7 +38050,7 @@
         <v>45103</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38123,7 +38123,7 @@
         <v>46245</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38196,7 +38196,7 @@
         <v>46287</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38269,7 +38269,7 @@
         <v>46246</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38342,7 +38342,7 @@
         <v>46287</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38415,7 +38415,7 @@
         <v>44760</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38488,7 +38488,7 @@
         <v>44526</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -38561,7 +38561,7 @@
         <v>46287</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -38634,7 +38634,7 @@
         <v>46287</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -38707,7 +38707,7 @@
         <v>45268</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -38780,7 +38780,7 @@
         <v>46287</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -38853,7 +38853,7 @@
         <v>45440</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -38926,7 +38926,7 @@
         <v>46283</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -38999,7 +38999,7 @@
         <v>45244</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39072,7 +39072,7 @@
         <v>46245</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39145,7 +39145,7 @@
         <v>46287</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39218,7 +39218,7 @@
         <v>45051</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39291,7 +39291,7 @@
         <v>46247</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39364,7 +39364,7 @@
         <v>45176</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39437,7 +39437,7 @@
         <v>46154</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39510,7 +39510,7 @@
         <v>45916</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -39583,7 +39583,7 @@
         <v>46290</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -39656,7 +39656,7 @@
         <v>44921</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -39729,7 +39729,7 @@
         <v>44928</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -39802,7 +39802,7 @@
         <v>44568</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -39875,7 +39875,7 @@
         <v>46248</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -39948,7 +39948,7 @@
         <v>46168</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40021,7 +40021,7 @@
         <v>44634</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40094,7 +40094,7 @@
         <v>46251</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40172,7 +40172,7 @@
         <v>46248</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40245,7 +40245,7 @@
         <v>46293</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40323,7 +40323,7 @@
         <v>46247</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40396,7 +40396,7 @@
         <v>44592</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40469,7 +40469,7 @@
         <v>46030</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -40542,7 +40542,7 @@
         <v>44777</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -40615,7 +40615,7 @@
         <v>44942</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -40688,7 +40688,7 @@
         <v>44942</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -40761,7 +40761,7 @@
         <v>45273</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -40834,7 +40834,7 @@
         <v>46290</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -40907,7 +40907,7 @@
         <v>45497</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -40980,7 +40980,7 @@
         <v>45217</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41053,7 +41053,7 @@
         <v>44621</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41126,7 +41126,7 @@
         <v>44922</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41199,7 +41199,7 @@
         <v>46294</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41272,7 +41272,7 @@
         <v>45169</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41345,7 +41345,7 @@
         <v>46295</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41418,7 +41418,7 @@
         <v>46294</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41491,7 +41491,7 @@
         <v>46295</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -41564,7 +41564,7 @@
         <v>46294</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -41637,7 +41637,7 @@
         <v>44860</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -41710,7 +41710,7 @@
         <v>46251</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -41783,7 +41783,7 @@
         <v>45154</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -41856,7 +41856,7 @@
         <v>46251</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -41929,7 +41929,7 @@
         <v>44636</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42002,7 +42002,7 @@
         <v>44529</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42075,7 +42075,7 @@
         <v>46155</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42148,7 +42148,7 @@
         <v>46254</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42221,7 +42221,7 @@
         <v>46254</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42294,7 +42294,7 @@
         <v>44508</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42367,7 +42367,7 @@
         <v>46258</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42440,7 +42440,7 @@
         <v>44858</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -42513,7 +42513,7 @@
         <v>45776</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -42586,7 +42586,7 @@
         <v>46257</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -42659,7 +42659,7 @@
         <v>46300</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -42732,7 +42732,7 @@
         <v>45663</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -42805,7 +42805,7 @@
         <v>46258</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -42878,7 +42878,7 @@
         <v>45624</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -42951,7 +42951,7 @@
         <v>45781</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43024,7 +43024,7 @@
         <v>45407</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43097,7 +43097,7 @@
         <v>45612</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43170,7 +43170,7 @@
         <v>45612</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43243,7 +43243,7 @@
         <v>45719</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43316,7 +43316,7 @@
         <v>45527</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43389,7 +43389,7 @@
         <v>45638</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43462,7 +43462,7 @@
         <v>46303</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -43535,7 +43535,7 @@
         <v>46302</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -43608,7 +43608,7 @@
         <v>46303</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -43681,7 +43681,7 @@
         <v>46262</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -43754,7 +43754,7 @@
         <v>46307</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -43827,7 +43827,7 @@
         <v>45799</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -43900,7 +43900,7 @@
         <v>46307</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -43973,7 +43973,7 @@
         <v>46307</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44046,7 +44046,7 @@
         <v>46307</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44119,7 +44119,7 @@
         <v>45405</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44192,7 +44192,7 @@
         <v>44511</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44265,7 +44265,7 @@
         <v>44511</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44338,7 +44338,7 @@
         <v>46261</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44411,7 +44411,7 @@
         <v>45702</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44484,7 +44484,7 @@
         <v>45589</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -44557,7 +44557,7 @@
         <v>45460</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -44630,7 +44630,7 @@
         <v>45663</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -44703,7 +44703,7 @@
         <v>45804</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -44776,7 +44776,7 @@
         <v>46268</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -44849,7 +44849,7 @@
         <v>45548</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -44922,7 +44922,7 @@
         <v>45818</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -44995,7 +44995,7 @@
         <v>45695</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45068,7 +45068,7 @@
         <v>46267</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45141,7 +45141,7 @@
         <v>45441</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45214,7 +45214,7 @@
         <v>45335</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45287,7 +45287,7 @@
         <v>45334</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45360,7 +45360,7 @@
         <v>45835</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45433,7 +45433,7 @@
         <v>45834</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -45506,7 +45506,7 @@
         <v>45839</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -45579,7 +45579,7 @@
         <v>44641</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -45652,7 +45652,7 @@
         <v>45841</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -45725,7 +45725,7 @@
         <v>45842</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -45798,7 +45798,7 @@
         <v>45842</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -45871,7 +45871,7 @@
         <v>45842</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -45944,7 +45944,7 @@
         <v>45529</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46017,7 +46017,7 @@
         <v>45845</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46090,7 +46090,7 @@
         <v>45846</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46163,7 +46163,7 @@
         <v>45726</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46236,7 +46236,7 @@
         <v>45726</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46309,7 +46309,7 @@
         <v>45854</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46382,7 +46382,7 @@
         <v>44979</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -46455,7 +46455,7 @@
         <v>45819</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -46528,7 +46528,7 @@
         <v>45581</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -46601,7 +46601,7 @@
         <v>45763</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -46674,7 +46674,7 @@
         <v>45763</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -46747,7 +46747,7 @@
         <v>45812</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -46820,7 +46820,7 @@
         <v>45631</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -46893,7 +46893,7 @@
         <v>45581</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -46966,7 +46966,7 @@
         <v>45867</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47039,7 +47039,7 @@
         <v>45726</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47112,7 +47112,7 @@
         <v>45476</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47185,7 +47185,7 @@
         <v>44634</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47258,7 +47258,7 @@
         <v>44658</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -47331,7 +47331,7 @@
         <v>44621</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -47404,7 +47404,7 @@
         <v>44607</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -47477,7 +47477,7 @@
         <v>44733</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -47555,7 +47555,7 @@
         <v>45302</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -47628,7 +47628,7 @@
         <v>45476</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -47701,7 +47701,7 @@
         <v>45649</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -47774,7 +47774,7 @@
         <v>45728</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -47847,7 +47847,7 @@
         <v>45953</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -47920,7 +47920,7 @@
         <v>45967</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -47993,7 +47993,7 @@
         <v>46010</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48066,7 +48066,7 @@
         <v>46010</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48139,7 +48139,7 @@
         <v>46029</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -48217,7 +48217,7 @@
         <v>46079</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -48290,7 +48290,7 @@
         <v>46094</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -48363,7 +48363,7 @@
         <v>46119</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -48436,7 +48436,7 @@
         <v>46182</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>

--- a/Översikt ÄLMHULT.xlsx
+++ b/Översikt ÄLMHULT.xlsx
@@ -601,7 +601,7 @@
         <v>46209</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>45786</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
         <v>46041</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
         <v>45945</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>44883</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>45215</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>45645</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>46043</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
         <v>46211</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>46171</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         <v>44883</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>45818</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>45183</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2022,7 +2022,7 @@
         <v>44889</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         <v>44830</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2238,7 +2238,7 @@
         <v>45012</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
         <v>45050</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2455,7 +2455,7 @@
         <v>45908</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
         <v>45560</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
         <v>45932</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2779,7 +2779,7 @@
         <v>45386</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
         <v>45280</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2989,7 +2989,7 @@
         <v>46204</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3094,7 +3094,7 @@
         <v>45888</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3199,7 +3199,7 @@
         <v>45763</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3304,7 +3304,7 @@
         <v>45856</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
         <v>46290</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3518,7 +3518,7 @@
         <v>45769</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
         <v>45631</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3728,7 +3728,7 @@
         <v>45218</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3833,7 +3833,7 @@
         <v>44882</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
         <v>45719</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         <v>44869</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4148,7 +4148,7 @@
         <v>45786</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4253,7 +4253,7 @@
         <v>44609</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4326,7 +4326,7 @@
         <v>44525</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4399,7 +4399,7 @@
         <v>44785</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4472,7 +4472,7 @@
         <v>44785</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4545,7 +4545,7 @@
         <v>44785</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4618,7 +4618,7 @@
         <v>44802</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4691,7 +4691,7 @@
         <v>44802</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4764,7 +4764,7 @@
         <v>44785</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4837,7 +4837,7 @@
         <v>44749</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4910,7 +4910,7 @@
         <v>44798</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4983,7 +4983,7 @@
         <v>44523</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5056,7 +5056,7 @@
         <v>44515</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5129,7 +5129,7 @@
         <v>44503</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5202,7 +5202,7 @@
         <v>44503</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5275,7 +5275,7 @@
         <v>44785</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5348,7 +5348,7 @@
         <v>44665</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5426,7 +5426,7 @@
         <v>44846</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5499,7 +5499,7 @@
         <v>44498</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5572,7 +5572,7 @@
         <v>44847</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5645,7 +5645,7 @@
         <v>44690</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5718,7 +5718,7 @@
         <v>44812</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5791,7 +5791,7 @@
         <v>44504</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5864,7 +5864,7 @@
         <v>44602</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5937,7 +5937,7 @@
         <v>44512</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6010,7 +6010,7 @@
         <v>44621</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6083,7 +6083,7 @@
         <v>44609</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6156,7 +6156,7 @@
         <v>44721</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6229,7 +6229,7 @@
         <v>44587</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6307,7 +6307,7 @@
         <v>44802</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6380,7 +6380,7 @@
         <v>44509</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6453,7 +6453,7 @@
         <v>44739</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6526,7 +6526,7 @@
         <v>44551</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6599,7 +6599,7 @@
         <v>44733</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6672,7 +6672,7 @@
         <v>44621</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6745,7 +6745,7 @@
         <v>44854</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6818,7 +6818,7 @@
         <v>44854</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6891,7 +6891,7 @@
         <v>44680</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6964,7 +6964,7 @@
         <v>44690</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7037,7 +7037,7 @@
         <v>44690</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7110,7 +7110,7 @@
         <v>44524</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7183,7 +7183,7 @@
         <v>44865</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7256,7 +7256,7 @@
         <v>44496</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7329,7 +7329,7 @@
         <v>44721</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7402,7 +7402,7 @@
         <v>44525</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         <v>44685</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7548,7 +7548,7 @@
         <v>44596</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7621,7 +7621,7 @@
         <v>44643</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7694,7 +7694,7 @@
         <v>44510</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7767,7 +7767,7 @@
         <v>44522</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7840,7 +7840,7 @@
         <v>44636</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7913,7 +7913,7 @@
         <v>44657</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7986,7 +7986,7 @@
         <v>44831</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8059,7 +8059,7 @@
         <v>44831</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8132,7 +8132,7 @@
         <v>45286</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8205,7 +8205,7 @@
         <v>45888</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8278,7 +8278,7 @@
         <v>45575</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8351,7 +8351,7 @@
         <v>45887</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8424,7 +8424,7 @@
         <v>44816</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8497,7 +8497,7 @@
         <v>45215</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8570,7 +8570,7 @@
         <v>45181</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8643,7 +8643,7 @@
         <v>45637</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8716,7 +8716,7 @@
         <v>44942</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8789,7 +8789,7 @@
         <v>45222</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8862,7 +8862,7 @@
         <v>45222</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8935,7 +8935,7 @@
         <v>45268</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9008,7 +9008,7 @@
         <v>45716</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9081,7 +9081,7 @@
         <v>45085</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9154,7 +9154,7 @@
         <v>45497</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9227,7 +9227,7 @@
         <v>44942</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9300,7 +9300,7 @@
         <v>44860</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9373,7 +9373,7 @@
         <v>45187</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9446,7 +9446,7 @@
         <v>45290</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9519,7 +9519,7 @@
         <v>45609</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9592,7 +9592,7 @@
         <v>45898</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9665,7 +9665,7 @@
         <v>45217</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9738,7 +9738,7 @@
         <v>44998</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9816,7 +9816,7 @@
         <v>45897</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9889,7 +9889,7 @@
         <v>45244</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9962,7 +9962,7 @@
         <v>45211</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10035,7 +10035,7 @@
         <v>45348</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10108,7 +10108,7 @@
         <v>45111</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10181,7 +10181,7 @@
         <v>45401</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10254,7 +10254,7 @@
         <v>44526</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10327,7 +10327,7 @@
         <v>44855</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10400,7 +10400,7 @@
         <v>45141</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10473,7 +10473,7 @@
         <v>45359</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10546,7 +10546,7 @@
         <v>45748</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10619,7 +10619,7 @@
         <v>45884</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10692,7 +10692,7 @@
         <v>45012</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10765,7 +10765,7 @@
         <v>46076</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10838,7 +10838,7 @@
         <v>44687</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10911,7 +10911,7 @@
         <v>45818</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10984,7 +10984,7 @@
         <v>45081</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11057,7 +11057,7 @@
         <v>45068</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11130,7 +11130,7 @@
         <v>45916</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11203,7 +11203,7 @@
         <v>45915</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11281,7 +11281,7 @@
         <v>45917</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11359,7 +11359,7 @@
         <v>45917</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11437,7 +11437,7 @@
         <v>45010</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11510,7 +11510,7 @@
         <v>45917</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11588,7 +11588,7 @@
         <v>45728</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11661,7 +11661,7 @@
         <v>45048</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11734,7 +11734,7 @@
         <v>45177</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11807,7 +11807,7 @@
         <v>45042</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11880,7 +11880,7 @@
         <v>45273</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11953,7 +11953,7 @@
         <v>45391</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12026,7 +12026,7 @@
         <v>45929</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12099,7 +12099,7 @@
         <v>45946</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12172,7 +12172,7 @@
         <v>45930</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12245,7 +12245,7 @@
         <v>45911</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12318,7 +12318,7 @@
         <v>45134</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12391,7 +12391,7 @@
         <v>45930</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12464,7 +12464,7 @@
         <v>44743</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12537,7 +12537,7 @@
         <v>45469</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12615,7 +12615,7 @@
         <v>45440</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12688,7 +12688,7 @@
         <v>44977</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12761,7 +12761,7 @@
         <v>45373</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12839,7 +12839,7 @@
         <v>45373</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12917,7 +12917,7 @@
         <v>45078</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12990,7 +12990,7 @@
         <v>45078</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13063,7 +13063,7 @@
         <v>45628</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13136,7 +13136,7 @@
         <v>45311</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13209,7 +13209,7 @@
         <v>45061</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13282,7 +13282,7 @@
         <v>45638</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13355,7 +13355,7 @@
         <v>45944</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13428,7 +13428,7 @@
         <v>45638</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13501,7 +13501,7 @@
         <v>45090</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13574,7 +13574,7 @@
         <v>45254</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13647,7 +13647,7 @@
         <v>45539</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13720,7 +13720,7 @@
         <v>45217</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13793,7 +13793,7 @@
         <v>45945</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13866,7 +13866,7 @@
         <v>45612</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13939,7 +13939,7 @@
         <v>45457</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14012,7 +14012,7 @@
         <v>44853</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14085,7 +14085,7 @@
         <v>45384</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14158,7 +14158,7 @@
         <v>45051</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14231,7 +14231,7 @@
         <v>45317</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14304,7 +14304,7 @@
         <v>45529</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14377,7 +14377,7 @@
         <v>44986</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14455,7 +14455,7 @@
         <v>45089</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14528,7 +14528,7 @@
         <v>45251</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14601,7 +14601,7 @@
         <v>45947</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14674,7 +14674,7 @@
         <v>44942</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14747,7 +14747,7 @@
         <v>45916</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14825,7 +14825,7 @@
         <v>45952</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14898,7 +14898,7 @@
         <v>45700</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14971,7 +14971,7 @@
         <v>45653</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15044,7 +15044,7 @@
         <v>46184</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15117,7 +15117,7 @@
         <v>45303</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15190,7 +15190,7 @@
         <v>45211</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15263,7 +15263,7 @@
         <v>45010</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15336,7 +15336,7 @@
         <v>46184</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15409,7 +15409,7 @@
         <v>45959</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15482,7 +15482,7 @@
         <v>45707</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15555,7 +15555,7 @@
         <v>45595</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15628,7 +15628,7 @@
         <v>45271</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15701,7 +15701,7 @@
         <v>45547</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15774,7 +15774,7 @@
         <v>45966</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15847,7 +15847,7 @@
         <v>44865</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15920,7 +15920,7 @@
         <v>45966</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15993,7 +15993,7 @@
         <v>45244</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16066,7 +16066,7 @@
         <v>45228</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16139,7 +16139,7 @@
         <v>45252</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16212,7 +16212,7 @@
         <v>44922</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16285,7 +16285,7 @@
         <v>45966</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16358,7 +16358,7 @@
         <v>45680</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16431,7 +16431,7 @@
         <v>45967</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16504,7 +16504,7 @@
         <v>45792</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16577,7 +16577,7 @@
         <v>45309</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16650,7 +16650,7 @@
         <v>45969</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16723,7 +16723,7 @@
         <v>45969</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16796,7 +16796,7 @@
         <v>45215</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16869,7 +16869,7 @@
         <v>45303</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16942,7 +16942,7 @@
         <v>46190</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17020,7 +17020,7 @@
         <v>44897</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17093,7 +17093,7 @@
         <v>46198</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17166,7 +17166,7 @@
         <v>45211</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17239,7 +17239,7 @@
         <v>46198</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17312,7 +17312,7 @@
         <v>45589</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17385,7 +17385,7 @@
         <v>46198</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17458,7 +17458,7 @@
         <v>46198</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17531,7 +17531,7 @@
         <v>45103</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17604,7 +17604,7 @@
         <v>44777</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17677,7 +17677,7 @@
         <v>45653</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17750,7 +17750,7 @@
         <v>46202</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17823,7 +17823,7 @@
         <v>46204</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17896,7 +17896,7 @@
         <v>46204</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17969,7 +17969,7 @@
         <v>45706</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18042,7 +18042,7 @@
         <v>46204</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18115,7 +18115,7 @@
         <v>45443</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18188,7 +18188,7 @@
         <v>45734</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18261,7 +18261,7 @@
         <v>46206</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18334,7 +18334,7 @@
         <v>46204</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18407,7 +18407,7 @@
         <v>46204</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18480,7 +18480,7 @@
         <v>46204</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18553,7 +18553,7 @@
         <v>46204</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18626,7 +18626,7 @@
         <v>46206</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18699,7 +18699,7 @@
         <v>45533</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18772,7 +18772,7 @@
         <v>44921</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18845,7 +18845,7 @@
         <v>44962</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18918,7 +18918,7 @@
         <v>45986</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18996,7 +18996,7 @@
         <v>45378</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19069,7 +19069,7 @@
         <v>44817</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19142,7 +19142,7 @@
         <v>45759</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19215,7 +19215,7 @@
         <v>45314</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19288,7 +19288,7 @@
         <v>44973</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19361,7 +19361,7 @@
         <v>45589</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19434,7 +19434,7 @@
         <v>45992</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19512,7 +19512,7 @@
         <v>45992</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19590,7 +19590,7 @@
         <v>45992</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19668,7 +19668,7 @@
         <v>45992</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19746,7 +19746,7 @@
         <v>46216</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19824,7 +19824,7 @@
         <v>45457</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19897,7 +19897,7 @@
         <v>45457</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19970,7 +19970,7 @@
         <v>46216</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20048,7 +20048,7 @@
         <v>46216</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20126,7 +20126,7 @@
         <v>45567</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20199,7 +20199,7 @@
         <v>45140</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20272,7 +20272,7 @@
         <v>46216</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20350,7 +20350,7 @@
         <v>46216</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20428,7 +20428,7 @@
         <v>46216</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20506,7 +20506,7 @@
         <v>45315</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20579,7 +20579,7 @@
         <v>44928</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20652,7 +20652,7 @@
         <v>45209</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20725,7 +20725,7 @@
         <v>46000</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20803,7 +20803,7 @@
         <v>45680</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20876,7 +20876,7 @@
         <v>45663</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20949,7 +20949,7 @@
         <v>45776</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21022,7 +21022,7 @@
         <v>46227</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21095,7 +21095,7 @@
         <v>46005</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21168,7 +21168,7 @@
         <v>46226</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21241,7 +21241,7 @@
         <v>45781</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21314,7 +21314,7 @@
         <v>46227</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21387,7 +21387,7 @@
         <v>46226</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21460,7 +21460,7 @@
         <v>46226</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21533,7 +21533,7 @@
         <v>45624</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21606,7 +21606,7 @@
         <v>46280</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21679,7 +21679,7 @@
         <v>45638</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21752,7 +21752,7 @@
         <v>45407</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21825,7 +21825,7 @@
         <v>45527</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21898,7 +21898,7 @@
         <v>45719</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21971,7 +21971,7 @@
         <v>45812</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22044,7 +22044,7 @@
         <v>46279</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22117,7 +22117,7 @@
         <v>46234</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22195,7 +22195,7 @@
         <v>46016</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22268,7 +22268,7 @@
         <v>46240</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22346,7 +22346,7 @@
         <v>46240</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22424,7 +22424,7 @@
         <v>46240</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22502,7 +22502,7 @@
         <v>46035</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22575,7 +22575,7 @@
         <v>44582</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22648,7 +22648,7 @@
         <v>46038</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22721,7 +22721,7 @@
         <v>46037</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22794,7 +22794,7 @@
         <v>46287</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22867,7 +22867,7 @@
         <v>46092</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22940,7 +22940,7 @@
         <v>46287</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23013,7 +23013,7 @@
         <v>45911</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23086,7 +23086,7 @@
         <v>46066</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23159,7 +23159,7 @@
         <v>46245</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23232,7 +23232,7 @@
         <v>46283</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23305,7 +23305,7 @@
         <v>46287</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23378,7 +23378,7 @@
         <v>45589</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23451,7 +23451,7 @@
         <v>45799</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23524,7 +23524,7 @@
         <v>45460</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23597,7 +23597,7 @@
         <v>46245</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23670,7 +23670,7 @@
         <v>45405</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23743,7 +23743,7 @@
         <v>46045</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23816,7 +23816,7 @@
         <v>45702</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23889,7 +23889,7 @@
         <v>45663</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23962,7 +23962,7 @@
         <v>46247</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24035,7 +24035,7 @@
         <v>46168</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24108,7 +24108,7 @@
         <v>44511</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24181,7 +24181,7 @@
         <v>44511</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24254,7 +24254,7 @@
         <v>46247</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24327,7 +24327,7 @@
         <v>46052</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24400,7 +24400,7 @@
         <v>46154</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24473,7 +24473,7 @@
         <v>46052</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24546,7 +24546,7 @@
         <v>46246</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24619,7 +24619,7 @@
         <v>46287</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24692,7 +24692,7 @@
         <v>46287</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24765,7 +24765,7 @@
         <v>46290</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24838,7 +24838,7 @@
         <v>45804</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24911,7 +24911,7 @@
         <v>46030</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24984,7 +24984,7 @@
         <v>46290</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25057,7 +25057,7 @@
         <v>46287</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25130,7 +25130,7 @@
         <v>45916</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25203,7 +25203,7 @@
         <v>46248</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25276,7 +25276,7 @@
         <v>46061</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25349,7 +25349,7 @@
         <v>46294</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25422,7 +25422,7 @@
         <v>44942</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25495,7 +25495,7 @@
         <v>46294</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25568,7 +25568,7 @@
         <v>46294</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25641,7 +25641,7 @@
         <v>46063</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25714,7 +25714,7 @@
         <v>45548</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25787,7 +25787,7 @@
         <v>45818</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25860,7 +25860,7 @@
         <v>45695</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25933,7 +25933,7 @@
         <v>46065</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26006,7 +26006,7 @@
         <v>46293</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26084,7 +26084,7 @@
         <v>46251</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26162,7 +26162,7 @@
         <v>46248</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26235,7 +26235,7 @@
         <v>46251</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26308,7 +26308,7 @@
         <v>46295</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26381,7 +26381,7 @@
         <v>46076</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26454,7 +26454,7 @@
         <v>45827</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26527,7 +26527,7 @@
         <v>46295</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26600,7 +26600,7 @@
         <v>46251</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26673,7 +26673,7 @@
         <v>45335</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26746,7 +26746,7 @@
         <v>45441</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26819,7 +26819,7 @@
         <v>45334</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26892,7 +26892,7 @@
         <v>45834</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -26965,7 +26965,7 @@
         <v>45835</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27038,7 +27038,7 @@
         <v>45113</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27111,7 +27111,7 @@
         <v>44641</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27184,7 +27184,7 @@
         <v>46093</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27257,7 +27257,7 @@
         <v>45839</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27330,7 +27330,7 @@
         <v>46300</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27403,7 +27403,7 @@
         <v>44545</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27476,7 +27476,7 @@
         <v>46257</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27549,7 +27549,7 @@
         <v>45169</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27622,7 +27622,7 @@
         <v>45612</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27695,7 +27695,7 @@
         <v>45612</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27768,7 +27768,7 @@
         <v>45842</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27841,7 +27841,7 @@
         <v>44943</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -27914,7 +27914,7 @@
         <v>46254</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -27987,7 +27987,7 @@
         <v>46254</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28060,7 +28060,7 @@
         <v>45842</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28133,7 +28133,7 @@
         <v>45842</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28206,7 +28206,7 @@
         <v>45841</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28279,7 +28279,7 @@
         <v>45529</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28352,7 +28352,7 @@
         <v>45846</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28425,7 +28425,7 @@
         <v>46155</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28498,7 +28498,7 @@
         <v>45845</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28571,7 +28571,7 @@
         <v>46105</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28649,7 +28649,7 @@
         <v>46105</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28727,7 +28727,7 @@
         <v>46105</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -28805,7 +28805,7 @@
         <v>46105</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -28883,7 +28883,7 @@
         <v>46105</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -28961,7 +28961,7 @@
         <v>46105</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29039,7 +29039,7 @@
         <v>46105</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29117,7 +29117,7 @@
         <v>46107</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29190,7 +29190,7 @@
         <v>46106</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29268,7 +29268,7 @@
         <v>45726</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29341,7 +29341,7 @@
         <v>45726</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29414,7 +29414,7 @@
         <v>45854</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29487,7 +29487,7 @@
         <v>45763</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29560,7 +29560,7 @@
         <v>45763</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29633,7 +29633,7 @@
         <v>44930</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -29706,7 +29706,7 @@
         <v>45581</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -29779,7 +29779,7 @@
         <v>46108</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -29852,7 +29852,7 @@
         <v>45819</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -29925,7 +29925,7 @@
         <v>44979</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -29998,7 +29998,7 @@
         <v>46108</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30071,7 +30071,7 @@
         <v>46258</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30144,7 +30144,7 @@
         <v>45812</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30217,7 +30217,7 @@
         <v>46302</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30290,7 +30290,7 @@
         <v>46258</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30363,7 +30363,7 @@
         <v>45631</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30436,7 +30436,7 @@
         <v>45373</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30514,7 +30514,7 @@
         <v>45373</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30592,7 +30592,7 @@
         <v>45435</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30665,7 +30665,7 @@
         <v>45435</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -30738,7 +30738,7 @@
         <v>45435</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -30811,7 +30811,7 @@
         <v>45726</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -30884,7 +30884,7 @@
         <v>44853</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -30957,7 +30957,7 @@
         <v>45867</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31030,7 +31030,7 @@
         <v>45581</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31103,7 +31103,7 @@
         <v>46303</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31176,7 +31176,7 @@
         <v>44994</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31249,7 +31249,7 @@
         <v>44994</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31322,7 +31322,7 @@
         <v>44531</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31395,7 +31395,7 @@
         <v>46125</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31468,7 +31468,7 @@
         <v>46261</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31541,7 +31541,7 @@
         <v>46303</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31614,7 +31614,7 @@
         <v>45373</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -31692,7 +31692,7 @@
         <v>46307</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -31765,7 +31765,7 @@
         <v>46128</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -31838,7 +31838,7 @@
         <v>45476</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -31911,7 +31911,7 @@
         <v>46307</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -31984,7 +31984,7 @@
         <v>44911</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32057,7 +32057,7 @@
         <v>46307</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32130,7 +32130,7 @@
         <v>45538</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32203,7 +32203,7 @@
         <v>46307</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32276,7 +32276,7 @@
         <v>45175</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32349,7 +32349,7 @@
         <v>44503</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32422,7 +32422,7 @@
         <v>44859</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32495,7 +32495,7 @@
         <v>45167</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32568,7 +32568,7 @@
         <v>44914</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -32641,7 +32641,7 @@
         <v>45574</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -32714,7 +32714,7 @@
         <v>45559</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -32787,7 +32787,7 @@
         <v>45938</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -32860,7 +32860,7 @@
         <v>45722</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -32933,7 +32933,7 @@
         <v>45835</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33006,7 +33006,7 @@
         <v>45531</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33084,7 +33084,7 @@
         <v>46267</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33157,7 +33157,7 @@
         <v>45681</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33230,7 +33230,7 @@
         <v>45911</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33303,7 +33303,7 @@
         <v>45887</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33376,7 +33376,7 @@
         <v>45883</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33449,7 +33449,7 @@
         <v>45817</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33522,7 +33522,7 @@
         <v>45733</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33595,7 +33595,7 @@
         <v>46268</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -33668,7 +33668,7 @@
         <v>45537</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -33741,7 +33741,7 @@
         <v>45531</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -33814,7 +33814,7 @@
         <v>46314</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -33887,7 +33887,7 @@
         <v>46000</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -33965,7 +33965,7 @@
         <v>45328</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34038,7 +34038,7 @@
         <v>46314</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34111,7 +34111,7 @@
         <v>45687</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34184,7 +34184,7 @@
         <v>46313</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34257,7 +34257,7 @@
         <v>45543</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34330,7 +34330,7 @@
         <v>45513</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34403,7 +34403,7 @@
         <v>45930</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34476,7 +34476,7 @@
         <v>45630</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34549,7 +34549,7 @@
         <v>45554</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -34622,7 +34622,7 @@
         <v>45564</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -34695,7 +34695,7 @@
         <v>45254</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -34768,7 +34768,7 @@
         <v>44994</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -34841,7 +34841,7 @@
         <v>46262</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -34914,7 +34914,7 @@
         <v>46140</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -34992,7 +34992,7 @@
         <v>45446</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35065,7 +35065,7 @@
         <v>46147</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35138,7 +35138,7 @@
         <v>46141</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35211,7 +35211,7 @@
         <v>45170</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35284,7 +35284,7 @@
         <v>45594</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35357,7 +35357,7 @@
         <v>45588</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35430,7 +35430,7 @@
         <v>45462</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35503,7 +35503,7 @@
         <v>45258</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -35576,7 +35576,7 @@
         <v>46155</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -35649,7 +35649,7 @@
         <v>45578</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -35722,7 +35722,7 @@
         <v>45308</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -35795,7 +35795,7 @@
         <v>45372</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -35868,7 +35868,7 @@
         <v>45629</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -35941,7 +35941,7 @@
         <v>45145</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36014,7 +36014,7 @@
         <v>45680</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36087,7 +36087,7 @@
         <v>45469</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36165,7 +36165,7 @@
         <v>45078</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36238,7 +36238,7 @@
         <v>45715</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36311,7 +36311,7 @@
         <v>45631</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36384,7 +36384,7 @@
         <v>45051</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36457,7 +36457,7 @@
         <v>45154</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36530,7 +36530,7 @@
         <v>44760</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -36603,7 +36603,7 @@
         <v>45610</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -36676,7 +36676,7 @@
         <v>44526</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -36749,7 +36749,7 @@
         <v>45076</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -36822,7 +36822,7 @@
         <v>45076</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -36895,7 +36895,7 @@
         <v>44826</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -36968,7 +36968,7 @@
         <v>45062</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37041,7 +37041,7 @@
         <v>44496</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37114,7 +37114,7 @@
         <v>44568</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37187,7 +37187,7 @@
         <v>45748</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37260,7 +37260,7 @@
         <v>45716</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37338,7 +37338,7 @@
         <v>45176</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37411,7 +37411,7 @@
         <v>44784</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -37489,7 +37489,7 @@
         <v>45348</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -37562,7 +37562,7 @@
         <v>45244</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -37635,7 +37635,7 @@
         <v>45735</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -37708,7 +37708,7 @@
         <v>45735</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -37781,7 +37781,7 @@
         <v>45273</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -37854,7 +37854,7 @@
         <v>45273</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -37927,7 +37927,7 @@
         <v>44865</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38000,7 +38000,7 @@
         <v>45078</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38073,7 +38073,7 @@
         <v>45113</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38146,7 +38146,7 @@
         <v>45180</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38219,7 +38219,7 @@
         <v>45583</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38292,7 +38292,7 @@
         <v>44529</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38365,7 +38365,7 @@
         <v>45090</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38438,7 +38438,7 @@
         <v>45133</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -38511,7 +38511,7 @@
         <v>44882</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -38584,7 +38584,7 @@
         <v>45467</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -38657,7 +38657,7 @@
         <v>44897</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -38730,7 +38730,7 @@
         <v>44858</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -38803,7 +38803,7 @@
         <v>45374</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -38876,7 +38876,7 @@
         <v>45433</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -38949,7 +38949,7 @@
         <v>44897</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39022,7 +39022,7 @@
         <v>45737</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39095,7 +39095,7 @@
         <v>44942</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39168,7 +39168,7 @@
         <v>45103</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39241,7 +39241,7 @@
         <v>45251</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39314,7 +39314,7 @@
         <v>45251</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39387,7 +39387,7 @@
         <v>45049</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39460,7 +39460,7 @@
         <v>44508</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -39533,7 +39533,7 @@
         <v>45566</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -39606,7 +39606,7 @@
         <v>45001</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -39679,7 +39679,7 @@
         <v>45352</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -39757,7 +39757,7 @@
         <v>44935</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -39830,7 +39830,7 @@
         <v>44992</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -39903,7 +39903,7 @@
         <v>45352</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -39981,7 +39981,7 @@
         <v>45092</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40054,7 +40054,7 @@
         <v>45006</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40132,7 +40132,7 @@
         <v>45092</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40205,7 +40205,7 @@
         <v>45166</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40278,7 +40278,7 @@
         <v>45376</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40351,7 +40351,7 @@
         <v>44942</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40424,7 +40424,7 @@
         <v>45015</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -40497,7 +40497,7 @@
         <v>44543</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -40570,7 +40570,7 @@
         <v>45155</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -40643,7 +40643,7 @@
         <v>45450</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -40716,7 +40716,7 @@
         <v>44523</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -40789,7 +40789,7 @@
         <v>45586</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -40862,7 +40862,7 @@
         <v>45615</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -40935,7 +40935,7 @@
         <v>44958</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41008,7 +41008,7 @@
         <v>45098</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41101,7 +41101,7 @@
         <v>45608</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41174,7 +41174,7 @@
         <v>45156</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41247,7 +41247,7 @@
         <v>45558</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41320,7 +41320,7 @@
         <v>45539</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41393,7 +41393,7 @@
         <v>45133</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41466,7 +41466,7 @@
         <v>45355</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -41539,7 +41539,7 @@
         <v>45355</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -41617,7 +41617,7 @@
         <v>44979</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -41690,7 +41690,7 @@
         <v>45189</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -41763,7 +41763,7 @@
         <v>45010</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -41836,7 +41836,7 @@
         <v>45539</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -41909,7 +41909,7 @@
         <v>45355</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -41987,7 +41987,7 @@
         <v>45720</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42060,7 +42060,7 @@
         <v>45462</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42133,7 +42133,7 @@
         <v>45049</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42206,7 +42206,7 @@
         <v>45706</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42279,7 +42279,7 @@
         <v>45282</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42352,7 +42352,7 @@
         <v>44686</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42425,7 +42425,7 @@
         <v>45350</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -42498,7 +42498,7 @@
         <v>45616</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -42571,7 +42571,7 @@
         <v>44636</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -42644,7 +42644,7 @@
         <v>45191</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -42717,7 +42717,7 @@
         <v>45716</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -42795,7 +42795,7 @@
         <v>44531</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -42868,7 +42868,7 @@
         <v>44587</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -42941,7 +42941,7 @@
         <v>45062</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43014,7 +43014,7 @@
         <v>45677</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43087,7 +43087,7 @@
         <v>45222</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43160,7 +43160,7 @@
         <v>44592</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43233,7 +43233,7 @@
         <v>45215</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43306,7 +43306,7 @@
         <v>45653</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43379,7 +43379,7 @@
         <v>44859</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43452,7 +43452,7 @@
         <v>44634</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -43525,7 +43525,7 @@
         <v>44861</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -43598,7 +43598,7 @@
         <v>45625</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -43671,7 +43671,7 @@
         <v>45716</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -43744,7 +43744,7 @@
         <v>44698</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -43817,7 +43817,7 @@
         <v>45771</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -43890,7 +43890,7 @@
         <v>45240</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -43968,7 +43968,7 @@
         <v>45166</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44041,7 +44041,7 @@
         <v>45460</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44114,7 +44114,7 @@
         <v>45693</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44187,7 +44187,7 @@
         <v>45698</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44260,7 +44260,7 @@
         <v>45202</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44333,7 +44333,7 @@
         <v>45180</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44406,7 +44406,7 @@
         <v>45211</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44479,7 +44479,7 @@
         <v>45214</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -44552,7 +44552,7 @@
         <v>45175</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -44625,7 +44625,7 @@
         <v>45175</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -44698,7 +44698,7 @@
         <v>45187</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -44771,7 +44771,7 @@
         <v>45681</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -44844,7 +44844,7 @@
         <v>45233</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -44917,7 +44917,7 @@
         <v>45233</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -44990,7 +44990,7 @@
         <v>45612</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45063,7 +45063,7 @@
         <v>45770</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45136,7 +45136,7 @@
         <v>45246</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45209,7 +45209,7 @@
         <v>45679</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45282,7 +45282,7 @@
         <v>45531</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45355,7 +45355,7 @@
         <v>45352</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45433,7 +45433,7 @@
         <v>45250</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -45506,7 +45506,7 @@
         <v>45250</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -45579,7 +45579,7 @@
         <v>45253</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -45652,7 +45652,7 @@
         <v>45421</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -45725,7 +45725,7 @@
         <v>45211</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -45798,7 +45798,7 @@
         <v>45084</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -45871,7 +45871,7 @@
         <v>44496</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -45944,7 +45944,7 @@
         <v>45051</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46017,7 +46017,7 @@
         <v>45268</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46090,7 +46090,7 @@
         <v>45469</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46163,7 +46163,7 @@
         <v>45175</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46236,7 +46236,7 @@
         <v>44876</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46309,7 +46309,7 @@
         <v>45440</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46382,7 +46382,7 @@
         <v>44921</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -46455,7 +46455,7 @@
         <v>45734</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -46528,7 +46528,7 @@
         <v>45608</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -46601,7 +46601,7 @@
         <v>45546</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -46674,7 +46674,7 @@
         <v>44621</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -46747,7 +46747,7 @@
         <v>44858</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -46820,7 +46820,7 @@
         <v>45187</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -46893,7 +46893,7 @@
         <v>45412</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -46966,7 +46966,7 @@
         <v>45414</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47039,7 +47039,7 @@
         <v>44992</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47112,7 +47112,7 @@
         <v>44610</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47185,7 +47185,7 @@
         <v>44992</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47258,7 +47258,7 @@
         <v>44634</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -47331,7 +47331,7 @@
         <v>44658</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -47404,7 +47404,7 @@
         <v>44621</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -47477,7 +47477,7 @@
         <v>44607</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -47550,7 +47550,7 @@
         <v>44733</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -47628,7 +47628,7 @@
         <v>45302</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -47701,7 +47701,7 @@
         <v>45476</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -47774,7 +47774,7 @@
         <v>45649</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -47847,7 +47847,7 @@
         <v>45728</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -47920,7 +47920,7 @@
         <v>45953</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -47993,7 +47993,7 @@
         <v>45967</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48066,7 +48066,7 @@
         <v>46010</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48139,7 +48139,7 @@
         <v>46010</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -48212,7 +48212,7 @@
         <v>46029</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -48290,7 +48290,7 @@
         <v>46079</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -48363,7 +48363,7 @@
         <v>46094</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -48436,7 +48436,7 @@
         <v>46119</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -48509,7 +48509,7 @@
         <v>46182</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>

--- a/Översikt ÄLMHULT.xlsx
+++ b/Översikt ÄLMHULT.xlsx
@@ -601,7 +601,7 @@
         <v>46209</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>45786</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
         <v>46041</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
         <v>45945</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>44883</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>45215</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>45645</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>46043</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
         <v>46211</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>46171</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         <v>44883</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>45818</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>45183</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2022,7 +2022,7 @@
         <v>44889</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         <v>44830</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2238,7 +2238,7 @@
         <v>45012</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
         <v>45050</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2455,7 +2455,7 @@
         <v>45908</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
         <v>45560</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
         <v>45932</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2779,7 +2779,7 @@
         <v>45386</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
         <v>45280</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2989,7 +2989,7 @@
         <v>46204</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3094,7 +3094,7 @@
         <v>45888</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3199,7 +3199,7 @@
         <v>45763</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3304,7 +3304,7 @@
         <v>45856</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
         <v>46290</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3518,7 +3518,7 @@
         <v>45769</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
         <v>45631</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3728,7 +3728,7 @@
         <v>45218</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3833,7 +3833,7 @@
         <v>44882</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
         <v>45719</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         <v>44869</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4148,7 +4148,7 @@
         <v>45786</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4253,7 +4253,7 @@
         <v>44609</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4326,7 +4326,7 @@
         <v>44525</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4399,7 +4399,7 @@
         <v>44785</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4472,7 +4472,7 @@
         <v>44785</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4545,7 +4545,7 @@
         <v>44785</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4618,7 +4618,7 @@
         <v>44802</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4691,7 +4691,7 @@
         <v>44802</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4764,7 +4764,7 @@
         <v>44785</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4837,7 +4837,7 @@
         <v>44749</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4910,7 +4910,7 @@
         <v>44798</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4983,7 +4983,7 @@
         <v>44523</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5056,7 +5056,7 @@
         <v>44515</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5129,7 +5129,7 @@
         <v>44503</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5202,7 +5202,7 @@
         <v>44503</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5275,7 +5275,7 @@
         <v>44785</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5348,7 +5348,7 @@
         <v>44665</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5426,7 +5426,7 @@
         <v>44846</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5499,7 +5499,7 @@
         <v>44498</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5572,7 +5572,7 @@
         <v>44847</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5645,7 +5645,7 @@
         <v>44690</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5718,7 +5718,7 @@
         <v>44812</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5791,7 +5791,7 @@
         <v>44504</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5864,7 +5864,7 @@
         <v>44602</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5937,7 +5937,7 @@
         <v>44512</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6010,7 +6010,7 @@
         <v>44621</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6083,7 +6083,7 @@
         <v>44609</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6156,7 +6156,7 @@
         <v>44721</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6229,7 +6229,7 @@
         <v>44587</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6307,7 +6307,7 @@
         <v>44802</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6380,7 +6380,7 @@
         <v>44509</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6453,7 +6453,7 @@
         <v>44739</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6526,7 +6526,7 @@
         <v>44551</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6599,7 +6599,7 @@
         <v>44733</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6672,7 +6672,7 @@
         <v>44621</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6745,7 +6745,7 @@
         <v>44854</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6818,7 +6818,7 @@
         <v>44854</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6891,7 +6891,7 @@
         <v>44680</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6964,7 +6964,7 @@
         <v>44690</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7037,7 +7037,7 @@
         <v>44690</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7110,7 +7110,7 @@
         <v>44524</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7183,7 +7183,7 @@
         <v>44865</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7256,7 +7256,7 @@
         <v>44496</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7329,7 +7329,7 @@
         <v>44721</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7402,7 +7402,7 @@
         <v>44525</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         <v>44685</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7548,7 +7548,7 @@
         <v>44596</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7621,7 +7621,7 @@
         <v>44643</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7694,7 +7694,7 @@
         <v>44510</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7767,7 +7767,7 @@
         <v>44522</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7840,7 +7840,7 @@
         <v>44636</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7913,7 +7913,7 @@
         <v>44657</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7986,7 +7986,7 @@
         <v>44831</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8059,7 +8059,7 @@
         <v>44831</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8132,7 +8132,7 @@
         <v>45286</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8205,7 +8205,7 @@
         <v>45888</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8278,7 +8278,7 @@
         <v>45575</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8351,7 +8351,7 @@
         <v>45887</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8424,7 +8424,7 @@
         <v>44816</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8497,7 +8497,7 @@
         <v>45215</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8570,7 +8570,7 @@
         <v>45181</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8643,7 +8643,7 @@
         <v>45637</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8716,7 +8716,7 @@
         <v>44942</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8789,7 +8789,7 @@
         <v>45222</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8862,7 +8862,7 @@
         <v>45222</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8935,7 +8935,7 @@
         <v>45268</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9008,7 +9008,7 @@
         <v>45716</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9081,7 +9081,7 @@
         <v>45085</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9154,7 +9154,7 @@
         <v>45497</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9227,7 +9227,7 @@
         <v>44942</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9300,7 +9300,7 @@
         <v>44860</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9373,7 +9373,7 @@
         <v>45187</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9446,7 +9446,7 @@
         <v>45290</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9519,7 +9519,7 @@
         <v>45609</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9592,7 +9592,7 @@
         <v>45898</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9665,7 +9665,7 @@
         <v>45217</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9738,7 +9738,7 @@
         <v>44998</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9816,7 +9816,7 @@
         <v>45897</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9889,7 +9889,7 @@
         <v>45244</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9962,7 +9962,7 @@
         <v>45211</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10035,7 +10035,7 @@
         <v>45348</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10108,7 +10108,7 @@
         <v>45111</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10181,7 +10181,7 @@
         <v>45401</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10254,7 +10254,7 @@
         <v>44526</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10327,7 +10327,7 @@
         <v>44855</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10400,7 +10400,7 @@
         <v>45141</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10473,7 +10473,7 @@
         <v>45359</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10546,7 +10546,7 @@
         <v>45748</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10619,7 +10619,7 @@
         <v>45884</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10692,7 +10692,7 @@
         <v>45012</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10765,7 +10765,7 @@
         <v>46076</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10838,7 +10838,7 @@
         <v>44687</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10911,7 +10911,7 @@
         <v>45818</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10984,7 +10984,7 @@
         <v>45081</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11057,7 +11057,7 @@
         <v>45068</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11130,7 +11130,7 @@
         <v>45916</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11203,7 +11203,7 @@
         <v>45915</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11281,7 +11281,7 @@
         <v>45917</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11359,7 +11359,7 @@
         <v>45917</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11437,7 +11437,7 @@
         <v>45010</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11510,7 +11510,7 @@
         <v>45917</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11588,7 +11588,7 @@
         <v>45728</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11661,7 +11661,7 @@
         <v>45048</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11734,7 +11734,7 @@
         <v>45177</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11807,7 +11807,7 @@
         <v>45042</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11880,7 +11880,7 @@
         <v>45273</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11953,7 +11953,7 @@
         <v>45391</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12026,7 +12026,7 @@
         <v>45929</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12099,7 +12099,7 @@
         <v>45946</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12172,7 +12172,7 @@
         <v>45930</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12245,7 +12245,7 @@
         <v>45911</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12318,7 +12318,7 @@
         <v>45134</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12391,7 +12391,7 @@
         <v>45930</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12464,7 +12464,7 @@
         <v>44743</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12537,7 +12537,7 @@
         <v>45469</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12615,7 +12615,7 @@
         <v>45440</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12688,7 +12688,7 @@
         <v>44977</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12761,7 +12761,7 @@
         <v>45373</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12839,7 +12839,7 @@
         <v>45373</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12917,7 +12917,7 @@
         <v>45078</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12990,7 +12990,7 @@
         <v>45078</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13063,7 +13063,7 @@
         <v>45628</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13136,7 +13136,7 @@
         <v>45311</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13209,7 +13209,7 @@
         <v>45061</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13282,7 +13282,7 @@
         <v>45638</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13355,7 +13355,7 @@
         <v>45944</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13428,7 +13428,7 @@
         <v>45638</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13501,7 +13501,7 @@
         <v>45090</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13574,7 +13574,7 @@
         <v>45254</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13647,7 +13647,7 @@
         <v>45539</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13720,7 +13720,7 @@
         <v>45217</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13793,7 +13793,7 @@
         <v>45945</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13866,7 +13866,7 @@
         <v>45612</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13939,7 +13939,7 @@
         <v>45457</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14012,7 +14012,7 @@
         <v>44853</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14085,7 +14085,7 @@
         <v>45384</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14158,7 +14158,7 @@
         <v>45051</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14231,7 +14231,7 @@
         <v>45317</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14304,7 +14304,7 @@
         <v>45529</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14377,7 +14377,7 @@
         <v>44986</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14455,7 +14455,7 @@
         <v>45089</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14528,7 +14528,7 @@
         <v>45251</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14601,7 +14601,7 @@
         <v>45947</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14674,7 +14674,7 @@
         <v>44942</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14747,7 +14747,7 @@
         <v>45916</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14825,7 +14825,7 @@
         <v>45952</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14898,7 +14898,7 @@
         <v>45700</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14971,7 +14971,7 @@
         <v>45653</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15044,7 +15044,7 @@
         <v>46184</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15117,7 +15117,7 @@
         <v>45303</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15190,7 +15190,7 @@
         <v>45211</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15263,7 +15263,7 @@
         <v>45010</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15336,7 +15336,7 @@
         <v>46184</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15409,7 +15409,7 @@
         <v>45959</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15482,7 +15482,7 @@
         <v>45707</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15555,7 +15555,7 @@
         <v>45595</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15628,7 +15628,7 @@
         <v>45271</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15701,7 +15701,7 @@
         <v>45547</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15774,7 +15774,7 @@
         <v>45966</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15847,7 +15847,7 @@
         <v>44865</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15920,7 +15920,7 @@
         <v>45966</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15993,7 +15993,7 @@
         <v>45244</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16066,7 +16066,7 @@
         <v>45228</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16139,7 +16139,7 @@
         <v>45252</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16212,7 +16212,7 @@
         <v>44922</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16285,7 +16285,7 @@
         <v>45966</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16358,7 +16358,7 @@
         <v>45680</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16431,7 +16431,7 @@
         <v>45967</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16504,7 +16504,7 @@
         <v>45792</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16577,7 +16577,7 @@
         <v>45309</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16650,7 +16650,7 @@
         <v>45969</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16723,7 +16723,7 @@
         <v>45969</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16796,7 +16796,7 @@
         <v>45215</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16869,7 +16869,7 @@
         <v>45303</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16942,7 +16942,7 @@
         <v>46190</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17020,7 +17020,7 @@
         <v>44897</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17093,7 +17093,7 @@
         <v>46198</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17166,7 +17166,7 @@
         <v>45211</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17239,7 +17239,7 @@
         <v>46198</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17312,7 +17312,7 @@
         <v>45589</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17385,7 +17385,7 @@
         <v>46198</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17458,7 +17458,7 @@
         <v>46198</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17531,7 +17531,7 @@
         <v>45103</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17604,7 +17604,7 @@
         <v>44777</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17677,7 +17677,7 @@
         <v>45653</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17750,7 +17750,7 @@
         <v>46202</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17823,7 +17823,7 @@
         <v>46204</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17896,7 +17896,7 @@
         <v>46204</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17969,7 +17969,7 @@
         <v>45706</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18042,7 +18042,7 @@
         <v>46204</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18115,7 +18115,7 @@
         <v>45443</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18188,7 +18188,7 @@
         <v>45734</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18261,7 +18261,7 @@
         <v>46206</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18334,7 +18334,7 @@
         <v>46204</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18407,7 +18407,7 @@
         <v>46204</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18480,7 +18480,7 @@
         <v>46204</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18553,7 +18553,7 @@
         <v>46204</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18626,7 +18626,7 @@
         <v>46206</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18699,7 +18699,7 @@
         <v>45533</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18772,7 +18772,7 @@
         <v>44921</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18845,7 +18845,7 @@
         <v>44962</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18918,7 +18918,7 @@
         <v>45986</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18996,7 +18996,7 @@
         <v>45378</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19069,7 +19069,7 @@
         <v>44817</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19142,7 +19142,7 @@
         <v>45759</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19215,7 +19215,7 @@
         <v>45314</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19288,7 +19288,7 @@
         <v>44973</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19361,7 +19361,7 @@
         <v>45589</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19434,7 +19434,7 @@
         <v>45992</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19512,7 +19512,7 @@
         <v>45992</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19590,7 +19590,7 @@
         <v>45992</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19668,7 +19668,7 @@
         <v>45992</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19746,7 +19746,7 @@
         <v>46216</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19824,7 +19824,7 @@
         <v>45457</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19897,7 +19897,7 @@
         <v>45457</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19970,7 +19970,7 @@
         <v>46216</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20048,7 +20048,7 @@
         <v>46216</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20126,7 +20126,7 @@
         <v>45567</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20199,7 +20199,7 @@
         <v>45140</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20272,7 +20272,7 @@
         <v>46216</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20350,7 +20350,7 @@
         <v>46216</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20428,7 +20428,7 @@
         <v>46216</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20506,7 +20506,7 @@
         <v>45315</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20579,7 +20579,7 @@
         <v>44928</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20652,7 +20652,7 @@
         <v>45209</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20725,7 +20725,7 @@
         <v>46000</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20803,7 +20803,7 @@
         <v>45680</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20876,7 +20876,7 @@
         <v>45663</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20949,7 +20949,7 @@
         <v>45776</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21022,7 +21022,7 @@
         <v>46227</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21095,7 +21095,7 @@
         <v>46005</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21168,7 +21168,7 @@
         <v>46226</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21241,7 +21241,7 @@
         <v>45781</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21314,7 +21314,7 @@
         <v>46227</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21387,7 +21387,7 @@
         <v>46226</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21460,7 +21460,7 @@
         <v>46226</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21533,7 +21533,7 @@
         <v>45624</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21606,7 +21606,7 @@
         <v>46280</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21679,7 +21679,7 @@
         <v>45638</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21752,7 +21752,7 @@
         <v>45407</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21825,7 +21825,7 @@
         <v>45527</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21898,7 +21898,7 @@
         <v>45719</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21971,7 +21971,7 @@
         <v>45812</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22044,7 +22044,7 @@
         <v>46279</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22117,7 +22117,7 @@
         <v>46234</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22195,7 +22195,7 @@
         <v>46016</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22268,7 +22268,7 @@
         <v>46240</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22346,7 +22346,7 @@
         <v>46240</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22424,7 +22424,7 @@
         <v>46240</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22502,7 +22502,7 @@
         <v>46035</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22575,7 +22575,7 @@
         <v>44582</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22648,7 +22648,7 @@
         <v>46038</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22721,7 +22721,7 @@
         <v>46037</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22794,7 +22794,7 @@
         <v>46287</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22867,7 +22867,7 @@
         <v>46092</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22940,7 +22940,7 @@
         <v>46287</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23013,7 +23013,7 @@
         <v>45911</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23086,7 +23086,7 @@
         <v>46066</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23159,7 +23159,7 @@
         <v>46245</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23232,7 +23232,7 @@
         <v>46283</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23305,7 +23305,7 @@
         <v>46287</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23378,7 +23378,7 @@
         <v>45589</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23451,7 +23451,7 @@
         <v>45799</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23524,7 +23524,7 @@
         <v>45460</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23597,7 +23597,7 @@
         <v>46245</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23670,7 +23670,7 @@
         <v>45405</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23743,7 +23743,7 @@
         <v>46045</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23816,7 +23816,7 @@
         <v>45702</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23889,7 +23889,7 @@
         <v>45663</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23962,7 +23962,7 @@
         <v>46247</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24035,7 +24035,7 @@
         <v>46168</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24108,7 +24108,7 @@
         <v>44511</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24181,7 +24181,7 @@
         <v>44511</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24254,7 +24254,7 @@
         <v>46247</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24327,7 +24327,7 @@
         <v>46052</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24400,7 +24400,7 @@
         <v>46154</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24473,7 +24473,7 @@
         <v>46052</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24546,7 +24546,7 @@
         <v>46246</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24619,7 +24619,7 @@
         <v>46287</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24692,7 +24692,7 @@
         <v>46287</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24765,7 +24765,7 @@
         <v>46290</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24838,7 +24838,7 @@
         <v>45804</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24911,7 +24911,7 @@
         <v>46030</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24984,7 +24984,7 @@
         <v>46290</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25057,7 +25057,7 @@
         <v>46287</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25130,7 +25130,7 @@
         <v>45916</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25203,7 +25203,7 @@
         <v>46248</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25276,7 +25276,7 @@
         <v>46061</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25349,7 +25349,7 @@
         <v>46294</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25422,7 +25422,7 @@
         <v>44942</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25495,7 +25495,7 @@
         <v>46294</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25568,7 +25568,7 @@
         <v>46294</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25641,7 +25641,7 @@
         <v>46063</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25714,7 +25714,7 @@
         <v>45548</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25787,7 +25787,7 @@
         <v>45818</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25860,7 +25860,7 @@
         <v>45695</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25933,7 +25933,7 @@
         <v>46065</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26006,7 +26006,7 @@
         <v>46293</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26084,7 +26084,7 @@
         <v>46251</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26162,7 +26162,7 @@
         <v>46248</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26235,7 +26235,7 @@
         <v>46251</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26308,7 +26308,7 @@
         <v>46295</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26381,7 +26381,7 @@
         <v>46076</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26454,7 +26454,7 @@
         <v>45827</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26527,7 +26527,7 @@
         <v>46295</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26600,7 +26600,7 @@
         <v>46251</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26673,7 +26673,7 @@
         <v>45335</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26746,7 +26746,7 @@
         <v>45441</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26819,7 +26819,7 @@
         <v>45334</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26892,7 +26892,7 @@
         <v>45834</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -26965,7 +26965,7 @@
         <v>45835</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27038,7 +27038,7 @@
         <v>45113</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27111,7 +27111,7 @@
         <v>44641</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27184,7 +27184,7 @@
         <v>46093</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27257,7 +27257,7 @@
         <v>45839</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27330,7 +27330,7 @@
         <v>46300</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27403,7 +27403,7 @@
         <v>44545</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27476,7 +27476,7 @@
         <v>46257</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27549,7 +27549,7 @@
         <v>45169</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27622,7 +27622,7 @@
         <v>45612</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27695,7 +27695,7 @@
         <v>45612</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27768,7 +27768,7 @@
         <v>45842</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27841,7 +27841,7 @@
         <v>44943</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -27914,7 +27914,7 @@
         <v>46254</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -27987,7 +27987,7 @@
         <v>46254</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28060,7 +28060,7 @@
         <v>45842</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28133,7 +28133,7 @@
         <v>45842</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28206,7 +28206,7 @@
         <v>45841</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28279,7 +28279,7 @@
         <v>45529</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28352,7 +28352,7 @@
         <v>45846</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28425,7 +28425,7 @@
         <v>46155</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28498,7 +28498,7 @@
         <v>45845</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28571,7 +28571,7 @@
         <v>46105</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28649,7 +28649,7 @@
         <v>46105</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28727,7 +28727,7 @@
         <v>46105</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -28805,7 +28805,7 @@
         <v>46105</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -28883,7 +28883,7 @@
         <v>46105</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -28961,7 +28961,7 @@
         <v>46105</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29039,7 +29039,7 @@
         <v>46105</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29117,7 +29117,7 @@
         <v>46107</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29190,7 +29190,7 @@
         <v>46106</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29268,7 +29268,7 @@
         <v>45726</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29341,7 +29341,7 @@
         <v>45726</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29414,7 +29414,7 @@
         <v>45854</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29487,7 +29487,7 @@
         <v>45763</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29560,7 +29560,7 @@
         <v>45763</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29633,7 +29633,7 @@
         <v>44930</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -29706,7 +29706,7 @@
         <v>45581</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -29779,7 +29779,7 @@
         <v>46108</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -29852,7 +29852,7 @@
         <v>45819</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -29925,7 +29925,7 @@
         <v>44979</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -29998,7 +29998,7 @@
         <v>46108</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30071,7 +30071,7 @@
         <v>46258</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30144,7 +30144,7 @@
         <v>45812</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30217,7 +30217,7 @@
         <v>46302</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30290,7 +30290,7 @@
         <v>46258</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30363,7 +30363,7 @@
         <v>45631</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30436,7 +30436,7 @@
         <v>45373</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30514,7 +30514,7 @@
         <v>45373</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30592,7 +30592,7 @@
         <v>45435</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30665,7 +30665,7 @@
         <v>45435</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -30738,7 +30738,7 @@
         <v>45435</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -30811,7 +30811,7 @@
         <v>45726</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -30884,7 +30884,7 @@
         <v>44853</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -30957,7 +30957,7 @@
         <v>45867</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31030,7 +31030,7 @@
         <v>45581</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31103,7 +31103,7 @@
         <v>46303</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31176,7 +31176,7 @@
         <v>44994</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31249,7 +31249,7 @@
         <v>44994</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31322,7 +31322,7 @@
         <v>44531</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31395,7 +31395,7 @@
         <v>46125</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31468,7 +31468,7 @@
         <v>46261</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31541,7 +31541,7 @@
         <v>46303</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31614,7 +31614,7 @@
         <v>45373</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -31692,7 +31692,7 @@
         <v>46307</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -31765,7 +31765,7 @@
         <v>46128</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -31838,7 +31838,7 @@
         <v>45476</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -31911,7 +31911,7 @@
         <v>46307</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -31984,7 +31984,7 @@
         <v>44911</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32057,7 +32057,7 @@
         <v>46307</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32130,7 +32130,7 @@
         <v>45538</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32203,7 +32203,7 @@
         <v>46307</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32276,7 +32276,7 @@
         <v>45175</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32349,7 +32349,7 @@
         <v>44503</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32422,7 +32422,7 @@
         <v>44859</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32495,7 +32495,7 @@
         <v>45167</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32568,7 +32568,7 @@
         <v>44914</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -32641,7 +32641,7 @@
         <v>45574</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -32714,7 +32714,7 @@
         <v>45559</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -32787,7 +32787,7 @@
         <v>45938</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -32860,7 +32860,7 @@
         <v>45722</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -32933,7 +32933,7 @@
         <v>45835</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33006,7 +33006,7 @@
         <v>45531</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33084,7 +33084,7 @@
         <v>46267</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33157,7 +33157,7 @@
         <v>45681</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33230,7 +33230,7 @@
         <v>45911</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33303,7 +33303,7 @@
         <v>45887</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33376,7 +33376,7 @@
         <v>45883</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33449,7 +33449,7 @@
         <v>45817</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33522,7 +33522,7 @@
         <v>45733</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33595,7 +33595,7 @@
         <v>46268</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -33668,7 +33668,7 @@
         <v>45537</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -33741,7 +33741,7 @@
         <v>45531</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -33814,7 +33814,7 @@
         <v>46314</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -33887,7 +33887,7 @@
         <v>46000</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -33965,7 +33965,7 @@
         <v>45328</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34038,7 +34038,7 @@
         <v>46314</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34111,7 +34111,7 @@
         <v>45687</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34184,7 +34184,7 @@
         <v>46313</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34257,7 +34257,7 @@
         <v>45543</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34330,7 +34330,7 @@
         <v>45513</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34403,7 +34403,7 @@
         <v>45930</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34476,7 +34476,7 @@
         <v>45630</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34549,7 +34549,7 @@
         <v>45554</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -34622,7 +34622,7 @@
         <v>45564</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -34695,7 +34695,7 @@
         <v>45254</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -34768,7 +34768,7 @@
         <v>44994</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -34841,7 +34841,7 @@
         <v>46262</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -34914,7 +34914,7 @@
         <v>46140</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -34992,7 +34992,7 @@
         <v>45446</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35065,7 +35065,7 @@
         <v>46147</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35138,7 +35138,7 @@
         <v>46141</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35211,7 +35211,7 @@
         <v>45170</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35284,7 +35284,7 @@
         <v>45594</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35357,7 +35357,7 @@
         <v>45588</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35430,7 +35430,7 @@
         <v>45462</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35503,7 +35503,7 @@
         <v>45258</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -35576,7 +35576,7 @@
         <v>46155</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -35649,7 +35649,7 @@
         <v>45578</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -35722,7 +35722,7 @@
         <v>45308</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -35795,7 +35795,7 @@
         <v>45372</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -35868,7 +35868,7 @@
         <v>45629</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -35941,7 +35941,7 @@
         <v>45145</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36014,7 +36014,7 @@
         <v>45680</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36087,7 +36087,7 @@
         <v>45469</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36165,7 +36165,7 @@
         <v>45078</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36238,7 +36238,7 @@
         <v>45715</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36311,7 +36311,7 @@
         <v>45631</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36384,7 +36384,7 @@
         <v>45051</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36457,7 +36457,7 @@
         <v>45154</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36530,7 +36530,7 @@
         <v>44760</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -36603,7 +36603,7 @@
         <v>45610</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -36676,7 +36676,7 @@
         <v>44526</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -36749,7 +36749,7 @@
         <v>45076</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -36822,7 +36822,7 @@
         <v>45076</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -36895,7 +36895,7 @@
         <v>44826</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -36968,7 +36968,7 @@
         <v>45062</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37041,7 +37041,7 @@
         <v>44496</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37114,7 +37114,7 @@
         <v>44568</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37187,7 +37187,7 @@
         <v>45748</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37260,7 +37260,7 @@
         <v>45716</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37338,7 +37338,7 @@
         <v>45176</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37411,7 +37411,7 @@
         <v>44784</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -37489,7 +37489,7 @@
         <v>45348</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -37562,7 +37562,7 @@
         <v>45244</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -37635,7 +37635,7 @@
         <v>45735</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -37708,7 +37708,7 @@
         <v>45735</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -37781,7 +37781,7 @@
         <v>45273</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -37854,7 +37854,7 @@
         <v>45273</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -37927,7 +37927,7 @@
         <v>44865</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38000,7 +38000,7 @@
         <v>45078</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38073,7 +38073,7 @@
         <v>45113</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38146,7 +38146,7 @@
         <v>45180</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38219,7 +38219,7 @@
         <v>45583</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38292,7 +38292,7 @@
         <v>44529</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38365,7 +38365,7 @@
         <v>45090</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38438,7 +38438,7 @@
         <v>45133</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -38511,7 +38511,7 @@
         <v>44882</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -38584,7 +38584,7 @@
         <v>45467</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -38657,7 +38657,7 @@
         <v>44897</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -38730,7 +38730,7 @@
         <v>44858</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -38803,7 +38803,7 @@
         <v>45374</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -38876,7 +38876,7 @@
         <v>45433</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -38949,7 +38949,7 @@
         <v>44897</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39022,7 +39022,7 @@
         <v>45737</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39095,7 +39095,7 @@
         <v>44942</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39168,7 +39168,7 @@
         <v>45103</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39241,7 +39241,7 @@
         <v>45251</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39314,7 +39314,7 @@
         <v>45251</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39387,7 +39387,7 @@
         <v>45049</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39460,7 +39460,7 @@
         <v>44508</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -39533,7 +39533,7 @@
         <v>45566</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -39606,7 +39606,7 @@
         <v>45001</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -39679,7 +39679,7 @@
         <v>45352</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -39757,7 +39757,7 @@
         <v>44935</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -39830,7 +39830,7 @@
         <v>44992</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -39903,7 +39903,7 @@
         <v>45352</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -39981,7 +39981,7 @@
         <v>45092</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40054,7 +40054,7 @@
         <v>45006</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40132,7 +40132,7 @@
         <v>45092</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40205,7 +40205,7 @@
         <v>45166</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40278,7 +40278,7 @@
         <v>45376</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40351,7 +40351,7 @@
         <v>44942</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40424,7 +40424,7 @@
         <v>45015</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -40497,7 +40497,7 @@
         <v>44543</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -40570,7 +40570,7 @@
         <v>45155</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -40643,7 +40643,7 @@
         <v>45450</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -40716,7 +40716,7 @@
         <v>44523</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -40789,7 +40789,7 @@
         <v>45586</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -40862,7 +40862,7 @@
         <v>45615</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -40935,7 +40935,7 @@
         <v>44958</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41008,7 +41008,7 @@
         <v>45098</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41101,7 +41101,7 @@
         <v>45608</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41174,7 +41174,7 @@
         <v>45156</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41247,7 +41247,7 @@
         <v>45558</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41320,7 +41320,7 @@
         <v>45539</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41393,7 +41393,7 @@
         <v>45133</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41466,7 +41466,7 @@
         <v>45355</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -41539,7 +41539,7 @@
         <v>45355</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -41617,7 +41617,7 @@
         <v>44979</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -41690,7 +41690,7 @@
         <v>45189</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -41763,7 +41763,7 @@
         <v>45010</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -41836,7 +41836,7 @@
         <v>45539</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -41909,7 +41909,7 @@
         <v>45355</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -41987,7 +41987,7 @@
         <v>45720</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42060,7 +42060,7 @@
         <v>45462</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42133,7 +42133,7 @@
         <v>45049</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42206,7 +42206,7 @@
         <v>45706</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42279,7 +42279,7 @@
         <v>45282</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42352,7 +42352,7 @@
         <v>44686</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42425,7 +42425,7 @@
         <v>45350</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -42498,7 +42498,7 @@
         <v>45616</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -42571,7 +42571,7 @@
         <v>44636</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -42644,7 +42644,7 @@
         <v>45191</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -42717,7 +42717,7 @@
         <v>45716</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -42795,7 +42795,7 @@
         <v>44531</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -42868,7 +42868,7 @@
         <v>44587</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -42941,7 +42941,7 @@
         <v>45062</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43014,7 +43014,7 @@
         <v>45677</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43087,7 +43087,7 @@
         <v>45222</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43160,7 +43160,7 @@
         <v>44592</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43233,7 +43233,7 @@
         <v>45215</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43306,7 +43306,7 @@
         <v>45653</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43379,7 +43379,7 @@
         <v>44859</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43452,7 +43452,7 @@
         <v>44634</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -43525,7 +43525,7 @@
         <v>44861</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -43598,7 +43598,7 @@
         <v>45625</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -43671,7 +43671,7 @@
         <v>45716</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -43744,7 +43744,7 @@
         <v>44698</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -43817,7 +43817,7 @@
         <v>45771</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -43890,7 +43890,7 @@
         <v>45240</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -43968,7 +43968,7 @@
         <v>45166</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44041,7 +44041,7 @@
         <v>45460</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44114,7 +44114,7 @@
         <v>45693</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44187,7 +44187,7 @@
         <v>45698</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44260,7 +44260,7 @@
         <v>45202</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44333,7 +44333,7 @@
         <v>45180</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44406,7 +44406,7 @@
         <v>45211</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44479,7 +44479,7 @@
         <v>45214</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -44552,7 +44552,7 @@
         <v>45175</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -44625,7 +44625,7 @@
         <v>45175</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -44698,7 +44698,7 @@
         <v>45187</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -44771,7 +44771,7 @@
         <v>45681</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -44844,7 +44844,7 @@
         <v>45233</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -44917,7 +44917,7 @@
         <v>45233</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -44990,7 +44990,7 @@
         <v>45612</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45063,7 +45063,7 @@
         <v>45770</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45136,7 +45136,7 @@
         <v>45246</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45209,7 +45209,7 @@
         <v>45679</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45282,7 +45282,7 @@
         <v>45531</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45355,7 +45355,7 @@
         <v>45352</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45433,7 +45433,7 @@
         <v>45250</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -45506,7 +45506,7 @@
         <v>45250</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -45579,7 +45579,7 @@
         <v>45253</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -45652,7 +45652,7 @@
         <v>45421</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -45725,7 +45725,7 @@
         <v>45211</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -45798,7 +45798,7 @@
         <v>45084</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -45871,7 +45871,7 @@
         <v>44496</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -45944,7 +45944,7 @@
         <v>45051</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46017,7 +46017,7 @@
         <v>45268</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46090,7 +46090,7 @@
         <v>45469</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46163,7 +46163,7 @@
         <v>45175</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46236,7 +46236,7 @@
         <v>44876</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46309,7 +46309,7 @@
         <v>45440</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46382,7 +46382,7 @@
         <v>44921</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -46455,7 +46455,7 @@
         <v>45734</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -46528,7 +46528,7 @@
         <v>45608</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -46601,7 +46601,7 @@
         <v>45546</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -46674,7 +46674,7 @@
         <v>44621</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -46747,7 +46747,7 @@
         <v>44858</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -46820,7 +46820,7 @@
         <v>45187</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -46893,7 +46893,7 @@
         <v>45412</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -46966,7 +46966,7 @@
         <v>45414</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47039,7 +47039,7 @@
         <v>44992</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47112,7 +47112,7 @@
         <v>44610</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47185,7 +47185,7 @@
         <v>44992</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47258,7 +47258,7 @@
         <v>44634</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -47331,7 +47331,7 @@
         <v>44658</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -47404,7 +47404,7 @@
         <v>44621</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -47477,7 +47477,7 @@
         <v>44607</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -47550,7 +47550,7 @@
         <v>44733</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -47628,7 +47628,7 @@
         <v>45302</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -47701,7 +47701,7 @@
         <v>45476</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -47774,7 +47774,7 @@
         <v>45649</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -47847,7 +47847,7 @@
         <v>45728</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -47920,7 +47920,7 @@
         <v>45953</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -47993,7 +47993,7 @@
         <v>45967</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48066,7 +48066,7 @@
         <v>46010</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48139,7 +48139,7 @@
         <v>46010</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -48212,7 +48212,7 @@
         <v>46029</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -48290,7 +48290,7 @@
         <v>46079</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -48363,7 +48363,7 @@
         <v>46094</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -48436,7 +48436,7 @@
         <v>46119</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -48509,7 +48509,7 @@
         <v>46182</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
